--- a/kapremont/output/Квитанции_квартальные_цветной.xlsx
+++ b/kapremont/output/Квитанции_квартальные_цветной.xlsx
@@ -26,12 +26,12 @@
     <definedName name="ИД_НАЧИСЛЕНО_МЕС">'ИСХОДНЫЕ ДАННЫЕ'!$C$8</definedName>
     <definedName name="ИД_ЛС">'ИСХОДНЫЕ ДАННЫЕ'!$C$11</definedName>
     <definedName name="ИД_КВАРТИРА">'ИСХОДНЫЕ ДАННЫЕ'!$C$12</definedName>
-    <definedName name="ИД_КВАРТАЛЫ">'ИСХОДНЫЕ ДАННЫЕ'!$B$30:$G$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'ИСХОДНЫЕ ДАННЫЕ'!$B$1:$G$50</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Квитанция 1 кв'!$A$1:$I$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Квитанция 2 кв'!$A$1:$I$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Квитанция 3 кв'!$A$1:$I$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Квитанция 4 кв'!$A$1:$I$44</definedName>
+    <definedName name="ИД_КВАРТАЛЫ">'ИСХОДНЫЕ ДАННЫЕ'!$B$30:$F$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'ИСХОДНЫЕ ДАННЫЕ'!$B$1:$F$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Квитанция 1 кв'!$A$1:$I$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Квитанция 2 кв'!$A$1:$I$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Квитанция 3 кв'!$A$1:$I$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Квитанция 4 кв'!$A$1:$I$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Письмо 1 кв'!$A$1:$G$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Письмо 2 кв'!$A$1:$G$28</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'Письмо 3 кв'!$A$1:$G$28</definedName>
@@ -392,7 +392,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -575,9 +575,6 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="4" fontId="17" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1132,11 +1129,11 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>31202</v>
+        <v>3120247</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Из образца</t>
+          <t>Лицевой счёт помещения по этому адресу</t>
         </is>
       </c>
     </row>
@@ -1384,11 +1381,6 @@
           <t>Поступило с начала года, руб.</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
-        <is>
-          <t>Остаток на спец. счёте, руб.</t>
-        </is>
-      </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="4" t="inlineStr">
@@ -1408,7 +1400,6 @@
         <v>46051</v>
       </c>
       <c r="F30" s="11" t="n"/>
-      <c r="G30" s="11" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="4" t="inlineStr">
@@ -1424,7 +1415,6 @@
         <v>46127</v>
       </c>
       <c r="F31" s="11" t="n"/>
-      <c r="G31" s="11" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="4" t="inlineStr">
@@ -1440,7 +1430,6 @@
         <v>46218</v>
       </c>
       <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="4" t="inlineStr">
@@ -1456,12 +1445,11 @@
         <v>46310</v>
       </c>
       <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Задолженность и даты — единственное, что меняется от квартала к кварталу. Столбцы «Поступило» и «Остаток» можно не заполнять: в квитанции тогда встанет прочерк.</t>
+          <t>Задолженность и даты — единственное, что меняется от квартала к кварталу. Столбец «Поступило» можно не заполнять: в квитанции тогда встанет прочерк.</t>
         </is>
       </c>
     </row>
@@ -1659,189 +1647,189 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="D1" s="80">
+      <c r="D1" s="79">
         <f>"В "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$24</f>
         <v/>
       </c>
-      <c r="E1" s="80" t="n"/>
-      <c r="F1" s="80" t="n"/>
+      <c r="E1" s="79" t="n"/>
+      <c r="F1" s="79" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="D2" s="80">
+      <c r="D2" s="79">
         <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$26="","",'ИСХОДНЫЕ ДАННЫЕ'!$C$25&amp;" "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$26)</f>
         <v/>
       </c>
-      <c r="E2" s="80" t="n"/>
-      <c r="F2" s="80" t="n"/>
+      <c r="E2" s="79" t="n"/>
+      <c r="F2" s="79" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="D3" s="81">
+      <c r="D3" s="80">
         <f>"от Председателя МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;", "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$18</f>
         <v/>
       </c>
-      <c r="E3" s="81" t="n"/>
-      <c r="F3" s="81" t="n"/>
+      <c r="E3" s="80" t="n"/>
+      <c r="F3" s="80" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="D4" s="81">
+      <c r="D4" s="80">
         <f>"проживающей по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$20</f>
         <v/>
       </c>
-      <c r="E4" s="81" t="n"/>
-      <c r="F4" s="81" t="n"/>
+      <c r="E4" s="80" t="n"/>
+      <c r="F4" s="80" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="D5" s="81">
+      <c r="D5" s="80">
         <f>"Конт. тел.: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21</f>
         <v/>
       </c>
-      <c r="E5" s="81" t="n"/>
-      <c r="F5" s="81" t="n"/>
+      <c r="E5" s="80" t="n"/>
+      <c r="F5" s="80" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="D6" s="81">
+      <c r="D6" s="80">
         <f>"Эл. почта: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22</f>
         <v/>
       </c>
-      <c r="E6" s="81" t="n"/>
-      <c r="F6" s="81" t="n"/>
+      <c r="E6" s="80" t="n"/>
+      <c r="F6" s="80" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1"/>
     <row r="8" ht="46" customHeight="1">
-      <c r="B8" s="81">
+      <c r="B8" s="80">
         <f>"В связи с тем, что на балансе департамента числится кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", сообщаю Вам о необходимости оплатить "&amp;IF(INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2)*100,0)-INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))*100),"00")&amp;" руб., в том числе:"</f>
         <v/>
       </c>
-      <c r="C8" s="81" t="n"/>
-      <c r="D8" s="81" t="n"/>
-      <c r="E8" s="81" t="n"/>
-      <c r="F8" s="81" t="n"/>
+      <c r="C8" s="80" t="n"/>
+      <c r="D8" s="80" t="n"/>
+      <c r="E8" s="80" t="n"/>
+      <c r="F8" s="80" t="n"/>
     </row>
     <row r="9" ht="8" customHeight="1"/>
     <row r="10" ht="32" customHeight="1">
-      <c r="B10" s="81">
+      <c r="B10" s="80">
         <f>"— текущий платёж за период с октября по декабрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года ("&amp;"IV квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;") в размере "&amp;IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100),"00")&amp;" рублей"</f>
         <v/>
       </c>
-      <c r="C10" s="81" t="n"/>
-      <c r="D10" s="81" t="n"/>
-      <c r="E10" s="81" t="n"/>
-      <c r="F10" s="81" t="n"/>
+      <c r="C10" s="80" t="n"/>
+      <c r="D10" s="80" t="n"/>
+      <c r="E10" s="80" t="n"/>
+      <c r="F10" s="80" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="82">
+      <c r="B11" s="81">
         <f>"("&amp;UPPER(LEFT(IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)=0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)=0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1),2,300)&amp;")."</f>
         <v/>
       </c>
-      <c r="C11" s="82" t="n"/>
-      <c r="D11" s="82" t="n"/>
-      <c r="E11" s="82" t="n"/>
-      <c r="F11" s="82" t="n"/>
+      <c r="C11" s="81" t="n"/>
+      <c r="D11" s="81" t="n"/>
+      <c r="E11" s="81" t="n"/>
+      <c r="F11" s="81" t="n"/>
     </row>
     <row r="12" ht="6" customHeight="1"/>
     <row r="13" ht="32" customHeight="1">
-      <c r="B13" s="81">
+      <c r="B13" s="80">
         <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$33=0,"— задолженности за предыдущие периоды нет.","— задолженность "&amp;IF('ИСХОДНЫЕ ДАННЫЕ'!$D$33="","за предыдущие периоды",'ИСХОДНЫЕ ДАННЫЕ'!$D$33)&amp;" в размере "&amp;IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)&gt;0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)&amp;" "&amp;TEXT((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000),"000"),(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))*100),"00")&amp;" рублей")</f>
         <v/>
       </c>
-      <c r="C13" s="81" t="n"/>
-      <c r="D13" s="81" t="n"/>
-      <c r="E13" s="81" t="n"/>
-      <c r="F13" s="81" t="n"/>
+      <c r="C13" s="80" t="n"/>
+      <c r="D13" s="80" t="n"/>
+      <c r="E13" s="80" t="n"/>
+      <c r="F13" s="80" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="82">
+      <c r="B14" s="81">
         <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$33=0,"","("&amp;UPPER(LEFT(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))*100)+1),2,300)&amp;").")</f>
         <v/>
       </c>
-      <c r="C14" s="82" t="n"/>
-      <c r="D14" s="82" t="n"/>
-      <c r="E14" s="82" t="n"/>
-      <c r="F14" s="82" t="n"/>
+      <c r="C14" s="81" t="n"/>
+      <c r="D14" s="81" t="n"/>
+      <c r="E14" s="81" t="n"/>
+      <c r="F14" s="81" t="n"/>
     </row>
     <row r="15" ht="10" customHeight="1"/>
     <row r="16" ht="76" customHeight="1">
-      <c r="B16" s="81">
+      <c r="B16" s="80">
         <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$33)&amp;" и с учётом начислений по "&amp;"декабрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
       </c>
-      <c r="C16" s="81" t="n"/>
-      <c r="D16" s="81" t="n"/>
-      <c r="E16" s="81" t="n"/>
-      <c r="F16" s="81" t="n"/>
+      <c r="C16" s="80" t="n"/>
+      <c r="D16" s="80" t="n"/>
+      <c r="E16" s="80" t="n"/>
+      <c r="F16" s="80" t="n"/>
     </row>
     <row r="17" ht="10" customHeight="1"/>
     <row r="18" ht="46" customHeight="1">
-      <c r="B18" s="81">
+      <c r="B18" s="80">
         <f>"В случае возникновения дополнительных вопросов прошу связаться со мной по электронной почте "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22&amp;" или по телефону "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
       </c>
-      <c r="C18" s="81" t="n"/>
-      <c r="D18" s="81" t="n"/>
-      <c r="E18" s="81" t="n"/>
-      <c r="F18" s="81" t="n"/>
+      <c r="C18" s="80" t="n"/>
+      <c r="D18" s="80" t="n"/>
+      <c r="E18" s="80" t="n"/>
+      <c r="F18" s="80" t="n"/>
     </row>
     <row r="19" ht="14" customHeight="1"/>
     <row r="20" ht="20" customHeight="1">
-      <c r="B20" s="80" t="inlineStr">
+      <c r="B20" s="79" t="inlineStr">
         <is>
           <t>ПРИЛОЖЕНИЯ:</t>
         </is>
       </c>
-      <c r="C20" s="80" t="n"/>
-      <c r="D20" s="80" t="n"/>
-      <c r="E20" s="80" t="n"/>
-      <c r="F20" s="80" t="n"/>
+      <c r="C20" s="79" t="n"/>
+      <c r="D20" s="79" t="n"/>
+      <c r="E20" s="79" t="n"/>
+      <c r="F20" s="79" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="81">
+      <c r="B21" s="80">
         <f>"1) Акт взаимных расчётов по состоянию на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$33)&amp;" — один экземпляр на 1 л."</f>
         <v/>
       </c>
-      <c r="C21" s="81" t="n"/>
-      <c r="D21" s="81" t="n"/>
-      <c r="E21" s="81" t="n"/>
-      <c r="F21" s="81" t="n"/>
+      <c r="C21" s="80" t="n"/>
+      <c r="D21" s="80" t="n"/>
+      <c r="E21" s="80" t="n"/>
+      <c r="F21" s="80" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="81">
+      <c r="B22" s="80">
         <f>"2) Квитанция для оплаты за "&amp;"IV квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — один экземпляр на 1 л."</f>
         <v/>
       </c>
-      <c r="C22" s="81" t="n"/>
-      <c r="D22" s="81" t="n"/>
-      <c r="E22" s="81" t="n"/>
-      <c r="F22" s="81" t="n"/>
+      <c r="C22" s="80" t="n"/>
+      <c r="D22" s="80" t="n"/>
+      <c r="E22" s="80" t="n"/>
+      <c r="F22" s="80" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1"/>
     <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="81">
+      <c r="B24" s="80">
         <f>"«______» ______________ "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="C24" s="81" t="n"/>
+      <c r="C24" s="80" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1"/>
     <row r="26" ht="16" customHeight="1">
-      <c r="B26" s="81" t="inlineStr">
+      <c r="B26" s="80" t="inlineStr">
         <is>
           <t>Председатель</t>
         </is>
       </c>
-      <c r="C26" s="81" t="n"/>
+      <c r="C26" s="80" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="B27" s="81">
+      <c r="B27" s="80">
         <f>"МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15</f>
         <v/>
       </c>
-      <c r="C27" s="81" t="n"/>
-      <c r="D27" s="83">
+      <c r="C27" s="80" t="n"/>
+      <c r="D27" s="82">
         <f>"___________________  /"&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$19&amp;"/"</f>
         <v/>
       </c>
-      <c r="E27" s="83" t="n"/>
-      <c r="F27" s="83" t="n"/>
+      <c r="E27" s="82" t="n"/>
+      <c r="F27" s="82" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -1889,141 +1877,141 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="84" t="inlineStr">
+      <c r="A1" s="83" t="inlineStr">
         <is>
           <t>КВАРТАЛЬНЫЕ КВИТАНЦИИ И ПИСЬМА — КАК ПОЛЬЗОВАТЬСЯ</t>
         </is>
       </c>
     </row>
     <row r="2" ht="8" customHeight="1">
-      <c r="A2" s="85" t="inlineStr"/>
+      <c r="A2" s="84" t="inlineStr"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="86" t="inlineStr">
+      <c r="A3" s="85" t="inlineStr">
         <is>
           <t>1. Где вводить данные</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="87" t="inlineStr">
+      <c r="A4" s="86" t="inlineStr">
         <is>
           <t>Всё вводится на листе «ИСХОДНЫЕ ДАННЫЕ», в жёлтых ячейках. Остальные девять листов — расчётные: они читают эти значения формулами и пересчитываются сами.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="87" t="inlineStr">
+      <c r="A5" s="86" t="inlineStr">
         <is>
           <t>Ежегодно меняется только тариф (блок 1). Поменяли размер взноса и год — все четыре квитанции и все четыре письма обновились.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="87" t="inlineStr">
+      <c r="A6" s="86" t="inlineStr">
         <is>
           <t>Начисление за месяц по умолчанию считается как площадь × тариф. Если сумму нужно задать вручную, замените в ячейке формулу числом.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="8" customHeight="1">
-      <c r="A7" s="85" t="inlineStr"/>
+      <c r="A7" s="84" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="86" t="inlineStr">
+      <c r="A8" s="85" t="inlineStr">
         <is>
           <t>2. Задолженность по кварталам</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="87" t="inlineStr">
+      <c r="A9" s="86" t="inlineStr">
         <is>
           <t>Блок 5 листа «ИСХОДНЫЕ ДАННЫЕ» — таблица на четыре строки. Для каждого квартала укажите сумму задолженности, её описание (оно попадёт и в квитанцию, и в письмо) и дату формирования.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="87" t="inlineStr">
+      <c r="A10" s="86" t="inlineStr">
         <is>
           <t>Если задолженности нет, поставьте 0: в письме вместо строки о долге напечатается «задолженности за предыдущие периоды нет», а в квитанции строка останется с нулём.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="8" customHeight="1">
-      <c r="A11" s="85" t="inlineStr"/>
+      <c r="A11" s="84" t="inlineStr"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="86" t="inlineStr">
+      <c r="A12" s="85" t="inlineStr">
         <is>
           <t>3. Сопроводительное письмо</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="87" t="inlineStr">
+      <c r="A13" s="86" t="inlineStr">
         <is>
           <t>Суммы, периоды, даты и приложения подтягиваются автоматически. Сумма прописью считается формулами по скрытому листу ПРОПИСЬ — макросы для этого не нужны, книга остаётся обычным .xlsx.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="87" t="inlineStr">
+      <c r="A14" s="86" t="inlineStr">
         <is>
           <t>Адресат письма — блок 4. Должность и ФИО руководителя правятся здесь; при смене директора достаточно поменять их один раз. Если ФИО оставить пустым, строка с ним не напечатается.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="8" customHeight="1">
-      <c r="A15" s="85" t="inlineStr"/>
+      <c r="A15" s="84" t="inlineStr"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="86" t="inlineStr">
+      <c r="A16" s="85" t="inlineStr">
         <is>
           <t>4. Печать</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="87" t="inlineStr">
+      <c r="A17" s="86" t="inlineStr">
         <is>
           <t>Каждый лист настроен на одну страницу А4. Квитанции — книжная ориентация, поля 6 мм; письма — стандартные поля 20/15 мм.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="87" t="inlineStr">
+      <c r="A18" s="86" t="inlineStr">
         <is>
           <t>Книга сохранена в чёрно-белом виде: заливок нет, акценты сделаны кеглем, полужирным и рамками. Цветной вариант для отправки по электронной почте лежит отдельным файлом.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="8" customHeight="1">
-      <c r="A19" s="85" t="inlineStr"/>
+      <c r="A19" s="84" t="inlineStr"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="86" t="inlineStr">
+      <c r="A20" s="85" t="inlineStr">
         <is>
           <t>5. Что проверить</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="87" t="inlineStr">
+      <c r="A21" s="86" t="inlineStr">
         <is>
           <t>• Тариф 15,30 руб./м² и площадь 52,8 м² взяты из вашего образца за I квартал 2026 года. Начисление выходит 807,84 руб. в месяц и 2 423,52 руб. за квартал — совпадает с образцом.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="87" t="inlineStr">
+      <c r="A22" s="86" t="inlineStr">
         <is>
           <t>• Задолженность 4 042,38 руб. проставлена только для I квартала. Для остальных кварталов стоят нули — заполните их по факту.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="87" t="inlineStr">
+      <c r="A23" s="86" t="inlineStr">
         <is>
           <t>• В образце письма период января–марта 2026 года был подписан как «I квартал 2025 г.» — в шаблоне это исправлено на 2026 год.</t>
         </is>
@@ -32112,7 +32100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H44"/>
+  <dimension ref="B2:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.8" customWidth="1" min="1" max="1"/>
@@ -32564,65 +32552,49 @@
       <c r="H28" s="25" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="53">
+      <c r="B29" s="64">
         <f>"Поступило оплат по лицевому счёту с начала "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года, руб."</f>
         <v/>
       </c>
-      <c r="C29" s="30" t="n"/>
-      <c r="D29" s="30" t="n"/>
-      <c r="E29" s="30" t="n"/>
-      <c r="F29" s="30" t="n"/>
-      <c r="G29" s="64">
+      <c r="C29" s="36" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="36" t="n"/>
+      <c r="F29" s="36" t="n"/>
+      <c r="G29" s="65">
         <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$F$30="","—",'ИСХОДНЫЕ ДАННЫЕ'!$F$30)</f>
         <v/>
       </c>
-      <c r="H29" s="55" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="B30" s="65" t="inlineStr">
-        <is>
-          <t>Остаток средств на специальном счёте многоквартирного дома, руб.</t>
-        </is>
-      </c>
-      <c r="C30" s="36" t="n"/>
-      <c r="D30" s="36" t="n"/>
-      <c r="E30" s="36" t="n"/>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="66">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$G$30="","—",'ИСХОДНЫЕ ДАННЫЕ'!$G$30)</f>
-        <v/>
-      </c>
-      <c r="H30" s="67" t="n"/>
-    </row>
-    <row r="31" ht="5" customHeight="1"/>
-    <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="23" t="inlineStr">
+      <c r="H29" s="66" t="n"/>
+    </row>
+    <row r="30" ht="5" customHeight="1"/>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>5. ПОРЯДОК ОПЛАТЫ</t>
         </is>
       </c>
-      <c r="C32" s="24" t="n"/>
-      <c r="D32" s="24" t="n"/>
-      <c r="E32" s="24" t="n"/>
-      <c r="F32" s="24" t="n"/>
-      <c r="G32" s="24" t="n"/>
-      <c r="H32" s="25" t="n"/>
-    </row>
-    <row r="33" ht="14" customHeight="1">
-      <c r="B33" s="68" t="inlineStr">
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="24" t="n"/>
+      <c r="E31" s="24" t="n"/>
+      <c r="F31" s="24" t="n"/>
+      <c r="G31" s="24" t="n"/>
+      <c r="H31" s="25" t="n"/>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="B32" s="67" t="inlineStr">
         <is>
           <t>1) без комиссии — в отделениях АО «Россельхозбанк» (банк, в котором открыт специальный счёт дома);</t>
         </is>
       </c>
-      <c r="C33" s="69" t="n"/>
-      <c r="D33" s="69" t="n"/>
-      <c r="E33" s="69" t="n"/>
-      <c r="F33" s="69" t="n"/>
-      <c r="G33" s="70" t="n"/>
-      <c r="H33" s="71" t="n"/>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="B34" s="68" t="inlineStr">
+      <c r="C32" s="68" t="n"/>
+      <c r="D32" s="68" t="n"/>
+      <c r="E32" s="68" t="n"/>
+      <c r="F32" s="68" t="n"/>
+      <c r="G32" s="69" t="n"/>
+      <c r="H32" s="70" t="n"/>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="B33" s="67" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32651,63 +32623,75 @@
           </r>
         </is>
       </c>
-      <c r="C34" s="69" t="n"/>
-      <c r="D34" s="69" t="n"/>
-      <c r="E34" s="69" t="n"/>
-      <c r="F34" s="69" t="n"/>
-      <c r="G34" s="70" t="n"/>
-      <c r="H34" s="71" t="n"/>
+      <c r="C33" s="68" t="n"/>
+      <c r="D33" s="68" t="n"/>
+      <c r="E33" s="68" t="n"/>
+      <c r="F33" s="68" t="n"/>
+      <c r="G33" s="69" t="n"/>
+      <c r="H33" s="70" t="n"/>
+    </row>
+    <row r="34" ht="14" customHeight="1">
+      <c r="B34" s="67" t="n"/>
+      <c r="C34" s="68" t="n"/>
+      <c r="D34" s="68" t="n"/>
+      <c r="E34" s="68" t="n"/>
+      <c r="F34" s="68" t="n"/>
+      <c r="G34" s="69" t="n"/>
+      <c r="H34" s="70" t="n"/>
     </row>
     <row r="35" ht="14" customHeight="1">
-      <c r="B35" s="68" t="n"/>
-      <c r="C35" s="69" t="n"/>
-      <c r="D35" s="69" t="n"/>
-      <c r="E35" s="69" t="n"/>
-      <c r="F35" s="69" t="n"/>
-      <c r="G35" s="70" t="n"/>
-      <c r="H35" s="71" t="n"/>
-    </row>
-    <row r="36" ht="14" customHeight="1">
-      <c r="B36" s="29" t="inlineStr">
+      <c r="B35" s="29" t="inlineStr">
         <is>
           <t>Назначение платежа:</t>
         </is>
       </c>
-      <c r="C36" s="32" t="n"/>
-      <c r="D36" s="32" t="n"/>
-      <c r="E36" s="32" t="n"/>
-      <c r="F36" s="32" t="n"/>
-      <c r="G36" s="70" t="n"/>
-      <c r="H36" s="71" t="n"/>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="B37" s="68">
+      <c r="C35" s="32" t="n"/>
+      <c r="D35" s="32" t="n"/>
+      <c r="E35" s="32" t="n"/>
+      <c r="F35" s="32" t="n"/>
+      <c r="G35" s="69" t="n"/>
+      <c r="H35" s="70" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="B36" s="67">
         <f>"Взнос на капитальный ремонт, л/с № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;", кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;", за "&amp;"I квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="C37" s="69" t="n"/>
-      <c r="D37" s="69" t="n"/>
-      <c r="E37" s="69" t="n"/>
-      <c r="F37" s="69" t="n"/>
-      <c r="G37" s="70" t="n"/>
-      <c r="H37" s="71" t="n"/>
-    </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="B38" s="72">
+      <c r="C36" s="68" t="n"/>
+      <c r="D36" s="68" t="n"/>
+      <c r="E36" s="68" t="n"/>
+      <c r="F36" s="68" t="n"/>
+      <c r="G36" s="69" t="n"/>
+      <c r="H36" s="70" t="n"/>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="B37" s="71">
         <f>"Срок оплаты: до "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$49&amp;" числа месяца, следующего за расчётным (за "&amp;"I квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — до "&amp;TEXT(DAY(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,3+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49)),"00")&amp;"."&amp;TEXT(MONTH(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,3+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49)),"00")&amp;"."&amp;YEAR(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,3+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49))&amp;")."&amp;CHAR(10)&amp;"Основание: ч. 1 ст. 155, ч. 2 ст. 171 ЖК РФ."</f>
         <v/>
       </c>
-      <c r="C38" s="73" t="n"/>
-      <c r="D38" s="73" t="n"/>
-      <c r="E38" s="73" t="n"/>
-      <c r="F38" s="73" t="n"/>
-      <c r="G38" s="74" t="n"/>
-      <c r="H38" s="75" t="n"/>
-    </row>
-    <row r="39" ht="5" customHeight="1"/>
-    <row r="40" ht="32" customHeight="1">
+      <c r="C37" s="72" t="n"/>
+      <c r="D37" s="72" t="n"/>
+      <c r="E37" s="72" t="n"/>
+      <c r="F37" s="72" t="n"/>
+      <c r="G37" s="73" t="n"/>
+      <c r="H37" s="74" t="n"/>
+    </row>
+    <row r="38" ht="5" customHeight="1"/>
+    <row r="39" ht="32" customHeight="1">
+      <c r="B39" s="75">
+        <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
+        <v/>
+      </c>
+      <c r="C39" s="75" t="n"/>
+      <c r="D39" s="75" t="n"/>
+      <c r="E39" s="75" t="n"/>
+      <c r="F39" s="75" t="n"/>
+      <c r="G39" s="75" t="n"/>
+      <c r="H39" s="75" t="n"/>
+    </row>
+    <row r="40" ht="44" customHeight="1">
       <c r="B40" s="76">
-        <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
+        <f>"В отделении банка и в мобильном приложении во вкладках ищите "&amp;"«РФКР МКД_капремонт, оплата по расчётному счёту» и указывайте номер расчётного счёта, приведённый выше. Оплата через общий поиск «Капитальный ремонт» уходит на общий счёт Регионального фонда капитального ремонта и на счёт вашего дома не поступает."&amp;CHAR(10)&amp;"Лицевой счёт № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;" при оплате НЕ вводится — он указан справочно, только для учёта начислений."</f>
         <v/>
       </c>
       <c r="C40" s="76" t="n"/>
@@ -32717,84 +32701,72 @@
       <c r="G40" s="76" t="n"/>
       <c r="H40" s="76" t="n"/>
     </row>
-    <row r="41" ht="44" customHeight="1">
-      <c r="B41" s="77">
-        <f>"В отделении банка и в мобильном приложении во вкладках ищите "&amp;"«РФКР МКД_капремонт, оплата по расчётному счёту» и указывайте номер расчётного счёта, приведённый выше. Оплата через общий поиск «Капитальный ремонт» уходит на общий счёт Регионального фонда капитального ремонта и на счёт вашего дома не поступает."&amp;CHAR(10)&amp;"Лицевой счёт № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;" при оплате НЕ вводится — он указан справочно, только для учёта начислений."</f>
+    <row r="41" ht="6" customHeight="1"/>
+    <row r="42" ht="24" customHeight="1">
+      <c r="B42" s="77" t="inlineStr">
+        <is>
+          <t>Подпись плательщика  ______________________</t>
+        </is>
+      </c>
+      <c r="C42" s="77" t="n"/>
+      <c r="D42" s="77" t="n"/>
+      <c r="E42" s="77" t="inlineStr">
+        <is>
+          <t>Кассир  ______________</t>
+        </is>
+      </c>
+      <c r="F42" s="77" t="n"/>
+      <c r="G42" s="77" t="inlineStr">
+        <is>
+          <t>Дата  ____________</t>
+        </is>
+      </c>
+      <c r="H42" s="77" t="n"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="B43" s="78">
+        <f>"Начисление за "&amp;"I квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;"    По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
-      </c>
-      <c r="C41" s="77" t="n"/>
-      <c r="D41" s="77" t="n"/>
-      <c r="E41" s="77" t="n"/>
-      <c r="F41" s="77" t="n"/>
-      <c r="G41" s="77" t="n"/>
-      <c r="H41" s="77" t="n"/>
-    </row>
-    <row r="42" ht="6" customHeight="1"/>
-    <row r="43" ht="24" customHeight="1">
-      <c r="B43" s="78" t="inlineStr">
-        <is>
-          <t>Подпись плательщика  ______________________</t>
-        </is>
       </c>
       <c r="C43" s="78" t="n"/>
       <c r="D43" s="78" t="n"/>
-      <c r="E43" s="78" t="inlineStr">
-        <is>
-          <t>Кассир  ______________</t>
-        </is>
-      </c>
+      <c r="E43" s="78" t="n"/>
       <c r="F43" s="78" t="n"/>
-      <c r="G43" s="78" t="inlineStr">
-        <is>
-          <t>Дата  ____________</t>
-        </is>
-      </c>
+      <c r="G43" s="78" t="n"/>
       <c r="H43" s="78" t="n"/>
     </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="B44" s="79">
-        <f>"Начисление за "&amp;"I квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;"    По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
-        <v/>
-      </c>
-      <c r="C44" s="79" t="n"/>
-      <c r="D44" s="79" t="n"/>
-      <c r="E44" s="79" t="n"/>
-      <c r="F44" s="79" t="n"/>
-      <c r="G44" s="79" t="n"/>
-      <c r="H44" s="79" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="E43:F43"/>
+  <mergeCells count="48">
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
-    <mergeCell ref="G43:H43"/>
     <mergeCell ref="B40:H40"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="F25:G25"/>
+    <mergeCell ref="G42:H42"/>
     <mergeCell ref="F8:H8"/>
+    <mergeCell ref="E42:F42"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B32:H32"/>
     <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B41:H41"/>
-    <mergeCell ref="G33:H38"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B31:H31"/>
     <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="G30:H30"/>
     <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G32:H37"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B39:H39"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="F22:G22"/>
@@ -32803,14 +32775,12 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C15:H15"/>
     <mergeCell ref="G29:H29"/>
-    <mergeCell ref="B30:F30"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B44:H44"/>
     <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B28:H28"/>
@@ -32828,7 +32798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H44"/>
+  <dimension ref="B2:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.8" customWidth="1" min="1" max="1"/>
@@ -33280,65 +33250,49 @@
       <c r="H28" s="25" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="53">
+      <c r="B29" s="64">
         <f>"Поступило оплат по лицевому счёту с начала "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года, руб."</f>
         <v/>
       </c>
-      <c r="C29" s="30" t="n"/>
-      <c r="D29" s="30" t="n"/>
-      <c r="E29" s="30" t="n"/>
-      <c r="F29" s="30" t="n"/>
-      <c r="G29" s="64">
+      <c r="C29" s="36" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="36" t="n"/>
+      <c r="F29" s="36" t="n"/>
+      <c r="G29" s="65">
         <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$F$31="","—",'ИСХОДНЫЕ ДАННЫЕ'!$F$31)</f>
         <v/>
       </c>
-      <c r="H29" s="55" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="B30" s="65" t="inlineStr">
-        <is>
-          <t>Остаток средств на специальном счёте многоквартирного дома, руб.</t>
-        </is>
-      </c>
-      <c r="C30" s="36" t="n"/>
-      <c r="D30" s="36" t="n"/>
-      <c r="E30" s="36" t="n"/>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="66">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$G$31="","—",'ИСХОДНЫЕ ДАННЫЕ'!$G$31)</f>
-        <v/>
-      </c>
-      <c r="H30" s="67" t="n"/>
-    </row>
-    <row r="31" ht="5" customHeight="1"/>
-    <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="23" t="inlineStr">
+      <c r="H29" s="66" t="n"/>
+    </row>
+    <row r="30" ht="5" customHeight="1"/>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>5. ПОРЯДОК ОПЛАТЫ</t>
         </is>
       </c>
-      <c r="C32" s="24" t="n"/>
-      <c r="D32" s="24" t="n"/>
-      <c r="E32" s="24" t="n"/>
-      <c r="F32" s="24" t="n"/>
-      <c r="G32" s="24" t="n"/>
-      <c r="H32" s="25" t="n"/>
-    </row>
-    <row r="33" ht="14" customHeight="1">
-      <c r="B33" s="68" t="inlineStr">
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="24" t="n"/>
+      <c r="E31" s="24" t="n"/>
+      <c r="F31" s="24" t="n"/>
+      <c r="G31" s="24" t="n"/>
+      <c r="H31" s="25" t="n"/>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="B32" s="67" t="inlineStr">
         <is>
           <t>1) без комиссии — в отделениях АО «Россельхозбанк» (банк, в котором открыт специальный счёт дома);</t>
         </is>
       </c>
-      <c r="C33" s="69" t="n"/>
-      <c r="D33" s="69" t="n"/>
-      <c r="E33" s="69" t="n"/>
-      <c r="F33" s="69" t="n"/>
-      <c r="G33" s="70" t="n"/>
-      <c r="H33" s="71" t="n"/>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="B34" s="68" t="inlineStr">
+      <c r="C32" s="68" t="n"/>
+      <c r="D32" s="68" t="n"/>
+      <c r="E32" s="68" t="n"/>
+      <c r="F32" s="68" t="n"/>
+      <c r="G32" s="69" t="n"/>
+      <c r="H32" s="70" t="n"/>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="B33" s="67" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33367,63 +33321,75 @@
           </r>
         </is>
       </c>
-      <c r="C34" s="69" t="n"/>
-      <c r="D34" s="69" t="n"/>
-      <c r="E34" s="69" t="n"/>
-      <c r="F34" s="69" t="n"/>
-      <c r="G34" s="70" t="n"/>
-      <c r="H34" s="71" t="n"/>
+      <c r="C33" s="68" t="n"/>
+      <c r="D33" s="68" t="n"/>
+      <c r="E33" s="68" t="n"/>
+      <c r="F33" s="68" t="n"/>
+      <c r="G33" s="69" t="n"/>
+      <c r="H33" s="70" t="n"/>
+    </row>
+    <row r="34" ht="14" customHeight="1">
+      <c r="B34" s="67" t="n"/>
+      <c r="C34" s="68" t="n"/>
+      <c r="D34" s="68" t="n"/>
+      <c r="E34" s="68" t="n"/>
+      <c r="F34" s="68" t="n"/>
+      <c r="G34" s="69" t="n"/>
+      <c r="H34" s="70" t="n"/>
     </row>
     <row r="35" ht="14" customHeight="1">
-      <c r="B35" s="68" t="n"/>
-      <c r="C35" s="69" t="n"/>
-      <c r="D35" s="69" t="n"/>
-      <c r="E35" s="69" t="n"/>
-      <c r="F35" s="69" t="n"/>
-      <c r="G35" s="70" t="n"/>
-      <c r="H35" s="71" t="n"/>
-    </row>
-    <row r="36" ht="14" customHeight="1">
-      <c r="B36" s="29" t="inlineStr">
+      <c r="B35" s="29" t="inlineStr">
         <is>
           <t>Назначение платежа:</t>
         </is>
       </c>
-      <c r="C36" s="32" t="n"/>
-      <c r="D36" s="32" t="n"/>
-      <c r="E36" s="32" t="n"/>
-      <c r="F36" s="32" t="n"/>
-      <c r="G36" s="70" t="n"/>
-      <c r="H36" s="71" t="n"/>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="B37" s="68">
+      <c r="C35" s="32" t="n"/>
+      <c r="D35" s="32" t="n"/>
+      <c r="E35" s="32" t="n"/>
+      <c r="F35" s="32" t="n"/>
+      <c r="G35" s="69" t="n"/>
+      <c r="H35" s="70" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="B36" s="67">
         <f>"Взнос на капитальный ремонт, л/с № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;", кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;", за "&amp;"II квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="C37" s="69" t="n"/>
-      <c r="D37" s="69" t="n"/>
-      <c r="E37" s="69" t="n"/>
-      <c r="F37" s="69" t="n"/>
-      <c r="G37" s="70" t="n"/>
-      <c r="H37" s="71" t="n"/>
-    </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="B38" s="72">
+      <c r="C36" s="68" t="n"/>
+      <c r="D36" s="68" t="n"/>
+      <c r="E36" s="68" t="n"/>
+      <c r="F36" s="68" t="n"/>
+      <c r="G36" s="69" t="n"/>
+      <c r="H36" s="70" t="n"/>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="B37" s="71">
         <f>"Срок оплаты: до "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$49&amp;" числа месяца, следующего за расчётным (за "&amp;"II квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — до "&amp;TEXT(DAY(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,6+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49)),"00")&amp;"."&amp;TEXT(MONTH(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,6+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49)),"00")&amp;"."&amp;YEAR(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,6+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49))&amp;")."&amp;CHAR(10)&amp;"Основание: ч. 1 ст. 155, ч. 2 ст. 171 ЖК РФ."</f>
         <v/>
       </c>
-      <c r="C38" s="73" t="n"/>
-      <c r="D38" s="73" t="n"/>
-      <c r="E38" s="73" t="n"/>
-      <c r="F38" s="73" t="n"/>
-      <c r="G38" s="74" t="n"/>
-      <c r="H38" s="75" t="n"/>
-    </row>
-    <row r="39" ht="5" customHeight="1"/>
-    <row r="40" ht="32" customHeight="1">
+      <c r="C37" s="72" t="n"/>
+      <c r="D37" s="72" t="n"/>
+      <c r="E37" s="72" t="n"/>
+      <c r="F37" s="72" t="n"/>
+      <c r="G37" s="73" t="n"/>
+      <c r="H37" s="74" t="n"/>
+    </row>
+    <row r="38" ht="5" customHeight="1"/>
+    <row r="39" ht="32" customHeight="1">
+      <c r="B39" s="75">
+        <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
+        <v/>
+      </c>
+      <c r="C39" s="75" t="n"/>
+      <c r="D39" s="75" t="n"/>
+      <c r="E39" s="75" t="n"/>
+      <c r="F39" s="75" t="n"/>
+      <c r="G39" s="75" t="n"/>
+      <c r="H39" s="75" t="n"/>
+    </row>
+    <row r="40" ht="44" customHeight="1">
       <c r="B40" s="76">
-        <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
+        <f>"В отделении банка и в мобильном приложении во вкладках ищите "&amp;"«РФКР МКД_капремонт, оплата по расчётному счёту» и указывайте номер расчётного счёта, приведённый выше. Оплата через общий поиск «Капитальный ремонт» уходит на общий счёт Регионального фонда капитального ремонта и на счёт вашего дома не поступает."&amp;CHAR(10)&amp;"Лицевой счёт № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;" при оплате НЕ вводится — он указан справочно, только для учёта начислений."</f>
         <v/>
       </c>
       <c r="C40" s="76" t="n"/>
@@ -33433,84 +33399,72 @@
       <c r="G40" s="76" t="n"/>
       <c r="H40" s="76" t="n"/>
     </row>
-    <row r="41" ht="44" customHeight="1">
-      <c r="B41" s="77">
-        <f>"В отделении банка и в мобильном приложении во вкладках ищите "&amp;"«РФКР МКД_капремонт, оплата по расчётному счёту» и указывайте номер расчётного счёта, приведённый выше. Оплата через общий поиск «Капитальный ремонт» уходит на общий счёт Регионального фонда капитального ремонта и на счёт вашего дома не поступает."&amp;CHAR(10)&amp;"Лицевой счёт № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;" при оплате НЕ вводится — он указан справочно, только для учёта начислений."</f>
+    <row r="41" ht="6" customHeight="1"/>
+    <row r="42" ht="24" customHeight="1">
+      <c r="B42" s="77" t="inlineStr">
+        <is>
+          <t>Подпись плательщика  ______________________</t>
+        </is>
+      </c>
+      <c r="C42" s="77" t="n"/>
+      <c r="D42" s="77" t="n"/>
+      <c r="E42" s="77" t="inlineStr">
+        <is>
+          <t>Кассир  ______________</t>
+        </is>
+      </c>
+      <c r="F42" s="77" t="n"/>
+      <c r="G42" s="77" t="inlineStr">
+        <is>
+          <t>Дата  ____________</t>
+        </is>
+      </c>
+      <c r="H42" s="77" t="n"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="B43" s="78">
+        <f>"Начисление за "&amp;"II квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;"    По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
-      </c>
-      <c r="C41" s="77" t="n"/>
-      <c r="D41" s="77" t="n"/>
-      <c r="E41" s="77" t="n"/>
-      <c r="F41" s="77" t="n"/>
-      <c r="G41" s="77" t="n"/>
-      <c r="H41" s="77" t="n"/>
-    </row>
-    <row r="42" ht="6" customHeight="1"/>
-    <row r="43" ht="24" customHeight="1">
-      <c r="B43" s="78" t="inlineStr">
-        <is>
-          <t>Подпись плательщика  ______________________</t>
-        </is>
       </c>
       <c r="C43" s="78" t="n"/>
       <c r="D43" s="78" t="n"/>
-      <c r="E43" s="78" t="inlineStr">
-        <is>
-          <t>Кассир  ______________</t>
-        </is>
-      </c>
+      <c r="E43" s="78" t="n"/>
       <c r="F43" s="78" t="n"/>
-      <c r="G43" s="78" t="inlineStr">
-        <is>
-          <t>Дата  ____________</t>
-        </is>
-      </c>
+      <c r="G43" s="78" t="n"/>
       <c r="H43" s="78" t="n"/>
     </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="B44" s="79">
-        <f>"Начисление за "&amp;"II квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;"    По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
-        <v/>
-      </c>
-      <c r="C44" s="79" t="n"/>
-      <c r="D44" s="79" t="n"/>
-      <c r="E44" s="79" t="n"/>
-      <c r="F44" s="79" t="n"/>
-      <c r="G44" s="79" t="n"/>
-      <c r="H44" s="79" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="E43:F43"/>
+  <mergeCells count="48">
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
-    <mergeCell ref="G43:H43"/>
     <mergeCell ref="B40:H40"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="F25:G25"/>
+    <mergeCell ref="G42:H42"/>
     <mergeCell ref="F8:H8"/>
+    <mergeCell ref="E42:F42"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B32:H32"/>
     <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B41:H41"/>
-    <mergeCell ref="G33:H38"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B31:H31"/>
     <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="G30:H30"/>
     <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G32:H37"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B39:H39"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="F22:G22"/>
@@ -33519,14 +33473,12 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C15:H15"/>
     <mergeCell ref="G29:H29"/>
-    <mergeCell ref="B30:F30"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B44:H44"/>
     <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B28:H28"/>
@@ -33544,7 +33496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H44"/>
+  <dimension ref="B2:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.8" customWidth="1" min="1" max="1"/>
@@ -33996,65 +33948,49 @@
       <c r="H28" s="25" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="53">
+      <c r="B29" s="64">
         <f>"Поступило оплат по лицевому счёту с начала "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года, руб."</f>
         <v/>
       </c>
-      <c r="C29" s="30" t="n"/>
-      <c r="D29" s="30" t="n"/>
-      <c r="E29" s="30" t="n"/>
-      <c r="F29" s="30" t="n"/>
-      <c r="G29" s="64">
+      <c r="C29" s="36" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="36" t="n"/>
+      <c r="F29" s="36" t="n"/>
+      <c r="G29" s="65">
         <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$F$32="","—",'ИСХОДНЫЕ ДАННЫЕ'!$F$32)</f>
         <v/>
       </c>
-      <c r="H29" s="55" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="B30" s="65" t="inlineStr">
-        <is>
-          <t>Остаток средств на специальном счёте многоквартирного дома, руб.</t>
-        </is>
-      </c>
-      <c r="C30" s="36" t="n"/>
-      <c r="D30" s="36" t="n"/>
-      <c r="E30" s="36" t="n"/>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="66">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$G$32="","—",'ИСХОДНЫЕ ДАННЫЕ'!$G$32)</f>
-        <v/>
-      </c>
-      <c r="H30" s="67" t="n"/>
-    </row>
-    <row r="31" ht="5" customHeight="1"/>
-    <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="23" t="inlineStr">
+      <c r="H29" s="66" t="n"/>
+    </row>
+    <row r="30" ht="5" customHeight="1"/>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>5. ПОРЯДОК ОПЛАТЫ</t>
         </is>
       </c>
-      <c r="C32" s="24" t="n"/>
-      <c r="D32" s="24" t="n"/>
-      <c r="E32" s="24" t="n"/>
-      <c r="F32" s="24" t="n"/>
-      <c r="G32" s="24" t="n"/>
-      <c r="H32" s="25" t="n"/>
-    </row>
-    <row r="33" ht="14" customHeight="1">
-      <c r="B33" s="68" t="inlineStr">
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="24" t="n"/>
+      <c r="E31" s="24" t="n"/>
+      <c r="F31" s="24" t="n"/>
+      <c r="G31" s="24" t="n"/>
+      <c r="H31" s="25" t="n"/>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="B32" s="67" t="inlineStr">
         <is>
           <t>1) без комиссии — в отделениях АО «Россельхозбанк» (банк, в котором открыт специальный счёт дома);</t>
         </is>
       </c>
-      <c r="C33" s="69" t="n"/>
-      <c r="D33" s="69" t="n"/>
-      <c r="E33" s="69" t="n"/>
-      <c r="F33" s="69" t="n"/>
-      <c r="G33" s="70" t="n"/>
-      <c r="H33" s="71" t="n"/>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="B34" s="68" t="inlineStr">
+      <c r="C32" s="68" t="n"/>
+      <c r="D32" s="68" t="n"/>
+      <c r="E32" s="68" t="n"/>
+      <c r="F32" s="68" t="n"/>
+      <c r="G32" s="69" t="n"/>
+      <c r="H32" s="70" t="n"/>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="B33" s="67" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34083,63 +34019,75 @@
           </r>
         </is>
       </c>
-      <c r="C34" s="69" t="n"/>
-      <c r="D34" s="69" t="n"/>
-      <c r="E34" s="69" t="n"/>
-      <c r="F34" s="69" t="n"/>
-      <c r="G34" s="70" t="n"/>
-      <c r="H34" s="71" t="n"/>
+      <c r="C33" s="68" t="n"/>
+      <c r="D33" s="68" t="n"/>
+      <c r="E33" s="68" t="n"/>
+      <c r="F33" s="68" t="n"/>
+      <c r="G33" s="69" t="n"/>
+      <c r="H33" s="70" t="n"/>
+    </row>
+    <row r="34" ht="14" customHeight="1">
+      <c r="B34" s="67" t="n"/>
+      <c r="C34" s="68" t="n"/>
+      <c r="D34" s="68" t="n"/>
+      <c r="E34" s="68" t="n"/>
+      <c r="F34" s="68" t="n"/>
+      <c r="G34" s="69" t="n"/>
+      <c r="H34" s="70" t="n"/>
     </row>
     <row r="35" ht="14" customHeight="1">
-      <c r="B35" s="68" t="n"/>
-      <c r="C35" s="69" t="n"/>
-      <c r="D35" s="69" t="n"/>
-      <c r="E35" s="69" t="n"/>
-      <c r="F35" s="69" t="n"/>
-      <c r="G35" s="70" t="n"/>
-      <c r="H35" s="71" t="n"/>
-    </row>
-    <row r="36" ht="14" customHeight="1">
-      <c r="B36" s="29" t="inlineStr">
+      <c r="B35" s="29" t="inlineStr">
         <is>
           <t>Назначение платежа:</t>
         </is>
       </c>
-      <c r="C36" s="32" t="n"/>
-      <c r="D36" s="32" t="n"/>
-      <c r="E36" s="32" t="n"/>
-      <c r="F36" s="32" t="n"/>
-      <c r="G36" s="70" t="n"/>
-      <c r="H36" s="71" t="n"/>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="B37" s="68">
+      <c r="C35" s="32" t="n"/>
+      <c r="D35" s="32" t="n"/>
+      <c r="E35" s="32" t="n"/>
+      <c r="F35" s="32" t="n"/>
+      <c r="G35" s="69" t="n"/>
+      <c r="H35" s="70" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="B36" s="67">
         <f>"Взнос на капитальный ремонт, л/с № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;", кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;", за "&amp;"III квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="C37" s="69" t="n"/>
-      <c r="D37" s="69" t="n"/>
-      <c r="E37" s="69" t="n"/>
-      <c r="F37" s="69" t="n"/>
-      <c r="G37" s="70" t="n"/>
-      <c r="H37" s="71" t="n"/>
-    </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="B38" s="72">
+      <c r="C36" s="68" t="n"/>
+      <c r="D36" s="68" t="n"/>
+      <c r="E36" s="68" t="n"/>
+      <c r="F36" s="68" t="n"/>
+      <c r="G36" s="69" t="n"/>
+      <c r="H36" s="70" t="n"/>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="B37" s="71">
         <f>"Срок оплаты: до "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$49&amp;" числа месяца, следующего за расчётным (за "&amp;"III квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — до "&amp;TEXT(DAY(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,9+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49)),"00")&amp;"."&amp;TEXT(MONTH(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,9+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49)),"00")&amp;"."&amp;YEAR(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,9+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49))&amp;")."&amp;CHAR(10)&amp;"Основание: ч. 1 ст. 155, ч. 2 ст. 171 ЖК РФ."</f>
         <v/>
       </c>
-      <c r="C38" s="73" t="n"/>
-      <c r="D38" s="73" t="n"/>
-      <c r="E38" s="73" t="n"/>
-      <c r="F38" s="73" t="n"/>
-      <c r="G38" s="74" t="n"/>
-      <c r="H38" s="75" t="n"/>
-    </row>
-    <row r="39" ht="5" customHeight="1"/>
-    <row r="40" ht="32" customHeight="1">
+      <c r="C37" s="72" t="n"/>
+      <c r="D37" s="72" t="n"/>
+      <c r="E37" s="72" t="n"/>
+      <c r="F37" s="72" t="n"/>
+      <c r="G37" s="73" t="n"/>
+      <c r="H37" s="74" t="n"/>
+    </row>
+    <row r="38" ht="5" customHeight="1"/>
+    <row r="39" ht="32" customHeight="1">
+      <c r="B39" s="75">
+        <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
+        <v/>
+      </c>
+      <c r="C39" s="75" t="n"/>
+      <c r="D39" s="75" t="n"/>
+      <c r="E39" s="75" t="n"/>
+      <c r="F39" s="75" t="n"/>
+      <c r="G39" s="75" t="n"/>
+      <c r="H39" s="75" t="n"/>
+    </row>
+    <row r="40" ht="44" customHeight="1">
       <c r="B40" s="76">
-        <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
+        <f>"В отделении банка и в мобильном приложении во вкладках ищите "&amp;"«РФКР МКД_капремонт, оплата по расчётному счёту» и указывайте номер расчётного счёта, приведённый выше. Оплата через общий поиск «Капитальный ремонт» уходит на общий счёт Регионального фонда капитального ремонта и на счёт вашего дома не поступает."&amp;CHAR(10)&amp;"Лицевой счёт № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;" при оплате НЕ вводится — он указан справочно, только для учёта начислений."</f>
         <v/>
       </c>
       <c r="C40" s="76" t="n"/>
@@ -34149,84 +34097,72 @@
       <c r="G40" s="76" t="n"/>
       <c r="H40" s="76" t="n"/>
     </row>
-    <row r="41" ht="44" customHeight="1">
-      <c r="B41" s="77">
-        <f>"В отделении банка и в мобильном приложении во вкладках ищите "&amp;"«РФКР МКД_капремонт, оплата по расчётному счёту» и указывайте номер расчётного счёта, приведённый выше. Оплата через общий поиск «Капитальный ремонт» уходит на общий счёт Регионального фонда капитального ремонта и на счёт вашего дома не поступает."&amp;CHAR(10)&amp;"Лицевой счёт № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;" при оплате НЕ вводится — он указан справочно, только для учёта начислений."</f>
+    <row r="41" ht="6" customHeight="1"/>
+    <row r="42" ht="24" customHeight="1">
+      <c r="B42" s="77" t="inlineStr">
+        <is>
+          <t>Подпись плательщика  ______________________</t>
+        </is>
+      </c>
+      <c r="C42" s="77" t="n"/>
+      <c r="D42" s="77" t="n"/>
+      <c r="E42" s="77" t="inlineStr">
+        <is>
+          <t>Кассир  ______________</t>
+        </is>
+      </c>
+      <c r="F42" s="77" t="n"/>
+      <c r="G42" s="77" t="inlineStr">
+        <is>
+          <t>Дата  ____________</t>
+        </is>
+      </c>
+      <c r="H42" s="77" t="n"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="B43" s="78">
+        <f>"Начисление за "&amp;"III квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;"    По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
-      </c>
-      <c r="C41" s="77" t="n"/>
-      <c r="D41" s="77" t="n"/>
-      <c r="E41" s="77" t="n"/>
-      <c r="F41" s="77" t="n"/>
-      <c r="G41" s="77" t="n"/>
-      <c r="H41" s="77" t="n"/>
-    </row>
-    <row r="42" ht="6" customHeight="1"/>
-    <row r="43" ht="24" customHeight="1">
-      <c r="B43" s="78" t="inlineStr">
-        <is>
-          <t>Подпись плательщика  ______________________</t>
-        </is>
       </c>
       <c r="C43" s="78" t="n"/>
       <c r="D43" s="78" t="n"/>
-      <c r="E43" s="78" t="inlineStr">
-        <is>
-          <t>Кассир  ______________</t>
-        </is>
-      </c>
+      <c r="E43" s="78" t="n"/>
       <c r="F43" s="78" t="n"/>
-      <c r="G43" s="78" t="inlineStr">
-        <is>
-          <t>Дата  ____________</t>
-        </is>
-      </c>
+      <c r="G43" s="78" t="n"/>
       <c r="H43" s="78" t="n"/>
     </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="B44" s="79">
-        <f>"Начисление за "&amp;"III квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;"    По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
-        <v/>
-      </c>
-      <c r="C44" s="79" t="n"/>
-      <c r="D44" s="79" t="n"/>
-      <c r="E44" s="79" t="n"/>
-      <c r="F44" s="79" t="n"/>
-      <c r="G44" s="79" t="n"/>
-      <c r="H44" s="79" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="E43:F43"/>
+  <mergeCells count="48">
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
-    <mergeCell ref="G43:H43"/>
     <mergeCell ref="B40:H40"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="F25:G25"/>
+    <mergeCell ref="G42:H42"/>
     <mergeCell ref="F8:H8"/>
+    <mergeCell ref="E42:F42"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B32:H32"/>
     <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B41:H41"/>
-    <mergeCell ref="G33:H38"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B31:H31"/>
     <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="G30:H30"/>
     <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G32:H37"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B39:H39"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="F22:G22"/>
@@ -34235,14 +34171,12 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C15:H15"/>
     <mergeCell ref="G29:H29"/>
-    <mergeCell ref="B30:F30"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B44:H44"/>
     <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B28:H28"/>
@@ -34260,7 +34194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H44"/>
+  <dimension ref="B2:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="1.8" customWidth="1" min="1" max="1"/>
@@ -34712,65 +34646,49 @@
       <c r="H28" s="25" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="53">
+      <c r="B29" s="64">
         <f>"Поступило оплат по лицевому счёту с начала "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года, руб."</f>
         <v/>
       </c>
-      <c r="C29" s="30" t="n"/>
-      <c r="D29" s="30" t="n"/>
-      <c r="E29" s="30" t="n"/>
-      <c r="F29" s="30" t="n"/>
-      <c r="G29" s="64">
+      <c r="C29" s="36" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="36" t="n"/>
+      <c r="F29" s="36" t="n"/>
+      <c r="G29" s="65">
         <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$F$33="","—",'ИСХОДНЫЕ ДАННЫЕ'!$F$33)</f>
         <v/>
       </c>
-      <c r="H29" s="55" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="B30" s="65" t="inlineStr">
-        <is>
-          <t>Остаток средств на специальном счёте многоквартирного дома, руб.</t>
-        </is>
-      </c>
-      <c r="C30" s="36" t="n"/>
-      <c r="D30" s="36" t="n"/>
-      <c r="E30" s="36" t="n"/>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="66">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$G$33="","—",'ИСХОДНЫЕ ДАННЫЕ'!$G$33)</f>
-        <v/>
-      </c>
-      <c r="H30" s="67" t="n"/>
-    </row>
-    <row r="31" ht="5" customHeight="1"/>
-    <row r="32" ht="16" customHeight="1">
-      <c r="B32" s="23" t="inlineStr">
+      <c r="H29" s="66" t="n"/>
+    </row>
+    <row r="30" ht="5" customHeight="1"/>
+    <row r="31" ht="16" customHeight="1">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>5. ПОРЯДОК ОПЛАТЫ</t>
         </is>
       </c>
-      <c r="C32" s="24" t="n"/>
-      <c r="D32" s="24" t="n"/>
-      <c r="E32" s="24" t="n"/>
-      <c r="F32" s="24" t="n"/>
-      <c r="G32" s="24" t="n"/>
-      <c r="H32" s="25" t="n"/>
-    </row>
-    <row r="33" ht="14" customHeight="1">
-      <c r="B33" s="68" t="inlineStr">
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="24" t="n"/>
+      <c r="E31" s="24" t="n"/>
+      <c r="F31" s="24" t="n"/>
+      <c r="G31" s="24" t="n"/>
+      <c r="H31" s="25" t="n"/>
+    </row>
+    <row r="32" ht="14" customHeight="1">
+      <c r="B32" s="67" t="inlineStr">
         <is>
           <t>1) без комиссии — в отделениях АО «Россельхозбанк» (банк, в котором открыт специальный счёт дома);</t>
         </is>
       </c>
-      <c r="C33" s="69" t="n"/>
-      <c r="D33" s="69" t="n"/>
-      <c r="E33" s="69" t="n"/>
-      <c r="F33" s="69" t="n"/>
-      <c r="G33" s="70" t="n"/>
-      <c r="H33" s="71" t="n"/>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="B34" s="68" t="inlineStr">
+      <c r="C32" s="68" t="n"/>
+      <c r="D32" s="68" t="n"/>
+      <c r="E32" s="68" t="n"/>
+      <c r="F32" s="68" t="n"/>
+      <c r="G32" s="69" t="n"/>
+      <c r="H32" s="70" t="n"/>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="B33" s="67" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34799,63 +34717,75 @@
           </r>
         </is>
       </c>
-      <c r="C34" s="69" t="n"/>
-      <c r="D34" s="69" t="n"/>
-      <c r="E34" s="69" t="n"/>
-      <c r="F34" s="69" t="n"/>
-      <c r="G34" s="70" t="n"/>
-      <c r="H34" s="71" t="n"/>
+      <c r="C33" s="68" t="n"/>
+      <c r="D33" s="68" t="n"/>
+      <c r="E33" s="68" t="n"/>
+      <c r="F33" s="68" t="n"/>
+      <c r="G33" s="69" t="n"/>
+      <c r="H33" s="70" t="n"/>
+    </row>
+    <row r="34" ht="14" customHeight="1">
+      <c r="B34" s="67" t="n"/>
+      <c r="C34" s="68" t="n"/>
+      <c r="D34" s="68" t="n"/>
+      <c r="E34" s="68" t="n"/>
+      <c r="F34" s="68" t="n"/>
+      <c r="G34" s="69" t="n"/>
+      <c r="H34" s="70" t="n"/>
     </row>
     <row r="35" ht="14" customHeight="1">
-      <c r="B35" s="68" t="n"/>
-      <c r="C35" s="69" t="n"/>
-      <c r="D35" s="69" t="n"/>
-      <c r="E35" s="69" t="n"/>
-      <c r="F35" s="69" t="n"/>
-      <c r="G35" s="70" t="n"/>
-      <c r="H35" s="71" t="n"/>
-    </row>
-    <row r="36" ht="14" customHeight="1">
-      <c r="B36" s="29" t="inlineStr">
+      <c r="B35" s="29" t="inlineStr">
         <is>
           <t>Назначение платежа:</t>
         </is>
       </c>
-      <c r="C36" s="32" t="n"/>
-      <c r="D36" s="32" t="n"/>
-      <c r="E36" s="32" t="n"/>
-      <c r="F36" s="32" t="n"/>
-      <c r="G36" s="70" t="n"/>
-      <c r="H36" s="71" t="n"/>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="B37" s="68">
+      <c r="C35" s="32" t="n"/>
+      <c r="D35" s="32" t="n"/>
+      <c r="E35" s="32" t="n"/>
+      <c r="F35" s="32" t="n"/>
+      <c r="G35" s="69" t="n"/>
+      <c r="H35" s="70" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="B36" s="67">
         <f>"Взнос на капитальный ремонт, л/с № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;", кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;", за "&amp;"IV квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="C37" s="69" t="n"/>
-      <c r="D37" s="69" t="n"/>
-      <c r="E37" s="69" t="n"/>
-      <c r="F37" s="69" t="n"/>
-      <c r="G37" s="70" t="n"/>
-      <c r="H37" s="71" t="n"/>
-    </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="B38" s="72">
+      <c r="C36" s="68" t="n"/>
+      <c r="D36" s="68" t="n"/>
+      <c r="E36" s="68" t="n"/>
+      <c r="F36" s="68" t="n"/>
+      <c r="G36" s="69" t="n"/>
+      <c r="H36" s="70" t="n"/>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="B37" s="71">
         <f>"Срок оплаты: до "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$49&amp;" числа месяца, следующего за расчётным (за "&amp;"IV квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — до "&amp;TEXT(DAY(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,12+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49)),"00")&amp;"."&amp;TEXT(MONTH(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,12+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49)),"00")&amp;"."&amp;YEAR(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,12+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49))&amp;")."&amp;CHAR(10)&amp;"Основание: ч. 1 ст. 155, ч. 2 ст. 171 ЖК РФ."</f>
         <v/>
       </c>
-      <c r="C38" s="73" t="n"/>
-      <c r="D38" s="73" t="n"/>
-      <c r="E38" s="73" t="n"/>
-      <c r="F38" s="73" t="n"/>
-      <c r="G38" s="74" t="n"/>
-      <c r="H38" s="75" t="n"/>
-    </row>
-    <row r="39" ht="5" customHeight="1"/>
-    <row r="40" ht="32" customHeight="1">
+      <c r="C37" s="72" t="n"/>
+      <c r="D37" s="72" t="n"/>
+      <c r="E37" s="72" t="n"/>
+      <c r="F37" s="72" t="n"/>
+      <c r="G37" s="73" t="n"/>
+      <c r="H37" s="74" t="n"/>
+    </row>
+    <row r="38" ht="5" customHeight="1"/>
+    <row r="39" ht="32" customHeight="1">
+      <c r="B39" s="75">
+        <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
+        <v/>
+      </c>
+      <c r="C39" s="75" t="n"/>
+      <c r="D39" s="75" t="n"/>
+      <c r="E39" s="75" t="n"/>
+      <c r="F39" s="75" t="n"/>
+      <c r="G39" s="75" t="n"/>
+      <c r="H39" s="75" t="n"/>
+    </row>
+    <row r="40" ht="44" customHeight="1">
       <c r="B40" s="76">
-        <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
+        <f>"В отделении банка и в мобильном приложении во вкладках ищите "&amp;"«РФКР МКД_капремонт, оплата по расчётному счёту» и указывайте номер расчётного счёта, приведённый выше. Оплата через общий поиск «Капитальный ремонт» уходит на общий счёт Регионального фонда капитального ремонта и на счёт вашего дома не поступает."&amp;CHAR(10)&amp;"Лицевой счёт № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;" при оплате НЕ вводится — он указан справочно, только для учёта начислений."</f>
         <v/>
       </c>
       <c r="C40" s="76" t="n"/>
@@ -34865,84 +34795,72 @@
       <c r="G40" s="76" t="n"/>
       <c r="H40" s="76" t="n"/>
     </row>
-    <row r="41" ht="44" customHeight="1">
-      <c r="B41" s="77">
-        <f>"В отделении банка и в мобильном приложении во вкладках ищите "&amp;"«РФКР МКД_капремонт, оплата по расчётному счёту» и указывайте номер расчётного счёта, приведённый выше. Оплата через общий поиск «Капитальный ремонт» уходит на общий счёт Регионального фонда капитального ремонта и на счёт вашего дома не поступает."&amp;CHAR(10)&amp;"Лицевой счёт № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;" при оплате НЕ вводится — он указан справочно, только для учёта начислений."</f>
+    <row r="41" ht="6" customHeight="1"/>
+    <row r="42" ht="24" customHeight="1">
+      <c r="B42" s="77" t="inlineStr">
+        <is>
+          <t>Подпись плательщика  ______________________</t>
+        </is>
+      </c>
+      <c r="C42" s="77" t="n"/>
+      <c r="D42" s="77" t="n"/>
+      <c r="E42" s="77" t="inlineStr">
+        <is>
+          <t>Кассир  ______________</t>
+        </is>
+      </c>
+      <c r="F42" s="77" t="n"/>
+      <c r="G42" s="77" t="inlineStr">
+        <is>
+          <t>Дата  ____________</t>
+        </is>
+      </c>
+      <c r="H42" s="77" t="n"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="B43" s="78">
+        <f>"Начисление за "&amp;"IV квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;"    По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
-      </c>
-      <c r="C41" s="77" t="n"/>
-      <c r="D41" s="77" t="n"/>
-      <c r="E41" s="77" t="n"/>
-      <c r="F41" s="77" t="n"/>
-      <c r="G41" s="77" t="n"/>
-      <c r="H41" s="77" t="n"/>
-    </row>
-    <row r="42" ht="6" customHeight="1"/>
-    <row r="43" ht="24" customHeight="1">
-      <c r="B43" s="78" t="inlineStr">
-        <is>
-          <t>Подпись плательщика  ______________________</t>
-        </is>
       </c>
       <c r="C43" s="78" t="n"/>
       <c r="D43" s="78" t="n"/>
-      <c r="E43" s="78" t="inlineStr">
-        <is>
-          <t>Кассир  ______________</t>
-        </is>
-      </c>
+      <c r="E43" s="78" t="n"/>
       <c r="F43" s="78" t="n"/>
-      <c r="G43" s="78" t="inlineStr">
-        <is>
-          <t>Дата  ____________</t>
-        </is>
-      </c>
+      <c r="G43" s="78" t="n"/>
       <c r="H43" s="78" t="n"/>
     </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="B44" s="79">
-        <f>"Начисление за "&amp;"IV квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;"    По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
-        <v/>
-      </c>
-      <c r="C44" s="79" t="n"/>
-      <c r="D44" s="79" t="n"/>
-      <c r="E44" s="79" t="n"/>
-      <c r="F44" s="79" t="n"/>
-      <c r="G44" s="79" t="n"/>
-      <c r="H44" s="79" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="E43:F43"/>
+  <mergeCells count="48">
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="C16:H16"/>
-    <mergeCell ref="G43:H43"/>
     <mergeCell ref="B40:H40"/>
     <mergeCell ref="C9:H9"/>
     <mergeCell ref="F25:G25"/>
+    <mergeCell ref="G42:H42"/>
     <mergeCell ref="F8:H8"/>
+    <mergeCell ref="E42:F42"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="G17:H17"/>
     <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B32:H32"/>
     <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B41:H41"/>
-    <mergeCell ref="G33:H38"/>
     <mergeCell ref="F20:G20"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B31:H31"/>
     <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="G30:H30"/>
     <mergeCell ref="B34:F34"/>
+    <mergeCell ref="G32:H37"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="B43:H43"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B39:H39"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="F22:G22"/>
@@ -34951,14 +34869,12 @@
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="C15:H15"/>
     <mergeCell ref="G29:H29"/>
-    <mergeCell ref="B30:F30"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B44:H44"/>
     <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B28:H28"/>
@@ -34989,189 +34905,189 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="D1" s="80">
+      <c r="D1" s="79">
         <f>"В "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$24</f>
         <v/>
       </c>
-      <c r="E1" s="80" t="n"/>
-      <c r="F1" s="80" t="n"/>
+      <c r="E1" s="79" t="n"/>
+      <c r="F1" s="79" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="D2" s="80">
+      <c r="D2" s="79">
         <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$26="","",'ИСХОДНЫЕ ДАННЫЕ'!$C$25&amp;" "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$26)</f>
         <v/>
       </c>
-      <c r="E2" s="80" t="n"/>
-      <c r="F2" s="80" t="n"/>
+      <c r="E2" s="79" t="n"/>
+      <c r="F2" s="79" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="D3" s="81">
+      <c r="D3" s="80">
         <f>"от Председателя МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;", "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$18</f>
         <v/>
       </c>
-      <c r="E3" s="81" t="n"/>
-      <c r="F3" s="81" t="n"/>
+      <c r="E3" s="80" t="n"/>
+      <c r="F3" s="80" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="D4" s="81">
+      <c r="D4" s="80">
         <f>"проживающей по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$20</f>
         <v/>
       </c>
-      <c r="E4" s="81" t="n"/>
-      <c r="F4" s="81" t="n"/>
+      <c r="E4" s="80" t="n"/>
+      <c r="F4" s="80" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="D5" s="81">
+      <c r="D5" s="80">
         <f>"Конт. тел.: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21</f>
         <v/>
       </c>
-      <c r="E5" s="81" t="n"/>
-      <c r="F5" s="81" t="n"/>
+      <c r="E5" s="80" t="n"/>
+      <c r="F5" s="80" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="D6" s="81">
+      <c r="D6" s="80">
         <f>"Эл. почта: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22</f>
         <v/>
       </c>
-      <c r="E6" s="81" t="n"/>
-      <c r="F6" s="81" t="n"/>
+      <c r="E6" s="80" t="n"/>
+      <c r="F6" s="80" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1"/>
     <row r="8" ht="46" customHeight="1">
-      <c r="B8" s="81">
+      <c r="B8" s="80">
         <f>"В связи с тем, что на балансе департамента числится кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", сообщаю Вам о необходимости оплатить "&amp;IF(INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2)*100,0)-INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))*100),"00")&amp;" руб., в том числе:"</f>
         <v/>
       </c>
-      <c r="C8" s="81" t="n"/>
-      <c r="D8" s="81" t="n"/>
-      <c r="E8" s="81" t="n"/>
-      <c r="F8" s="81" t="n"/>
+      <c r="C8" s="80" t="n"/>
+      <c r="D8" s="80" t="n"/>
+      <c r="E8" s="80" t="n"/>
+      <c r="F8" s="80" t="n"/>
     </row>
     <row r="9" ht="8" customHeight="1"/>
     <row r="10" ht="32" customHeight="1">
-      <c r="B10" s="81">
+      <c r="B10" s="80">
         <f>"— текущий платёж за период с января по март "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года ("&amp;"I квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;") в размере "&amp;IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100),"00")&amp;" рублей"</f>
         <v/>
       </c>
-      <c r="C10" s="81" t="n"/>
-      <c r="D10" s="81" t="n"/>
-      <c r="E10" s="81" t="n"/>
-      <c r="F10" s="81" t="n"/>
+      <c r="C10" s="80" t="n"/>
+      <c r="D10" s="80" t="n"/>
+      <c r="E10" s="80" t="n"/>
+      <c r="F10" s="80" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="82">
+      <c r="B11" s="81">
         <f>"("&amp;UPPER(LEFT(IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)=0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)=0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1),2,300)&amp;")."</f>
         <v/>
       </c>
-      <c r="C11" s="82" t="n"/>
-      <c r="D11" s="82" t="n"/>
-      <c r="E11" s="82" t="n"/>
-      <c r="F11" s="82" t="n"/>
+      <c r="C11" s="81" t="n"/>
+      <c r="D11" s="81" t="n"/>
+      <c r="E11" s="81" t="n"/>
+      <c r="F11" s="81" t="n"/>
     </row>
     <row r="12" ht="6" customHeight="1"/>
     <row r="13" ht="32" customHeight="1">
-      <c r="B13" s="81">
+      <c r="B13" s="80">
         <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$30=0,"— задолженности за предыдущие периоды нет.","— задолженность "&amp;IF('ИСХОДНЫЕ ДАННЫЕ'!$D$30="","за предыдущие периоды",'ИСХОДНЫЕ ДАННЫЕ'!$D$30)&amp;" в размере "&amp;IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)&gt;0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)&amp;" "&amp;TEXT((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)*1000),"000"),(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))*100),"00")&amp;" рублей")</f>
         <v/>
       </c>
-      <c r="C13" s="81" t="n"/>
-      <c r="D13" s="81" t="n"/>
-      <c r="E13" s="81" t="n"/>
-      <c r="F13" s="81" t="n"/>
+      <c r="C13" s="80" t="n"/>
+      <c r="D13" s="80" t="n"/>
+      <c r="E13" s="80" t="n"/>
+      <c r="F13" s="80" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="82">
+      <c r="B14" s="81">
         <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$30=0,"","("&amp;UPPER(LEFT(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))*100)+1),2,300)&amp;").")</f>
         <v/>
       </c>
-      <c r="C14" s="82" t="n"/>
-      <c r="D14" s="82" t="n"/>
-      <c r="E14" s="82" t="n"/>
-      <c r="F14" s="82" t="n"/>
+      <c r="C14" s="81" t="n"/>
+      <c r="D14" s="81" t="n"/>
+      <c r="E14" s="81" t="n"/>
+      <c r="F14" s="81" t="n"/>
     </row>
     <row r="15" ht="10" customHeight="1"/>
     <row r="16" ht="76" customHeight="1">
-      <c r="B16" s="81">
+      <c r="B16" s="80">
         <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$30),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$30),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$30)&amp;" и с учётом начислений по "&amp;"март "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
       </c>
-      <c r="C16" s="81" t="n"/>
-      <c r="D16" s="81" t="n"/>
-      <c r="E16" s="81" t="n"/>
-      <c r="F16" s="81" t="n"/>
+      <c r="C16" s="80" t="n"/>
+      <c r="D16" s="80" t="n"/>
+      <c r="E16" s="80" t="n"/>
+      <c r="F16" s="80" t="n"/>
     </row>
     <row r="17" ht="10" customHeight="1"/>
     <row r="18" ht="46" customHeight="1">
-      <c r="B18" s="81">
+      <c r="B18" s="80">
         <f>"В случае возникновения дополнительных вопросов прошу связаться со мной по электронной почте "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22&amp;" или по телефону "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
       </c>
-      <c r="C18" s="81" t="n"/>
-      <c r="D18" s="81" t="n"/>
-      <c r="E18" s="81" t="n"/>
-      <c r="F18" s="81" t="n"/>
+      <c r="C18" s="80" t="n"/>
+      <c r="D18" s="80" t="n"/>
+      <c r="E18" s="80" t="n"/>
+      <c r="F18" s="80" t="n"/>
     </row>
     <row r="19" ht="14" customHeight="1"/>
     <row r="20" ht="20" customHeight="1">
-      <c r="B20" s="80" t="inlineStr">
+      <c r="B20" s="79" t="inlineStr">
         <is>
           <t>ПРИЛОЖЕНИЯ:</t>
         </is>
       </c>
-      <c r="C20" s="80" t="n"/>
-      <c r="D20" s="80" t="n"/>
-      <c r="E20" s="80" t="n"/>
-      <c r="F20" s="80" t="n"/>
+      <c r="C20" s="79" t="n"/>
+      <c r="D20" s="79" t="n"/>
+      <c r="E20" s="79" t="n"/>
+      <c r="F20" s="79" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="81">
+      <c r="B21" s="80">
         <f>"1) Акт взаимных расчётов по состоянию на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$30),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$30),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$30)&amp;" — один экземпляр на 1 л."</f>
         <v/>
       </c>
-      <c r="C21" s="81" t="n"/>
-      <c r="D21" s="81" t="n"/>
-      <c r="E21" s="81" t="n"/>
-      <c r="F21" s="81" t="n"/>
+      <c r="C21" s="80" t="n"/>
+      <c r="D21" s="80" t="n"/>
+      <c r="E21" s="80" t="n"/>
+      <c r="F21" s="80" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="81">
+      <c r="B22" s="80">
         <f>"2) Квитанция для оплаты за "&amp;"I квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — один экземпляр на 1 л."</f>
         <v/>
       </c>
-      <c r="C22" s="81" t="n"/>
-      <c r="D22" s="81" t="n"/>
-      <c r="E22" s="81" t="n"/>
-      <c r="F22" s="81" t="n"/>
+      <c r="C22" s="80" t="n"/>
+      <c r="D22" s="80" t="n"/>
+      <c r="E22" s="80" t="n"/>
+      <c r="F22" s="80" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1"/>
     <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="81">
+      <c r="B24" s="80">
         <f>"«______» ______________ "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="C24" s="81" t="n"/>
+      <c r="C24" s="80" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1"/>
     <row r="26" ht="16" customHeight="1">
-      <c r="B26" s="81" t="inlineStr">
+      <c r="B26" s="80" t="inlineStr">
         <is>
           <t>Председатель</t>
         </is>
       </c>
-      <c r="C26" s="81" t="n"/>
+      <c r="C26" s="80" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="B27" s="81">
+      <c r="B27" s="80">
         <f>"МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15</f>
         <v/>
       </c>
-      <c r="C27" s="81" t="n"/>
-      <c r="D27" s="83">
+      <c r="C27" s="80" t="n"/>
+      <c r="D27" s="82">
         <f>"___________________  /"&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$19&amp;"/"</f>
         <v/>
       </c>
-      <c r="E27" s="83" t="n"/>
-      <c r="F27" s="83" t="n"/>
+      <c r="E27" s="82" t="n"/>
+      <c r="F27" s="82" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -35220,189 +35136,189 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="D1" s="80">
+      <c r="D1" s="79">
         <f>"В "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$24</f>
         <v/>
       </c>
-      <c r="E1" s="80" t="n"/>
-      <c r="F1" s="80" t="n"/>
+      <c r="E1" s="79" t="n"/>
+      <c r="F1" s="79" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="D2" s="80">
+      <c r="D2" s="79">
         <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$26="","",'ИСХОДНЫЕ ДАННЫЕ'!$C$25&amp;" "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$26)</f>
         <v/>
       </c>
-      <c r="E2" s="80" t="n"/>
-      <c r="F2" s="80" t="n"/>
+      <c r="E2" s="79" t="n"/>
+      <c r="F2" s="79" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="D3" s="81">
+      <c r="D3" s="80">
         <f>"от Председателя МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;", "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$18</f>
         <v/>
       </c>
-      <c r="E3" s="81" t="n"/>
-      <c r="F3" s="81" t="n"/>
+      <c r="E3" s="80" t="n"/>
+      <c r="F3" s="80" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="D4" s="81">
+      <c r="D4" s="80">
         <f>"проживающей по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$20</f>
         <v/>
       </c>
-      <c r="E4" s="81" t="n"/>
-      <c r="F4" s="81" t="n"/>
+      <c r="E4" s="80" t="n"/>
+      <c r="F4" s="80" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="D5" s="81">
+      <c r="D5" s="80">
         <f>"Конт. тел.: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21</f>
         <v/>
       </c>
-      <c r="E5" s="81" t="n"/>
-      <c r="F5" s="81" t="n"/>
+      <c r="E5" s="80" t="n"/>
+      <c r="F5" s="80" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="D6" s="81">
+      <c r="D6" s="80">
         <f>"Эл. почта: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22</f>
         <v/>
       </c>
-      <c r="E6" s="81" t="n"/>
-      <c r="F6" s="81" t="n"/>
+      <c r="E6" s="80" t="n"/>
+      <c r="F6" s="80" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1"/>
     <row r="8" ht="46" customHeight="1">
-      <c r="B8" s="81">
+      <c r="B8" s="80">
         <f>"В связи с тем, что на балансе департамента числится кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", сообщаю Вам о необходимости оплатить "&amp;IF(INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2)*100,0)-INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))*100),"00")&amp;" руб., в том числе:"</f>
         <v/>
       </c>
-      <c r="C8" s="81" t="n"/>
-      <c r="D8" s="81" t="n"/>
-      <c r="E8" s="81" t="n"/>
-      <c r="F8" s="81" t="n"/>
+      <c r="C8" s="80" t="n"/>
+      <c r="D8" s="80" t="n"/>
+      <c r="E8" s="80" t="n"/>
+      <c r="F8" s="80" t="n"/>
     </row>
     <row r="9" ht="8" customHeight="1"/>
     <row r="10" ht="32" customHeight="1">
-      <c r="B10" s="81">
+      <c r="B10" s="80">
         <f>"— текущий платёж за период с апреля по июнь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года ("&amp;"II квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;") в размере "&amp;IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100),"00")&amp;" рублей"</f>
         <v/>
       </c>
-      <c r="C10" s="81" t="n"/>
-      <c r="D10" s="81" t="n"/>
-      <c r="E10" s="81" t="n"/>
-      <c r="F10" s="81" t="n"/>
+      <c r="C10" s="80" t="n"/>
+      <c r="D10" s="80" t="n"/>
+      <c r="E10" s="80" t="n"/>
+      <c r="F10" s="80" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="82">
+      <c r="B11" s="81">
         <f>"("&amp;UPPER(LEFT(IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)=0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)=0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1),2,300)&amp;")."</f>
         <v/>
       </c>
-      <c r="C11" s="82" t="n"/>
-      <c r="D11" s="82" t="n"/>
-      <c r="E11" s="82" t="n"/>
-      <c r="F11" s="82" t="n"/>
+      <c r="C11" s="81" t="n"/>
+      <c r="D11" s="81" t="n"/>
+      <c r="E11" s="81" t="n"/>
+      <c r="F11" s="81" t="n"/>
     </row>
     <row r="12" ht="6" customHeight="1"/>
     <row r="13" ht="32" customHeight="1">
-      <c r="B13" s="81">
+      <c r="B13" s="80">
         <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$31=0,"— задолженности за предыдущие периоды нет.","— задолженность "&amp;IF('ИСХОДНЫЕ ДАННЫЕ'!$D$31="","за предыдущие периоды",'ИСХОДНЫЕ ДАННЫЕ'!$D$31)&amp;" в размере "&amp;IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)&gt;0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)&amp;" "&amp;TEXT((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000),"000"),(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))*100),"00")&amp;" рублей")</f>
         <v/>
       </c>
-      <c r="C13" s="81" t="n"/>
-      <c r="D13" s="81" t="n"/>
-      <c r="E13" s="81" t="n"/>
-      <c r="F13" s="81" t="n"/>
+      <c r="C13" s="80" t="n"/>
+      <c r="D13" s="80" t="n"/>
+      <c r="E13" s="80" t="n"/>
+      <c r="F13" s="80" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="82">
+      <c r="B14" s="81">
         <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$31=0,"","("&amp;UPPER(LEFT(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))*100)+1),2,300)&amp;").")</f>
         <v/>
       </c>
-      <c r="C14" s="82" t="n"/>
-      <c r="D14" s="82" t="n"/>
-      <c r="E14" s="82" t="n"/>
-      <c r="F14" s="82" t="n"/>
+      <c r="C14" s="81" t="n"/>
+      <c r="D14" s="81" t="n"/>
+      <c r="E14" s="81" t="n"/>
+      <c r="F14" s="81" t="n"/>
     </row>
     <row r="15" ht="10" customHeight="1"/>
     <row r="16" ht="76" customHeight="1">
-      <c r="B16" s="81">
+      <c r="B16" s="80">
         <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$31)&amp;" и с учётом начислений по "&amp;"июнь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
       </c>
-      <c r="C16" s="81" t="n"/>
-      <c r="D16" s="81" t="n"/>
-      <c r="E16" s="81" t="n"/>
-      <c r="F16" s="81" t="n"/>
+      <c r="C16" s="80" t="n"/>
+      <c r="D16" s="80" t="n"/>
+      <c r="E16" s="80" t="n"/>
+      <c r="F16" s="80" t="n"/>
     </row>
     <row r="17" ht="10" customHeight="1"/>
     <row r="18" ht="46" customHeight="1">
-      <c r="B18" s="81">
+      <c r="B18" s="80">
         <f>"В случае возникновения дополнительных вопросов прошу связаться со мной по электронной почте "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22&amp;" или по телефону "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
       </c>
-      <c r="C18" s="81" t="n"/>
-      <c r="D18" s="81" t="n"/>
-      <c r="E18" s="81" t="n"/>
-      <c r="F18" s="81" t="n"/>
+      <c r="C18" s="80" t="n"/>
+      <c r="D18" s="80" t="n"/>
+      <c r="E18" s="80" t="n"/>
+      <c r="F18" s="80" t="n"/>
     </row>
     <row r="19" ht="14" customHeight="1"/>
     <row r="20" ht="20" customHeight="1">
-      <c r="B20" s="80" t="inlineStr">
+      <c r="B20" s="79" t="inlineStr">
         <is>
           <t>ПРИЛОЖЕНИЯ:</t>
         </is>
       </c>
-      <c r="C20" s="80" t="n"/>
-      <c r="D20" s="80" t="n"/>
-      <c r="E20" s="80" t="n"/>
-      <c r="F20" s="80" t="n"/>
+      <c r="C20" s="79" t="n"/>
+      <c r="D20" s="79" t="n"/>
+      <c r="E20" s="79" t="n"/>
+      <c r="F20" s="79" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="81">
+      <c r="B21" s="80">
         <f>"1) Акт взаимных расчётов по состоянию на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$31)&amp;" — один экземпляр на 1 л."</f>
         <v/>
       </c>
-      <c r="C21" s="81" t="n"/>
-      <c r="D21" s="81" t="n"/>
-      <c r="E21" s="81" t="n"/>
-      <c r="F21" s="81" t="n"/>
+      <c r="C21" s="80" t="n"/>
+      <c r="D21" s="80" t="n"/>
+      <c r="E21" s="80" t="n"/>
+      <c r="F21" s="80" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="81">
+      <c r="B22" s="80">
         <f>"2) Квитанция для оплаты за "&amp;"II квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — один экземпляр на 1 л."</f>
         <v/>
       </c>
-      <c r="C22" s="81" t="n"/>
-      <c r="D22" s="81" t="n"/>
-      <c r="E22" s="81" t="n"/>
-      <c r="F22" s="81" t="n"/>
+      <c r="C22" s="80" t="n"/>
+      <c r="D22" s="80" t="n"/>
+      <c r="E22" s="80" t="n"/>
+      <c r="F22" s="80" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1"/>
     <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="81">
+      <c r="B24" s="80">
         <f>"«______» ______________ "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="C24" s="81" t="n"/>
+      <c r="C24" s="80" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1"/>
     <row r="26" ht="16" customHeight="1">
-      <c r="B26" s="81" t="inlineStr">
+      <c r="B26" s="80" t="inlineStr">
         <is>
           <t>Председатель</t>
         </is>
       </c>
-      <c r="C26" s="81" t="n"/>
+      <c r="C26" s="80" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="B27" s="81">
+      <c r="B27" s="80">
         <f>"МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15</f>
         <v/>
       </c>
-      <c r="C27" s="81" t="n"/>
-      <c r="D27" s="83">
+      <c r="C27" s="80" t="n"/>
+      <c r="D27" s="82">
         <f>"___________________  /"&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$19&amp;"/"</f>
         <v/>
       </c>
-      <c r="E27" s="83" t="n"/>
-      <c r="F27" s="83" t="n"/>
+      <c r="E27" s="82" t="n"/>
+      <c r="F27" s="82" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -35451,189 +35367,189 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="D1" s="80">
+      <c r="D1" s="79">
         <f>"В "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$24</f>
         <v/>
       </c>
-      <c r="E1" s="80" t="n"/>
-      <c r="F1" s="80" t="n"/>
+      <c r="E1" s="79" t="n"/>
+      <c r="F1" s="79" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="D2" s="80">
+      <c r="D2" s="79">
         <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$26="","",'ИСХОДНЫЕ ДАННЫЕ'!$C$25&amp;" "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$26)</f>
         <v/>
       </c>
-      <c r="E2" s="80" t="n"/>
-      <c r="F2" s="80" t="n"/>
+      <c r="E2" s="79" t="n"/>
+      <c r="F2" s="79" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="D3" s="81">
+      <c r="D3" s="80">
         <f>"от Председателя МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;", "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$18</f>
         <v/>
       </c>
-      <c r="E3" s="81" t="n"/>
-      <c r="F3" s="81" t="n"/>
+      <c r="E3" s="80" t="n"/>
+      <c r="F3" s="80" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="D4" s="81">
+      <c r="D4" s="80">
         <f>"проживающей по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$20</f>
         <v/>
       </c>
-      <c r="E4" s="81" t="n"/>
-      <c r="F4" s="81" t="n"/>
+      <c r="E4" s="80" t="n"/>
+      <c r="F4" s="80" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="D5" s="81">
+      <c r="D5" s="80">
         <f>"Конт. тел.: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21</f>
         <v/>
       </c>
-      <c r="E5" s="81" t="n"/>
-      <c r="F5" s="81" t="n"/>
+      <c r="E5" s="80" t="n"/>
+      <c r="F5" s="80" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="D6" s="81">
+      <c r="D6" s="80">
         <f>"Эл. почта: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22</f>
         <v/>
       </c>
-      <c r="E6" s="81" t="n"/>
-      <c r="F6" s="81" t="n"/>
+      <c r="E6" s="80" t="n"/>
+      <c r="F6" s="80" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1"/>
     <row r="8" ht="46" customHeight="1">
-      <c r="B8" s="81">
+      <c r="B8" s="80">
         <f>"В связи с тем, что на балансе департамента числится кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", сообщаю Вам о необходимости оплатить "&amp;IF(INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2)*100,0)-INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))*100),"00")&amp;" руб., в том числе:"</f>
         <v/>
       </c>
-      <c r="C8" s="81" t="n"/>
-      <c r="D8" s="81" t="n"/>
-      <c r="E8" s="81" t="n"/>
-      <c r="F8" s="81" t="n"/>
+      <c r="C8" s="80" t="n"/>
+      <c r="D8" s="80" t="n"/>
+      <c r="E8" s="80" t="n"/>
+      <c r="F8" s="80" t="n"/>
     </row>
     <row r="9" ht="8" customHeight="1"/>
     <row r="10" ht="32" customHeight="1">
-      <c r="B10" s="81">
+      <c r="B10" s="80">
         <f>"— текущий платёж за период с июля по сентябрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года ("&amp;"III квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;") в размере "&amp;IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100),"00")&amp;" рублей"</f>
         <v/>
       </c>
-      <c r="C10" s="81" t="n"/>
-      <c r="D10" s="81" t="n"/>
-      <c r="E10" s="81" t="n"/>
-      <c r="F10" s="81" t="n"/>
+      <c r="C10" s="80" t="n"/>
+      <c r="D10" s="80" t="n"/>
+      <c r="E10" s="80" t="n"/>
+      <c r="F10" s="80" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="82">
+      <c r="B11" s="81">
         <f>"("&amp;UPPER(LEFT(IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)=0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)=0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1),2,300)&amp;")."</f>
         <v/>
       </c>
-      <c r="C11" s="82" t="n"/>
-      <c r="D11" s="82" t="n"/>
-      <c r="E11" s="82" t="n"/>
-      <c r="F11" s="82" t="n"/>
+      <c r="C11" s="81" t="n"/>
+      <c r="D11" s="81" t="n"/>
+      <c r="E11" s="81" t="n"/>
+      <c r="F11" s="81" t="n"/>
     </row>
     <row r="12" ht="6" customHeight="1"/>
     <row r="13" ht="32" customHeight="1">
-      <c r="B13" s="81">
+      <c r="B13" s="80">
         <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$32=0,"— задолженности за предыдущие периоды нет.","— задолженность "&amp;IF('ИСХОДНЫЕ ДАННЫЕ'!$D$32="","за предыдущие периоды",'ИСХОДНЫЕ ДАННЫЕ'!$D$32)&amp;" в размере "&amp;IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)&gt;0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)&amp;" "&amp;TEXT((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000),"000"),(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))*100),"00")&amp;" рублей")</f>
         <v/>
       </c>
-      <c r="C13" s="81" t="n"/>
-      <c r="D13" s="81" t="n"/>
-      <c r="E13" s="81" t="n"/>
-      <c r="F13" s="81" t="n"/>
+      <c r="C13" s="80" t="n"/>
+      <c r="D13" s="80" t="n"/>
+      <c r="E13" s="80" t="n"/>
+      <c r="F13" s="80" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="82">
+      <c r="B14" s="81">
         <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$32=0,"","("&amp;UPPER(LEFT(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))*100)+1),2,300)&amp;").")</f>
         <v/>
       </c>
-      <c r="C14" s="82" t="n"/>
-      <c r="D14" s="82" t="n"/>
-      <c r="E14" s="82" t="n"/>
-      <c r="F14" s="82" t="n"/>
+      <c r="C14" s="81" t="n"/>
+      <c r="D14" s="81" t="n"/>
+      <c r="E14" s="81" t="n"/>
+      <c r="F14" s="81" t="n"/>
     </row>
     <row r="15" ht="10" customHeight="1"/>
     <row r="16" ht="76" customHeight="1">
-      <c r="B16" s="81">
+      <c r="B16" s="80">
         <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$32)&amp;" и с учётом начислений по "&amp;"сентябрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
       </c>
-      <c r="C16" s="81" t="n"/>
-      <c r="D16" s="81" t="n"/>
-      <c r="E16" s="81" t="n"/>
-      <c r="F16" s="81" t="n"/>
+      <c r="C16" s="80" t="n"/>
+      <c r="D16" s="80" t="n"/>
+      <c r="E16" s="80" t="n"/>
+      <c r="F16" s="80" t="n"/>
     </row>
     <row r="17" ht="10" customHeight="1"/>
     <row r="18" ht="46" customHeight="1">
-      <c r="B18" s="81">
+      <c r="B18" s="80">
         <f>"В случае возникновения дополнительных вопросов прошу связаться со мной по электронной почте "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22&amp;" или по телефону "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
       </c>
-      <c r="C18" s="81" t="n"/>
-      <c r="D18" s="81" t="n"/>
-      <c r="E18" s="81" t="n"/>
-      <c r="F18" s="81" t="n"/>
+      <c r="C18" s="80" t="n"/>
+      <c r="D18" s="80" t="n"/>
+      <c r="E18" s="80" t="n"/>
+      <c r="F18" s="80" t="n"/>
     </row>
     <row r="19" ht="14" customHeight="1"/>
     <row r="20" ht="20" customHeight="1">
-      <c r="B20" s="80" t="inlineStr">
+      <c r="B20" s="79" t="inlineStr">
         <is>
           <t>ПРИЛОЖЕНИЯ:</t>
         </is>
       </c>
-      <c r="C20" s="80" t="n"/>
-      <c r="D20" s="80" t="n"/>
-      <c r="E20" s="80" t="n"/>
-      <c r="F20" s="80" t="n"/>
+      <c r="C20" s="79" t="n"/>
+      <c r="D20" s="79" t="n"/>
+      <c r="E20" s="79" t="n"/>
+      <c r="F20" s="79" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="81">
+      <c r="B21" s="80">
         <f>"1) Акт взаимных расчётов по состоянию на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$32)&amp;" — один экземпляр на 1 л."</f>
         <v/>
       </c>
-      <c r="C21" s="81" t="n"/>
-      <c r="D21" s="81" t="n"/>
-      <c r="E21" s="81" t="n"/>
-      <c r="F21" s="81" t="n"/>
+      <c r="C21" s="80" t="n"/>
+      <c r="D21" s="80" t="n"/>
+      <c r="E21" s="80" t="n"/>
+      <c r="F21" s="80" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="81">
+      <c r="B22" s="80">
         <f>"2) Квитанция для оплаты за "&amp;"III квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — один экземпляр на 1 л."</f>
         <v/>
       </c>
-      <c r="C22" s="81" t="n"/>
-      <c r="D22" s="81" t="n"/>
-      <c r="E22" s="81" t="n"/>
-      <c r="F22" s="81" t="n"/>
+      <c r="C22" s="80" t="n"/>
+      <c r="D22" s="80" t="n"/>
+      <c r="E22" s="80" t="n"/>
+      <c r="F22" s="80" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1"/>
     <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="81">
+      <c r="B24" s="80">
         <f>"«______» ______________ "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="C24" s="81" t="n"/>
+      <c r="C24" s="80" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1"/>
     <row r="26" ht="16" customHeight="1">
-      <c r="B26" s="81" t="inlineStr">
+      <c r="B26" s="80" t="inlineStr">
         <is>
           <t>Председатель</t>
         </is>
       </c>
-      <c r="C26" s="81" t="n"/>
+      <c r="C26" s="80" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="B27" s="81">
+      <c r="B27" s="80">
         <f>"МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15</f>
         <v/>
       </c>
-      <c r="C27" s="81" t="n"/>
-      <c r="D27" s="83">
+      <c r="C27" s="80" t="n"/>
+      <c r="D27" s="82">
         <f>"___________________  /"&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$19&amp;"/"</f>
         <v/>
       </c>
-      <c r="E27" s="83" t="n"/>
-      <c r="F27" s="83" t="n"/>
+      <c r="E27" s="82" t="n"/>
+      <c r="F27" s="82" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/kapremont/output/Квитанции_квартальные_цветной.xlsx
+++ b/kapremont/output/Квитанции_квартальные_цветной.xlsx
@@ -1015,12 +1015,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1382,7 +1382,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
+    <row r="30" ht="30" customHeight="1">
       <c r="B30" s="4" t="inlineStr">
         <is>
           <t>I квартал</t>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="F30" s="11" t="n"/>
     </row>
-    <row r="31" ht="18" customHeight="1">
+    <row r="31" ht="30" customHeight="1">
       <c r="B31" s="4" t="inlineStr">
         <is>
           <t>II квартал</t>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="F31" s="11" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1">
+    <row r="32" ht="30" customHeight="1">
       <c r="B32" s="4" t="inlineStr">
         <is>
           <t>III квартал</t>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F32" s="11" t="n"/>
     </row>
-    <row r="33" ht="18" customHeight="1">
+    <row r="33" ht="30" customHeight="1">
       <c r="B33" s="4" t="inlineStr">
         <is>
           <t>IV квартал</t>
@@ -1624,7 +1624,7 @@
     <mergeCell ref="B4:G4"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1637,13 +1637,13 @@
   <dimension ref="B1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="2" customWidth="1" min="7" max="7"/>
+    <col width="0.8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="0.8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1695,7 +1695,7 @@
       <c r="F6" s="80" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1"/>
-    <row r="8" ht="46" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="B8" s="80">
         <f>"В связи с тем, что на балансе департамента числится кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", сообщаю Вам о необходимости оплатить "&amp;IF(INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2)*100,0)-INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))*100),"00")&amp;" руб., в том числе:"</f>
         <v/>
@@ -1706,7 +1706,7 @@
       <c r="F8" s="80" t="n"/>
     </row>
     <row r="9" ht="8" customHeight="1"/>
-    <row r="10" ht="32" customHeight="1">
+    <row r="10" ht="38" customHeight="1">
       <c r="B10" s="80">
         <f>"— текущий платёж за период с октября по декабрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года ("&amp;"IV квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;") в размере "&amp;IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100),"00")&amp;" рублей"</f>
         <v/>
@@ -1748,7 +1748,7 @@
       <c r="F14" s="81" t="n"/>
     </row>
     <row r="15" ht="10" customHeight="1"/>
-    <row r="16" ht="76" customHeight="1">
+    <row r="16" ht="90" customHeight="1">
       <c r="B16" s="80">
         <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$33)&amp;" и с учётом начислений по "&amp;"декабрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
@@ -1759,7 +1759,7 @@
       <c r="F16" s="80" t="n"/>
     </row>
     <row r="17" ht="10" customHeight="1"/>
-    <row r="18" ht="46" customHeight="1">
+    <row r="18" ht="54" customHeight="1">
       <c r="B18" s="80">
         <f>"В случае возникновения дополнительных вопросов прошу связаться со мной по электронной почте "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22&amp;" или по телефону "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
@@ -1854,7 +1854,7 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="D6:F6"/>
   </mergeCells>
-  <pageMargins left="0.79" right="0.59" top="0.59" bottom="0.59" header="0.5" footer="0.5"/>
+  <pageMargins left="0.79" right="0.39" top="0.59" bottom="0.59" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
@@ -1868,12 +1868,12 @@
   <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -2043,7 +2043,7 @@
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A7:F7"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
@@ -34895,13 +34895,13 @@
   <dimension ref="B1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="2" customWidth="1" min="7" max="7"/>
+    <col width="0.8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="0.8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -34953,7 +34953,7 @@
       <c r="F6" s="80" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1"/>
-    <row r="8" ht="46" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="B8" s="80">
         <f>"В связи с тем, что на балансе департамента числится кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", сообщаю Вам о необходимости оплатить "&amp;IF(INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2)*100,0)-INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))*100),"00")&amp;" руб., в том числе:"</f>
         <v/>
@@ -34964,7 +34964,7 @@
       <c r="F8" s="80" t="n"/>
     </row>
     <row r="9" ht="8" customHeight="1"/>
-    <row r="10" ht="32" customHeight="1">
+    <row r="10" ht="38" customHeight="1">
       <c r="B10" s="80">
         <f>"— текущий платёж за период с января по март "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года ("&amp;"I квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;") в размере "&amp;IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100),"00")&amp;" рублей"</f>
         <v/>
@@ -35006,7 +35006,7 @@
       <c r="F14" s="81" t="n"/>
     </row>
     <row r="15" ht="10" customHeight="1"/>
-    <row r="16" ht="76" customHeight="1">
+    <row r="16" ht="90" customHeight="1">
       <c r="B16" s="80">
         <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$30),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$30),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$30)&amp;" и с учётом начислений по "&amp;"март "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
@@ -35017,7 +35017,7 @@
       <c r="F16" s="80" t="n"/>
     </row>
     <row r="17" ht="10" customHeight="1"/>
-    <row r="18" ht="46" customHeight="1">
+    <row r="18" ht="54" customHeight="1">
       <c r="B18" s="80">
         <f>"В случае возникновения дополнительных вопросов прошу связаться со мной по электронной почте "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22&amp;" или по телефону "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
@@ -35112,7 +35112,7 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="D6:F6"/>
   </mergeCells>
-  <pageMargins left="0.79" right="0.59" top="0.59" bottom="0.59" header="0.5" footer="0.5"/>
+  <pageMargins left="0.79" right="0.39" top="0.59" bottom="0.59" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
@@ -35126,13 +35126,13 @@
   <dimension ref="B1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="2" customWidth="1" min="7" max="7"/>
+    <col width="0.8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="0.8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -35184,7 +35184,7 @@
       <c r="F6" s="80" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1"/>
-    <row r="8" ht="46" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="B8" s="80">
         <f>"В связи с тем, что на балансе департамента числится кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", сообщаю Вам о необходимости оплатить "&amp;IF(INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2)*100,0)-INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))*100),"00")&amp;" руб., в том числе:"</f>
         <v/>
@@ -35195,7 +35195,7 @@
       <c r="F8" s="80" t="n"/>
     </row>
     <row r="9" ht="8" customHeight="1"/>
-    <row r="10" ht="32" customHeight="1">
+    <row r="10" ht="38" customHeight="1">
       <c r="B10" s="80">
         <f>"— текущий платёж за период с апреля по июнь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года ("&amp;"II квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;") в размере "&amp;IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100),"00")&amp;" рублей"</f>
         <v/>
@@ -35237,7 +35237,7 @@
       <c r="F14" s="81" t="n"/>
     </row>
     <row r="15" ht="10" customHeight="1"/>
-    <row r="16" ht="76" customHeight="1">
+    <row r="16" ht="90" customHeight="1">
       <c r="B16" s="80">
         <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$31)&amp;" и с учётом начислений по "&amp;"июнь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
@@ -35248,7 +35248,7 @@
       <c r="F16" s="80" t="n"/>
     </row>
     <row r="17" ht="10" customHeight="1"/>
-    <row r="18" ht="46" customHeight="1">
+    <row r="18" ht="54" customHeight="1">
       <c r="B18" s="80">
         <f>"В случае возникновения дополнительных вопросов прошу связаться со мной по электронной почте "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22&amp;" или по телефону "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
@@ -35343,7 +35343,7 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="D6:F6"/>
   </mergeCells>
-  <pageMargins left="0.79" right="0.59" top="0.59" bottom="0.59" header="0.5" footer="0.5"/>
+  <pageMargins left="0.79" right="0.39" top="0.59" bottom="0.59" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
@@ -35357,13 +35357,13 @@
   <dimension ref="B1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="2" customWidth="1" min="7" max="7"/>
+    <col width="0.8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="0.8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -35415,7 +35415,7 @@
       <c r="F6" s="80" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1"/>
-    <row r="8" ht="46" customHeight="1">
+    <row r="8" ht="54" customHeight="1">
       <c r="B8" s="80">
         <f>"В связи с тем, что на балансе департамента числится кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", сообщаю Вам о необходимости оплатить "&amp;IF(INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2)*100,0)-INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))*100),"00")&amp;" руб., в том числе:"</f>
         <v/>
@@ -35426,7 +35426,7 @@
       <c r="F8" s="80" t="n"/>
     </row>
     <row r="9" ht="8" customHeight="1"/>
-    <row r="10" ht="32" customHeight="1">
+    <row r="10" ht="38" customHeight="1">
       <c r="B10" s="80">
         <f>"— текущий платёж за период с июля по сентябрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года ("&amp;"III квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;") в размере "&amp;IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100),"00")&amp;" рублей"</f>
         <v/>
@@ -35468,7 +35468,7 @@
       <c r="F14" s="81" t="n"/>
     </row>
     <row r="15" ht="10" customHeight="1"/>
-    <row r="16" ht="76" customHeight="1">
+    <row r="16" ht="90" customHeight="1">
       <c r="B16" s="80">
         <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$32)&amp;" и с учётом начислений по "&amp;"сентябрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
@@ -35479,7 +35479,7 @@
       <c r="F16" s="80" t="n"/>
     </row>
     <row r="17" ht="10" customHeight="1"/>
-    <row r="18" ht="46" customHeight="1">
+    <row r="18" ht="54" customHeight="1">
       <c r="B18" s="80">
         <f>"В случае возникновения дополнительных вопросов прошу связаться со мной по электронной почте "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22&amp;" или по телефону "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
@@ -35574,7 +35574,7 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="D6:F6"/>
   </mergeCells>
-  <pageMargins left="0.79" right="0.59" top="0.59" bottom="0.59" header="0.5" footer="0.5"/>
+  <pageMargins left="0.79" right="0.39" top="0.59" bottom="0.59" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/kapremont/output/Квитанции_квартальные_цветной.xlsx
+++ b/kapremont/output/Квитанции_квартальные_цветной.xlsx
@@ -26,16 +26,16 @@
     <definedName name="ИД_НАЧИСЛЕНО_МЕС">'ИСХОДНЫЕ ДАННЫЕ'!$C$8</definedName>
     <definedName name="ИД_ЛС">'ИСХОДНЫЕ ДАННЫЕ'!$C$11</definedName>
     <definedName name="ИД_КВАРТИРА">'ИСХОДНЫЕ ДАННЫЕ'!$C$12</definedName>
-    <definedName name="ИД_КВАРТАЛЫ">'ИСХОДНЫЕ ДАННЫЕ'!$B$30:$F$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'ИСХОДНЫЕ ДАННЫЕ'!$B$1:$F$50</definedName>
+    <definedName name="ИД_КВАРТАЛЫ">'ИСХОДНЫЕ ДАННЫЕ'!$B$31:$F$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'ИСХОДНЫЕ ДАННЫЕ'!$B$1:$F$52</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Квитанция 1 кв'!$A$1:$I$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Квитанция 2 кв'!$A$1:$I$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Квитанция 3 кв'!$A$1:$I$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Квитанция 4 кв'!$A$1:$I$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Письмо 1 кв'!$A$1:$G$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Письмо 2 кв'!$A$1:$G$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'Письмо 3 кв'!$A$1:$G$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'Письмо 4 кв'!$A$1:$G$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Письмо 1 кв'!$B$1:$F$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Письмо 2 кв'!$B$1:$F$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Письмо 3 кв'!$B$1:$F$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'Письмо 4 кв'!$B$1:$F$27</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="10">'ИНСТРУКЦИЯ'!$A$1:$F$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -49,7 +49,7 @@
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="166" formatCode="DD.MM.YYYY"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,6 +78,18 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="00263238"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000F6B70"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
@@ -88,6 +100,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="000F6B70"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00263238"/>
       <sz val="10"/>
     </font>
     <font>
@@ -128,18 +146,7 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00263238"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00263238"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00263238"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -182,8 +189,12 @@
       <color rgb="000F6B70"/>
       <sz val="13"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -192,17 +203,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00263238"/>
+        <fgColor rgb="000F6B70"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F3F5F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F6B70"/>
+        <fgColor rgb="00E8F3F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -212,17 +223,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F5F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F3F3"/>
+        <fgColor rgb="00263238"/>
       </patternFill>
     </fill>
   </fills>
@@ -392,258 +398,261 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="9" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="13" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="13" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="13" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="17" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="18" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="13" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="4" fontId="13" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1011,13 +1020,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G49"/>
+  <dimension ref="B1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -1033,7 +1042,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Жёлтые ячейки — для ввода. Всё остальное в книге считается формулами от них; квитанции и письма пересчитаются сами.</t>
+          <t>Ячейки на бирюзовом фоне — для ввода. Всё остальное в книге считается формулами от них; квитанции и письма пересчитаются сами.</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1058,7 @@
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n"/>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Год</t>
@@ -1064,7 +1073,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
+    <row r="6" ht="30" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Площадь помещения, м²</t>
@@ -1079,7 +1088,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Размер взноса, руб./м² в месяц</t>
@@ -1095,12 +1104,12 @@
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Начислено за месяц, руб.</t>
         </is>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="10">
         <f>ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$6*'ИСХОДНЫЕ ДАННЫЕ'!$C$7,2)</f>
         <v/>
       </c>
@@ -1122,7 +1131,7 @@
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="3" t="n"/>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11" ht="30" customHeight="1">
       <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Лицевой счёт</t>
@@ -1137,7 +1146,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
+    <row r="12" ht="30" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Квартира №</t>
@@ -1152,7 +1161,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
+    <row r="13" ht="30" customHeight="1">
       <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Плательщик (собственник)</t>
@@ -1169,7 +1178,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
+    <row r="14" ht="30" customHeight="1">
       <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Адрес МКД</t>
@@ -1186,7 +1195,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
+    <row r="15" ht="30" customHeight="1">
       <c r="B15" s="4" t="inlineStr">
         <is>
           <t>МКД кратко</t>
@@ -1215,7 +1224,7 @@
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
     </row>
-    <row r="18" ht="18" customHeight="1">
+    <row r="18" ht="30" customHeight="1">
       <c r="B18" s="4" t="inlineStr">
         <is>
           <t>ФИО в родительном падеже</t>
@@ -1232,7 +1241,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
+    <row r="19" ht="30" customHeight="1">
       <c r="B19" s="4" t="inlineStr">
         <is>
           <t>ФИО кратко</t>
@@ -1249,7 +1258,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
+    <row r="20" ht="30" customHeight="1">
       <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Адрес проживания</t>
@@ -1262,7 +1271,7 @@
       </c>
       <c r="D20" s="6" t="inlineStr"/>
     </row>
-    <row r="21" ht="18" customHeight="1">
+    <row r="21" ht="30" customHeight="1">
       <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Телефон</t>
@@ -1275,7 +1284,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr"/>
     </row>
-    <row r="22" ht="18" customHeight="1">
+    <row r="22" ht="30" customHeight="1">
       <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Электронная почта</t>
@@ -1288,324 +1297,324 @@
       </c>
       <c r="D22" s="6" t="inlineStr"/>
     </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="B23" s="3" t="inlineStr">
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>4. АДРЕСАТ ПИСЬМА (МЕНЯЕТСЯ ПРИ СМЕНЕ РУКОВОДИТЕЛЯ)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-      <c r="E23" s="3" t="n"/>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
+      <c r="C24" s="3" t="n"/>
+      <c r="D24" s="3" t="n"/>
+      <c r="E24" s="3" t="n"/>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="3" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Организация</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Департамент жилищной политики Администрации города Омска</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="4" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Должность руководителя</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Директору</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>В дательном падеже: «Директору»</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="4" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>ФИО руководителя</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>Оставьте пустым — строка не напечатается</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="B28" s="3" t="inlineStr">
+    <row r="29" ht="20" customHeight="1">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>5. ПО КВАРТАЛАМ: ЗАДОЛЖЕННОСТЬ И ДАТЫ</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n"/>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="B29" s="10" t="inlineStr">
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>Квартал</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>Задолженность, руб.</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>Описание задолженности</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Дата формирования</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>Поступило с начала года, руб.</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>I квартал</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="n">
-        <v>4042.38</v>
-      </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>за III и IV кварталы 2025 года</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="n">
-        <v>46051</v>
-      </c>
-      <c r="F30" s="11" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>II квартал</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="12" t="inlineStr"/>
-      <c r="E31" s="13" t="n">
-        <v>46127</v>
-      </c>
-      <c r="F31" s="11" t="n"/>
+          <t>I квартал</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>4042.38</v>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>за III и IV кварталы 2025 года</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>46051</v>
+      </c>
+      <c r="F31" s="12" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>III квартал</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="n">
+          <t>II квартал</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="12" t="inlineStr"/>
-      <c r="E32" s="13" t="n">
-        <v>46218</v>
-      </c>
-      <c r="F32" s="11" t="n"/>
+      <c r="D32" s="13" t="inlineStr"/>
+      <c r="E32" s="14" t="n">
+        <v>46127</v>
+      </c>
+      <c r="F32" s="12" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="B33" s="4" t="inlineStr">
         <is>
+          <t>III квартал</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="13" t="inlineStr"/>
+      <c r="E33" s="14" t="n">
+        <v>46218</v>
+      </c>
+      <c r="F33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
           <t>IV квартал</t>
         </is>
       </c>
-      <c r="C33" s="11" t="n">
+      <c r="C34" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="12" t="inlineStr"/>
-      <c r="E33" s="13" t="n">
+      <c r="D34" s="13" t="inlineStr"/>
+      <c r="E34" s="14" t="n">
         <v>46310</v>
       </c>
-      <c r="F33" s="11" t="n"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="14" t="inlineStr">
+      <c r="F34" s="12" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>Задолженность и даты — единственное, что меняется от квартала к кварталу. Столбец «Поступило» можно не заполнять: в квитанции тогда встанет прочерк.</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="38" ht="20" customHeight="1">
-      <c r="B38" s="3" t="inlineStr">
+    <row r="37"/>
+    <row r="39" ht="20" customHeight="1">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>6. РЕКВИЗИТЫ СПЕЦИАЛЬНОГО СЧЁТА (НЕ МЕНЯЮТСЯ)</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="3" t="n"/>
-      <c r="E38" s="3" t="n"/>
-      <c r="F38" s="3" t="n"/>
-      <c r="G38" s="3" t="n"/>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="B39" s="4" t="inlineStr">
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n"/>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+    </row>
+    <row r="40" ht="44" customHeight="1">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Получатель платежа</t>
         </is>
       </c>
-      <c r="C39" s="15" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>РЕГИОНАЛЬНЫЙ ФОНД КАПИТАЛЬНОГО РЕМОНТА МНОГОКВАРТИРНЫХ ДОМОВ ОМСКОЙ ОБЛАСТИ (СПЕЦ. СЧЕТ)</t>
         </is>
       </c>
-      <c r="D39" s="16" t="n"/>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="B40" s="4" t="inlineStr">
+      <c r="D40" s="17" t="n"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Юридический адрес</t>
         </is>
       </c>
-      <c r="C40" s="15" t="inlineStr">
+      <c r="C41" s="16" t="inlineStr">
         <is>
           <t>644099, г. Омск, ул. Краснофлотская, 24</t>
         </is>
       </c>
-      <c r="D40" s="16" t="n"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="B41" s="4" t="inlineStr">
+      <c r="D41" s="17" t="n"/>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>ИНН</t>
         </is>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="C42" s="16" t="inlineStr">
         <is>
           <t>5503239348</t>
         </is>
       </c>
-      <c r="D41" s="16" t="n"/>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="B42" s="4" t="inlineStr">
+      <c r="D42" s="17" t="n"/>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>КПП</t>
         </is>
       </c>
-      <c r="C42" s="15" t="inlineStr">
+      <c r="C43" s="16" t="inlineStr">
         <is>
           <t>550301001</t>
         </is>
       </c>
-      <c r="D42" s="16" t="n"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="B43" s="4" t="inlineStr">
+      <c r="D43" s="17" t="n"/>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>ОГРН</t>
         </is>
       </c>
-      <c r="C43" s="15" t="inlineStr">
+      <c r="C44" s="16" t="inlineStr">
         <is>
           <t>1027700342890</t>
         </is>
       </c>
-      <c r="D43" s="16" t="n"/>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="B44" s="4" t="inlineStr">
+      <c r="D44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Расчётный счёт (спец. счёт МКД)</t>
         </is>
       </c>
-      <c r="C44" s="15" t="inlineStr">
+      <c r="C45" s="16" t="inlineStr">
         <is>
           <t>40604810809000000154</t>
         </is>
       </c>
-      <c r="D44" s="16" t="n"/>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="B45" s="4" t="inlineStr">
+      <c r="D45" s="17" t="n"/>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
       </c>
-      <c r="C45" s="15" t="inlineStr">
+      <c r="C46" s="16" t="inlineStr">
         <is>
           <t>Омский РФ АО «Россельхозбанк»</t>
         </is>
       </c>
-      <c r="D45" s="16" t="n"/>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="B46" s="4" t="inlineStr">
+      <c r="D46" s="17" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Корреспондентский счёт</t>
         </is>
       </c>
-      <c r="C46" s="15" t="inlineStr">
+      <c r="C47" s="16" t="inlineStr">
         <is>
           <t>30101810900000000822</t>
         </is>
       </c>
-      <c r="D46" s="16" t="n"/>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="B47" s="4" t="inlineStr">
+      <c r="D47" s="17" t="n"/>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>БИК</t>
         </is>
       </c>
-      <c r="C47" s="15" t="inlineStr">
+      <c r="C48" s="16" t="inlineStr">
         <is>
           <t>045209822</t>
         </is>
       </c>
-      <c r="D47" s="16" t="n"/>
-    </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="B48" s="4" t="inlineStr">
+      <c r="D48" s="17" t="n"/>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>ИНН/КПП банка</t>
         </is>
       </c>
-      <c r="C48" s="15" t="inlineStr">
+      <c r="C49" s="16" t="inlineStr">
         <is>
           <t>7725114488 / 550502001</t>
         </is>
       </c>
-      <c r="D48" s="16" t="n"/>
-    </row>
-    <row r="49" ht="18" customHeight="1">
-      <c r="B49" s="4" t="inlineStr">
+      <c r="D49" s="17" t="n"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>День срока оплаты</t>
         </is>
       </c>
-      <c r="C49" s="15" t="n">
+      <c r="C50" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>Единый срок по ч. 1 ст. 155 и ч. 2 ст. 171 ЖК РФ (ФЗ от 24.06.2025 № 177-ФЗ)</t>
         </is>
@@ -1613,15 +1622,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B24:G24"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B10:G10"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="B35:G36"/>
     <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B23:G23"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B36:G37"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B39:G39"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1638,198 +1647,198 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="0.8" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="0.8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="D1" s="79">
-        <f>"В "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$24</f>
+      <c r="D1" s="80">
+        <f>"В "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$25</f>
         <v/>
       </c>
-      <c r="E1" s="79" t="n"/>
-      <c r="F1" s="79" t="n"/>
+      <c r="E1" s="80" t="n"/>
+      <c r="F1" s="80" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="D2" s="79">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$26="","",'ИСХОДНЫЕ ДАННЫЕ'!$C$25&amp;" "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$26)</f>
+      <c r="D2" s="80">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$27="","",'ИСХОДНЫЕ ДАННЫЕ'!$C$26&amp;" "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$27)</f>
         <v/>
       </c>
-      <c r="E2" s="79" t="n"/>
-      <c r="F2" s="79" t="n"/>
+      <c r="E2" s="80" t="n"/>
+      <c r="F2" s="80" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="D3" s="80">
+      <c r="D3" s="81">
         <f>"от Председателя МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;", "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$18</f>
         <v/>
       </c>
-      <c r="E3" s="80" t="n"/>
-      <c r="F3" s="80" t="n"/>
+      <c r="E3" s="81" t="n"/>
+      <c r="F3" s="81" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="D4" s="80">
+      <c r="D4" s="81">
         <f>"проживающей по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$20</f>
         <v/>
       </c>
-      <c r="E4" s="80" t="n"/>
-      <c r="F4" s="80" t="n"/>
+      <c r="E4" s="81" t="n"/>
+      <c r="F4" s="81" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="D5" s="80">
+      <c r="D5" s="81">
         <f>"Конт. тел.: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21</f>
         <v/>
       </c>
-      <c r="E5" s="80" t="n"/>
-      <c r="F5" s="80" t="n"/>
+      <c r="E5" s="81" t="n"/>
+      <c r="F5" s="81" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="D6" s="80">
+      <c r="D6" s="81">
         <f>"Эл. почта: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22</f>
         <v/>
       </c>
-      <c r="E6" s="80" t="n"/>
-      <c r="F6" s="80" t="n"/>
+      <c r="E6" s="81" t="n"/>
+      <c r="F6" s="81" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1"/>
     <row r="8" ht="54" customHeight="1">
-      <c r="B8" s="80">
-        <f>"В связи с тем, что на балансе департамента числится кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", сообщаю Вам о необходимости оплатить "&amp;IF(INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2)*100,0)-INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))*100),"00")&amp;" руб., в том числе:"</f>
+      <c r="B8" s="81">
+        <f>"В связи с тем, что на балансе департамента числится кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", сообщаю Вам о необходимости оплатить "&amp;IF(INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$34,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$34,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$34,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$34,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$34,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$34,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$34,2),2)*100,0)-INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$34,2),2))*100),"00")&amp;" руб., в том числе:"</f>
         <v/>
       </c>
-      <c r="C8" s="80" t="n"/>
-      <c r="D8" s="80" t="n"/>
-      <c r="E8" s="80" t="n"/>
-      <c r="F8" s="80" t="n"/>
+      <c r="C8" s="81" t="n"/>
+      <c r="D8" s="81" t="n"/>
+      <c r="E8" s="81" t="n"/>
+      <c r="F8" s="81" t="n"/>
     </row>
     <row r="9" ht="8" customHeight="1"/>
     <row r="10" ht="38" customHeight="1">
-      <c r="B10" s="80">
+      <c r="B10" s="81">
         <f>"— текущий платёж за период с октября по декабрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года ("&amp;"IV квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;") в размере "&amp;IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100),"00")&amp;" рублей"</f>
         <v/>
       </c>
-      <c r="C10" s="80" t="n"/>
-      <c r="D10" s="80" t="n"/>
-      <c r="E10" s="80" t="n"/>
-      <c r="F10" s="80" t="n"/>
+      <c r="C10" s="81" t="n"/>
+      <c r="D10" s="81" t="n"/>
+      <c r="E10" s="81" t="n"/>
+      <c r="F10" s="81" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="81">
+      <c r="B11" s="82">
         <f>"("&amp;UPPER(LEFT(IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)=0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)=0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1),2,300)&amp;")."</f>
         <v/>
       </c>
-      <c r="C11" s="81" t="n"/>
-      <c r="D11" s="81" t="n"/>
-      <c r="E11" s="81" t="n"/>
-      <c r="F11" s="81" t="n"/>
+      <c r="C11" s="82" t="n"/>
+      <c r="D11" s="82" t="n"/>
+      <c r="E11" s="82" t="n"/>
+      <c r="F11" s="82" t="n"/>
     </row>
     <row r="12" ht="6" customHeight="1"/>
     <row r="13" ht="32" customHeight="1">
-      <c r="B13" s="80">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$33=0,"— задолженности за предыдущие периоды нет.","— задолженность "&amp;IF('ИСХОДНЫЕ ДАННЫЕ'!$D$33="","за предыдущие периоды",'ИСХОДНЫЕ ДАННЫЕ'!$D$33)&amp;" в размере "&amp;IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)&gt;0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)&amp;" "&amp;TEXT((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000),"000"),(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))*100),"00")&amp;" рублей")</f>
+      <c r="B13" s="81">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$34=0,"— задолженности за предыдущие периоды нет.","— задолженность "&amp;IF('ИСХОДНЫЕ ДАННЫЕ'!$D$34="","за предыдущие периоды",'ИСХОДНЫЕ ДАННЫЕ'!$D$34)&amp;" в размере "&amp;IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))/1000)&gt;0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))/1000)&amp;" "&amp;TEXT((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))/1000)*1000),"000"),(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))*100),"00")&amp;" рублей")</f>
         <v/>
       </c>
-      <c r="C13" s="80" t="n"/>
-      <c r="D13" s="80" t="n"/>
-      <c r="E13" s="80" t="n"/>
-      <c r="F13" s="80" t="n"/>
+      <c r="C13" s="81" t="n"/>
+      <c r="D13" s="81" t="n"/>
+      <c r="E13" s="81" t="n"/>
+      <c r="F13" s="81" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="81">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$33=0,"","("&amp;UPPER(LEFT(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))*100)+1),2,300)&amp;").")</f>
+      <c r="B14" s="82">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$34=0,"","("&amp;UPPER(LEFT(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$34,2))*100)+1),2,300)&amp;").")</f>
         <v/>
       </c>
-      <c r="C14" s="81" t="n"/>
-      <c r="D14" s="81" t="n"/>
-      <c r="E14" s="81" t="n"/>
-      <c r="F14" s="81" t="n"/>
+      <c r="C14" s="82" t="n"/>
+      <c r="D14" s="82" t="n"/>
+      <c r="E14" s="82" t="n"/>
+      <c r="F14" s="82" t="n"/>
     </row>
     <row r="15" ht="10" customHeight="1"/>
     <row r="16" ht="90" customHeight="1">
-      <c r="B16" s="80">
-        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$33)&amp;" и с учётом начислений по "&amp;"декабрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
+      <c r="B16" s="81">
+        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$34),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$34),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$34)&amp;" и с учётом начислений по "&amp;"декабрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
       </c>
-      <c r="C16" s="80" t="n"/>
-      <c r="D16" s="80" t="n"/>
-      <c r="E16" s="80" t="n"/>
-      <c r="F16" s="80" t="n"/>
+      <c r="C16" s="81" t="n"/>
+      <c r="D16" s="81" t="n"/>
+      <c r="E16" s="81" t="n"/>
+      <c r="F16" s="81" t="n"/>
     </row>
     <row r="17" ht="10" customHeight="1"/>
     <row r="18" ht="54" customHeight="1">
-      <c r="B18" s="80">
+      <c r="B18" s="81">
         <f>"В случае возникновения дополнительных вопросов прошу связаться со мной по электронной почте "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22&amp;" или по телефону "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
       </c>
-      <c r="C18" s="80" t="n"/>
-      <c r="D18" s="80" t="n"/>
-      <c r="E18" s="80" t="n"/>
-      <c r="F18" s="80" t="n"/>
+      <c r="C18" s="81" t="n"/>
+      <c r="D18" s="81" t="n"/>
+      <c r="E18" s="81" t="n"/>
+      <c r="F18" s="81" t="n"/>
     </row>
     <row r="19" ht="14" customHeight="1"/>
     <row r="20" ht="20" customHeight="1">
-      <c r="B20" s="79" t="inlineStr">
+      <c r="B20" s="80" t="inlineStr">
         <is>
           <t>ПРИЛОЖЕНИЯ:</t>
         </is>
       </c>
-      <c r="C20" s="79" t="n"/>
-      <c r="D20" s="79" t="n"/>
-      <c r="E20" s="79" t="n"/>
-      <c r="F20" s="79" t="n"/>
+      <c r="C20" s="80" t="n"/>
+      <c r="D20" s="80" t="n"/>
+      <c r="E20" s="80" t="n"/>
+      <c r="F20" s="80" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="80">
-        <f>"1) Акт взаимных расчётов по состоянию на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$33)&amp;" — один экземпляр на 1 л."</f>
+      <c r="B21" s="81">
+        <f>"1) Акт взаимных расчётов по состоянию на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$34),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$34),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$34)&amp;" — один экземпляр на 1 л."</f>
         <v/>
       </c>
-      <c r="C21" s="80" t="n"/>
-      <c r="D21" s="80" t="n"/>
-      <c r="E21" s="80" t="n"/>
-      <c r="F21" s="80" t="n"/>
+      <c r="C21" s="81" t="n"/>
+      <c r="D21" s="81" t="n"/>
+      <c r="E21" s="81" t="n"/>
+      <c r="F21" s="81" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="80">
+      <c r="B22" s="81">
         <f>"2) Квитанция для оплаты за "&amp;"IV квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — один экземпляр на 1 л."</f>
         <v/>
       </c>
-      <c r="C22" s="80" t="n"/>
-      <c r="D22" s="80" t="n"/>
-      <c r="E22" s="80" t="n"/>
-      <c r="F22" s="80" t="n"/>
+      <c r="C22" s="81" t="n"/>
+      <c r="D22" s="81" t="n"/>
+      <c r="E22" s="81" t="n"/>
+      <c r="F22" s="81" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1"/>
     <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="80">
+      <c r="B24" s="81">
         <f>"«______» ______________ "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="C24" s="80" t="n"/>
+      <c r="C24" s="81" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1"/>
     <row r="26" ht="16" customHeight="1">
-      <c r="B26" s="80" t="inlineStr">
+      <c r="B26" s="81" t="inlineStr">
         <is>
           <t>Председатель</t>
         </is>
       </c>
-      <c r="C26" s="80" t="n"/>
+      <c r="C26" s="81" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="B27" s="80">
+      <c r="B27" s="81">
         <f>"МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15</f>
         <v/>
       </c>
-      <c r="C27" s="80" t="n"/>
-      <c r="D27" s="82">
+      <c r="C27" s="81" t="n"/>
+      <c r="D27" s="83">
         <f>"___________________  /"&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$19&amp;"/"</f>
         <v/>
       </c>
-      <c r="E27" s="82" t="n"/>
-      <c r="F27" s="82" t="n"/>
+      <c r="E27" s="83" t="n"/>
+      <c r="F27" s="83" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -1854,7 +1863,7 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="D6:F6"/>
   </mergeCells>
-  <pageMargins left="0.79" right="0.39" top="0.59" bottom="0.59" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.39" top="0.51" bottom="0.51" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
@@ -1877,141 +1886,141 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="83" t="inlineStr">
+      <c r="A1" s="84" t="inlineStr">
         <is>
           <t>КВАРТАЛЬНЫЕ КВИТАНЦИИ И ПИСЬМА — КАК ПОЛЬЗОВАТЬСЯ</t>
         </is>
       </c>
     </row>
     <row r="2" ht="8" customHeight="1">
-      <c r="A2" s="84" t="inlineStr"/>
+      <c r="A2" s="85" t="inlineStr"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="85" t="inlineStr">
+      <c r="A3" s="86" t="inlineStr">
         <is>
           <t>1. Где вводить данные</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="86" t="inlineStr">
+      <c r="A4" s="87" t="inlineStr">
         <is>
           <t>Всё вводится на листе «ИСХОДНЫЕ ДАННЫЕ», в жёлтых ячейках. Остальные девять листов — расчётные: они читают эти значения формулами и пересчитываются сами.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="86" t="inlineStr">
+      <c r="A5" s="87" t="inlineStr">
         <is>
           <t>Ежегодно меняется только тариф (блок 1). Поменяли размер взноса и год — все четыре квитанции и все четыре письма обновились.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="86" t="inlineStr">
+      <c r="A6" s="87" t="inlineStr">
         <is>
           <t>Начисление за месяц по умолчанию считается как площадь × тариф. Если сумму нужно задать вручную, замените в ячейке формулу числом.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="8" customHeight="1">
-      <c r="A7" s="84" t="inlineStr"/>
+      <c r="A7" s="85" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="85" t="inlineStr">
+      <c r="A8" s="86" t="inlineStr">
         <is>
           <t>2. Задолженность по кварталам</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="86" t="inlineStr">
+      <c r="A9" s="87" t="inlineStr">
         <is>
           <t>Блок 5 листа «ИСХОДНЫЕ ДАННЫЕ» — таблица на четыре строки. Для каждого квартала укажите сумму задолженности, её описание (оно попадёт и в квитанцию, и в письмо) и дату формирования.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="86" t="inlineStr">
+      <c r="A10" s="87" t="inlineStr">
         <is>
           <t>Если задолженности нет, поставьте 0: в письме вместо строки о долге напечатается «задолженности за предыдущие периоды нет», а в квитанции строка останется с нулём.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="8" customHeight="1">
-      <c r="A11" s="84" t="inlineStr"/>
+      <c r="A11" s="85" t="inlineStr"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="85" t="inlineStr">
+      <c r="A12" s="86" t="inlineStr">
         <is>
           <t>3. Сопроводительное письмо</t>
         </is>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="86" t="inlineStr">
+      <c r="A13" s="87" t="inlineStr">
         <is>
           <t>Суммы, периоды, даты и приложения подтягиваются автоматически. Сумма прописью считается формулами по скрытому листу ПРОПИСЬ — макросы для этого не нужны, книга остаётся обычным .xlsx.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="86" t="inlineStr">
+      <c r="A14" s="87" t="inlineStr">
         <is>
           <t>Адресат письма — блок 4. Должность и ФИО руководителя правятся здесь; при смене директора достаточно поменять их один раз. Если ФИО оставить пустым, строка с ним не напечатается.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="8" customHeight="1">
-      <c r="A15" s="84" t="inlineStr"/>
+      <c r="A15" s="85" t="inlineStr"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="85" t="inlineStr">
+      <c r="A16" s="86" t="inlineStr">
         <is>
           <t>4. Печать</t>
         </is>
       </c>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="86" t="inlineStr">
+      <c r="A17" s="87" t="inlineStr">
         <is>
           <t>Каждый лист настроен на одну страницу А4. Квитанции — книжная ориентация, поля 6 мм; письма — стандартные поля 20/15 мм.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="86" t="inlineStr">
+      <c r="A18" s="87" t="inlineStr">
         <is>
           <t>Книга сохранена в чёрно-белом виде: заливок нет, акценты сделаны кеглем, полужирным и рамками. Цветной вариант для отправки по электронной почте лежит отдельным файлом.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="8" customHeight="1">
-      <c r="A19" s="84" t="inlineStr"/>
+      <c r="A19" s="85" t="inlineStr"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="85" t="inlineStr">
+      <c r="A20" s="86" t="inlineStr">
         <is>
           <t>5. Что проверить</t>
         </is>
       </c>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="86" t="inlineStr">
+      <c r="A21" s="87" t="inlineStr">
         <is>
           <t>• Тариф 15,30 руб./м² и площадь 52,8 м² взяты из вашего образца за I квартал 2026 года. Начисление выходит 807,84 руб. в месяц и 2 423,52 руб. за квартал — совпадает с образцом.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="86" t="inlineStr">
+      <c r="A22" s="87" t="inlineStr">
         <is>
           <t>• Задолженность 4 042,38 руб. проставлена только для I квартала. Для остальных кварталов стоят нули — заполните их по факту.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="86" t="inlineStr">
+      <c r="A23" s="87" t="inlineStr">
         <is>
           <t>• В образце письма период января–марта 2026 года был подписан как «I квартал 2025 г.» — в шаблоне это исправлено на 2026 год.</t>
         </is>
@@ -2058,32 +2067,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>Число</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>Прописью (муж.)</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="C1" s="18" t="inlineStr">
         <is>
           <t>Форма рубля</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
+      <c r="D1" s="18" t="inlineStr">
         <is>
           <t>Прописью (жен.)</t>
         </is>
       </c>
-      <c r="E1" s="17" t="inlineStr">
+      <c r="E1" s="18" t="inlineStr">
         <is>
           <t>Форма тысячи</t>
         </is>
       </c>
-      <c r="F1" s="17" t="inlineStr">
+      <c r="F1" s="18" t="inlineStr">
         <is>
           <t>Форма копейки</t>
         </is>
@@ -32116,7 +32125,7 @@
   <sheetData>
     <row r="1" ht="6" customHeight="1"/>
     <row r="2" ht="40" customHeight="1">
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32139,462 +32148,462 @@
           </r>
         </is>
       </c>
-      <c r="C2" s="18" t="n"/>
-      <c r="D2" s="18" t="n"/>
-      <c r="E2" s="18" t="n"/>
-      <c r="F2" s="18" t="n"/>
-      <c r="G2" s="18" t="n"/>
-      <c r="H2" s="18" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
+      <c r="H2" s="19" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="B3" s="19">
+      <c r="B3" s="20">
         <f>"Специальный счёт МКД · "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14</f>
         <v/>
       </c>
-      <c r="C3" s="20" t="n"/>
-      <c r="D3" s="20" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="21">
+      <c r="C3" s="21" t="n"/>
+      <c r="D3" s="21" t="n"/>
+      <c r="E3" s="21" t="n"/>
+      <c r="F3" s="22">
         <f>"Расчётный период: "&amp;"I квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G3" s="21" t="n"/>
-      <c r="H3" s="22" t="n"/>
+      <c r="G3" s="22" t="n"/>
+      <c r="H3" s="23" t="n"/>
     </row>
     <row r="4" ht="5" customHeight="1"/>
     <row r="5" ht="16" customHeight="1">
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>1. ПОЛУЧАТЕЛЬ ПЛАТЕЖА — ВЛАДЕЛЕЦ СПЕЦИАЛЬНОГО СЧЁТА</t>
         </is>
       </c>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="24" t="n"/>
-      <c r="G5" s="24" t="n"/>
-      <c r="H5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="26" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>Получатель платежа</t>
         </is>
       </c>
-      <c r="C6" s="27">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$39</f>
-        <v/>
-      </c>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="27" t="n"/>
-      <c r="G6" s="27" t="n"/>
-      <c r="H6" s="28" t="n"/>
-    </row>
-    <row r="7" ht="14" customHeight="1">
-      <c r="B7" s="29" t="inlineStr">
-        <is>
-          <t>Юридический адрес</t>
-        </is>
-      </c>
-      <c r="C7" s="30">
+      <c r="C6" s="28">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$40</f>
         <v/>
       </c>
-      <c r="D7" s="30" t="n"/>
-      <c r="E7" s="30" t="n"/>
-      <c r="F7" s="30" t="n"/>
-      <c r="G7" s="30" t="n"/>
-      <c r="H7" s="31" t="n"/>
+      <c r="D6" s="28" t="n"/>
+      <c r="E6" s="28" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
+      <c r="H6" s="29" t="n"/>
+    </row>
+    <row r="7" ht="14" customHeight="1">
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Юридический адрес</t>
+        </is>
+      </c>
+      <c r="C7" s="31">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$41</f>
+        <v/>
+      </c>
+      <c r="D7" s="31" t="n"/>
+      <c r="E7" s="31" t="n"/>
+      <c r="F7" s="31" t="n"/>
+      <c r="G7" s="31" t="n"/>
+      <c r="H7" s="32" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>ИНН / КПП</t>
         </is>
       </c>
-      <c r="C8" s="30">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$41&amp;" / "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$42</f>
+      <c r="C8" s="31">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$42&amp;" / "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$43</f>
         <v/>
       </c>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="32" t="inlineStr">
+      <c r="D8" s="31" t="n"/>
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>ОГРН</t>
         </is>
       </c>
-      <c r="F8" s="30">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$43</f>
+      <c r="F8" s="31">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$44</f>
         <v/>
       </c>
-      <c r="G8" s="30" t="n"/>
-      <c r="H8" s="31" t="n"/>
+      <c r="G8" s="31" t="n"/>
+      <c r="H8" s="32" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Расчётный счёт</t>
         </is>
       </c>
-      <c r="C9" s="33">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;"   (специальный счёт МКД: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;")"</f>
+      <c r="C9" s="34">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (специальный счёт МКД: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;")"</f>
         <v/>
       </c>
-      <c r="D9" s="33" t="n"/>
-      <c r="E9" s="33" t="n"/>
-      <c r="F9" s="33" t="n"/>
-      <c r="G9" s="33" t="n"/>
-      <c r="H9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="35" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
       </c>
-      <c r="C10" s="30">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45</f>
+      <c r="C10" s="31">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$46</f>
         <v/>
       </c>
-      <c r="D10" s="30" t="n"/>
-      <c r="E10" s="30" t="n"/>
-      <c r="F10" s="30" t="n"/>
-      <c r="G10" s="30" t="n"/>
-      <c r="H10" s="31" t="n"/>
+      <c r="D10" s="31" t="n"/>
+      <c r="E10" s="31" t="n"/>
+      <c r="F10" s="31" t="n"/>
+      <c r="G10" s="31" t="n"/>
+      <c r="H10" s="32" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>Корр. счёт / БИК</t>
         </is>
       </c>
-      <c r="C11" s="36">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$46&amp;" / "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$47</f>
+      <c r="C11" s="37">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$47&amp;" / "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$48</f>
         <v/>
       </c>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="37" t="inlineStr">
+      <c r="D11" s="37" t="n"/>
+      <c r="E11" s="38" t="inlineStr">
         <is>
           <t>ИНН/КПП банка</t>
         </is>
       </c>
-      <c r="F11" s="36">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$48</f>
+      <c r="F11" s="37">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$49</f>
         <v/>
       </c>
-      <c r="G11" s="36" t="n"/>
-      <c r="H11" s="38" t="n"/>
+      <c r="G11" s="37" t="n"/>
+      <c r="H11" s="39" t="n"/>
     </row>
     <row r="12" ht="5" customHeight="1"/>
     <row r="13" ht="16" customHeight="1">
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>2. ПЛАТЕЛЬЩИК И ПОМЕЩЕНИЕ</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
-      <c r="D13" s="24" t="n"/>
-      <c r="E13" s="24" t="n"/>
-      <c r="F13" s="24" t="n"/>
-      <c r="G13" s="24" t="n"/>
-      <c r="H13" s="25" t="n"/>
+      <c r="C13" s="25" t="n"/>
+      <c r="D13" s="25" t="n"/>
+      <c r="E13" s="25" t="n"/>
+      <c r="F13" s="25" t="n"/>
+      <c r="G13" s="25" t="n"/>
+      <c r="H13" s="26" t="n"/>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>Лицевой счёт</t>
         </is>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="40">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$11</f>
         <v/>
       </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>Квартира №</t>
         </is>
       </c>
-      <c r="E14" s="40">
+      <c r="E14" s="41">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$12</f>
         <v/>
       </c>
-      <c r="F14" s="41" t="inlineStr">
+      <c r="F14" s="42" t="inlineStr">
         <is>
           <t>Дата формирования</t>
         </is>
       </c>
-      <c r="G14" s="42">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$E$30</f>
+      <c r="G14" s="43">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$E$31</f>
         <v/>
       </c>
-      <c r="H14" s="43" t="n"/>
+      <c r="H14" s="44" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="B15" s="29" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Плательщик</t>
         </is>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="34">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$13</f>
         <v/>
       </c>
-      <c r="D15" s="33" t="n"/>
-      <c r="E15" s="33" t="n"/>
-      <c r="F15" s="33" t="n"/>
-      <c r="G15" s="33" t="n"/>
-      <c r="H15" s="34" t="n"/>
+      <c r="D15" s="34" t="n"/>
+      <c r="E15" s="34" t="n"/>
+      <c r="F15" s="34" t="n"/>
+      <c r="G15" s="34" t="n"/>
+      <c r="H15" s="35" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>Адрес помещения</t>
         </is>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", кв. "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12</f>
         <v/>
       </c>
-      <c r="D16" s="30" t="n"/>
-      <c r="E16" s="30" t="n"/>
-      <c r="F16" s="30" t="n"/>
-      <c r="G16" s="30" t="n"/>
-      <c r="H16" s="31" t="n"/>
+      <c r="D16" s="31" t="n"/>
+      <c r="E16" s="31" t="n"/>
+      <c r="F16" s="31" t="n"/>
+      <c r="G16" s="31" t="n"/>
+      <c r="H16" s="32" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="B17" s="44" t="inlineStr">
+      <c r="B17" s="45" t="inlineStr">
         <is>
           <t>Площадь помещения, м²</t>
         </is>
       </c>
-      <c r="C17" s="45">
+      <c r="C17" s="46">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$6</f>
         <v/>
       </c>
-      <c r="D17" s="46" t="inlineStr">
+      <c r="D17" s="47" t="inlineStr">
         <is>
           <t>Размер взноса, руб./м²</t>
         </is>
       </c>
-      <c r="E17" s="47">
+      <c r="E17" s="48">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$7</f>
         <v/>
       </c>
-      <c r="F17" s="37" t="inlineStr">
+      <c r="F17" s="38" t="inlineStr">
         <is>
           <t>Период оплаты</t>
         </is>
       </c>
-      <c r="G17" s="48">
+      <c r="G17" s="49">
         <f>"I квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="H17" s="49" t="n"/>
+      <c r="H17" s="50" t="n"/>
     </row>
     <row r="18" ht="5" customHeight="1"/>
     <row r="19" ht="16" customHeight="1">
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>3. РАСЧЁТ РАЗМЕРА ВЗНОСА И СУММЫ К ОПЛАТЕ</t>
         </is>
       </c>
-      <c r="C19" s="24" t="n"/>
-      <c r="D19" s="24" t="n"/>
-      <c r="E19" s="24" t="n"/>
-      <c r="F19" s="24" t="n"/>
-      <c r="G19" s="24" t="n"/>
-      <c r="H19" s="25" t="n"/>
+      <c r="C19" s="25" t="n"/>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="25" t="n"/>
+      <c r="G19" s="25" t="n"/>
+      <c r="H19" s="26" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="50" t="inlineStr">
+      <c r="B20" s="51" t="inlineStr">
         <is>
           <t>Вид платежа</t>
         </is>
       </c>
-      <c r="C20" s="51" t="n"/>
-      <c r="D20" s="51" t="n"/>
-      <c r="E20" s="51" t="n"/>
-      <c r="F20" s="51" t="inlineStr">
+      <c r="C20" s="52" t="n"/>
+      <c r="D20" s="52" t="n"/>
+      <c r="E20" s="52" t="n"/>
+      <c r="F20" s="52" t="inlineStr">
         <is>
           <t>Расчётный период</t>
         </is>
       </c>
-      <c r="G20" s="51" t="n"/>
-      <c r="H20" s="52" t="inlineStr">
+      <c r="G20" s="52" t="n"/>
+      <c r="H20" s="53" t="inlineStr">
         <is>
           <t>Сумма, руб.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="B21" s="53" t="inlineStr">
+      <c r="B21" s="54" t="inlineStr">
         <is>
           <t>Взнос на капитальный ремонт (площадь × размер взноса)</t>
         </is>
       </c>
-      <c r="C21" s="30" t="n"/>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="30" t="n"/>
-      <c r="F21" s="54">
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+      <c r="E21" s="31" t="n"/>
+      <c r="F21" s="55">
         <f>"январь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G21" s="54" t="n"/>
-      <c r="H21" s="55">
+      <c r="G21" s="55" t="n"/>
+      <c r="H21" s="56">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$8</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="53" t="inlineStr">
+      <c r="B22" s="54" t="inlineStr">
         <is>
           <t>Взнос на капитальный ремонт (площадь × размер взноса)</t>
         </is>
       </c>
-      <c r="C22" s="30" t="n"/>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="30" t="n"/>
-      <c r="F22" s="54">
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+      <c r="E22" s="31" t="n"/>
+      <c r="F22" s="55">
         <f>"февраль "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G22" s="54" t="n"/>
-      <c r="H22" s="55">
+      <c r="G22" s="55" t="n"/>
+      <c r="H22" s="56">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$8</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="53" t="inlineStr">
+      <c r="B23" s="54" t="inlineStr">
         <is>
           <t>Взнос на капитальный ремонт (площадь × размер взноса)</t>
         </is>
       </c>
-      <c r="C23" s="30" t="n"/>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="30" t="n"/>
-      <c r="F23" s="54">
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+      <c r="E23" s="31" t="n"/>
+      <c r="F23" s="55">
         <f>"март "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G23" s="54" t="n"/>
-      <c r="H23" s="55">
+      <c r="G23" s="55" t="n"/>
+      <c r="H23" s="56">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$8</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="B24" s="56" t="inlineStr">
+      <c r="B24" s="57" t="inlineStr">
         <is>
           <t>Итого начислено за квартал</t>
         </is>
       </c>
-      <c r="C24" s="57" t="n"/>
-      <c r="D24" s="57" t="n"/>
-      <c r="E24" s="57" t="n"/>
-      <c r="F24" s="58">
+      <c r="C24" s="58" t="n"/>
+      <c r="D24" s="58" t="n"/>
+      <c r="E24" s="58" t="n"/>
+      <c r="F24" s="59">
         <f>"I квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G24" s="58" t="n"/>
-      <c r="H24" s="59">
+      <c r="G24" s="59" t="n"/>
+      <c r="H24" s="60">
         <f>ROUND(SUM(H21:H23),2)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="B25" s="53" t="inlineStr">
+      <c r="B25" s="54" t="inlineStr">
         <is>
           <t>Задолженность за предыдущие периоды</t>
         </is>
       </c>
-      <c r="C25" s="30" t="n"/>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="30" t="n"/>
-      <c r="F25" s="60">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$D$30="","",'ИСХОДНЫЕ ДАННЫЕ'!$D$30)</f>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+      <c r="E25" s="31" t="n"/>
+      <c r="F25" s="61">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$D$31="","",'ИСХОДНЫЕ ДАННЫЕ'!$D$31)</f>
         <v/>
       </c>
-      <c r="G25" s="60" t="n"/>
-      <c r="H25" s="55">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$30</f>
+      <c r="G25" s="61" t="n"/>
+      <c r="H25" s="56">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$31</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="B26" s="61" t="inlineStr">
+      <c r="B26" s="62" t="inlineStr">
         <is>
           <t>ИТОГО К ОПЛАТЕ</t>
         </is>
       </c>
-      <c r="C26" s="62" t="n"/>
-      <c r="D26" s="62" t="n"/>
-      <c r="E26" s="62" t="n"/>
-      <c r="F26" s="62" t="n"/>
-      <c r="G26" s="62" t="n"/>
-      <c r="H26" s="63">
+      <c r="C26" s="63" t="n"/>
+      <c r="D26" s="63" t="n"/>
+      <c r="E26" s="63" t="n"/>
+      <c r="F26" s="63" t="n"/>
+      <c r="G26" s="63" t="n"/>
+      <c r="H26" s="64">
         <f>ROUND(H24+H25,2)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="5" customHeight="1"/>
     <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>4. СПРАВОЧНАЯ ИНФОРМАЦИЯ ПО СПЕЦИАЛЬНОМУ СЧЁТУ (ч. 7 ст. 177 ЖК РФ)</t>
         </is>
       </c>
-      <c r="C28" s="24" t="n"/>
-      <c r="D28" s="24" t="n"/>
-      <c r="E28" s="24" t="n"/>
-      <c r="F28" s="24" t="n"/>
-      <c r="G28" s="24" t="n"/>
-      <c r="H28" s="25" t="n"/>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="25" t="n"/>
+      <c r="G28" s="25" t="n"/>
+      <c r="H28" s="26" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="64">
+      <c r="B29" s="65">
         <f>"Поступило оплат по лицевому счёту с начала "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года, руб."</f>
         <v/>
       </c>
-      <c r="C29" s="36" t="n"/>
-      <c r="D29" s="36" t="n"/>
-      <c r="E29" s="36" t="n"/>
-      <c r="F29" s="36" t="n"/>
-      <c r="G29" s="65">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$F$30="","—",'ИСХОДНЫЕ ДАННЫЕ'!$F$30)</f>
+      <c r="C29" s="37" t="n"/>
+      <c r="D29" s="37" t="n"/>
+      <c r="E29" s="37" t="n"/>
+      <c r="F29" s="37" t="n"/>
+      <c r="G29" s="66">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$F$31="","—",'ИСХОДНЫЕ ДАННЫЕ'!$F$31)</f>
         <v/>
       </c>
-      <c r="H29" s="66" t="n"/>
+      <c r="H29" s="67" t="n"/>
     </row>
     <row r="30" ht="5" customHeight="1"/>
     <row r="31" ht="16" customHeight="1">
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>5. ПОРЯДОК ОПЛАТЫ</t>
         </is>
       </c>
-      <c r="C31" s="24" t="n"/>
-      <c r="D31" s="24" t="n"/>
-      <c r="E31" s="24" t="n"/>
-      <c r="F31" s="24" t="n"/>
-      <c r="G31" s="24" t="n"/>
-      <c r="H31" s="25" t="n"/>
+      <c r="C31" s="25" t="n"/>
+      <c r="D31" s="25" t="n"/>
+      <c r="E31" s="25" t="n"/>
+      <c r="F31" s="25" t="n"/>
+      <c r="G31" s="25" t="n"/>
+      <c r="H31" s="26" t="n"/>
     </row>
     <row r="32" ht="14" customHeight="1">
-      <c r="B32" s="67" t="inlineStr">
+      <c r="B32" s="68" t="inlineStr">
         <is>
           <t>1) без комиссии — в отделениях АО «Россельхозбанк» (банк, в котором открыт специальный счёт дома);</t>
         </is>
       </c>
-      <c r="C32" s="68" t="n"/>
-      <c r="D32" s="68" t="n"/>
-      <c r="E32" s="68" t="n"/>
-      <c r="F32" s="68" t="n"/>
-      <c r="G32" s="69" t="n"/>
-      <c r="H32" s="70" t="n"/>
+      <c r="C32" s="69" t="n"/>
+      <c r="D32" s="69" t="n"/>
+      <c r="E32" s="69" t="n"/>
+      <c r="F32" s="69" t="n"/>
+      <c r="G32" s="70" t="n"/>
+      <c r="H32" s="71" t="n"/>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="B33" s="67" t="inlineStr">
+      <c r="B33" s="68" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32623,117 +32632,117 @@
           </r>
         </is>
       </c>
-      <c r="C33" s="68" t="n"/>
-      <c r="D33" s="68" t="n"/>
-      <c r="E33" s="68" t="n"/>
-      <c r="F33" s="68" t="n"/>
-      <c r="G33" s="69" t="n"/>
-      <c r="H33" s="70" t="n"/>
+      <c r="C33" s="69" t="n"/>
+      <c r="D33" s="69" t="n"/>
+      <c r="E33" s="69" t="n"/>
+      <c r="F33" s="69" t="n"/>
+      <c r="G33" s="70" t="n"/>
+      <c r="H33" s="71" t="n"/>
     </row>
     <row r="34" ht="14" customHeight="1">
-      <c r="B34" s="67" t="n"/>
-      <c r="C34" s="68" t="n"/>
-      <c r="D34" s="68" t="n"/>
-      <c r="E34" s="68" t="n"/>
-      <c r="F34" s="68" t="n"/>
-      <c r="G34" s="69" t="n"/>
-      <c r="H34" s="70" t="n"/>
+      <c r="B34" s="68" t="n"/>
+      <c r="C34" s="69" t="n"/>
+      <c r="D34" s="69" t="n"/>
+      <c r="E34" s="69" t="n"/>
+      <c r="F34" s="69" t="n"/>
+      <c r="G34" s="70" t="n"/>
+      <c r="H34" s="71" t="n"/>
     </row>
     <row r="35" ht="14" customHeight="1">
-      <c r="B35" s="29" t="inlineStr">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>Назначение платежа:</t>
         </is>
       </c>
-      <c r="C35" s="32" t="n"/>
-      <c r="D35" s="32" t="n"/>
-      <c r="E35" s="32" t="n"/>
-      <c r="F35" s="32" t="n"/>
-      <c r="G35" s="69" t="n"/>
-      <c r="H35" s="70" t="n"/>
+      <c r="C35" s="33" t="n"/>
+      <c r="D35" s="33" t="n"/>
+      <c r="E35" s="33" t="n"/>
+      <c r="F35" s="33" t="n"/>
+      <c r="G35" s="70" t="n"/>
+      <c r="H35" s="71" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="B36" s="67">
+      <c r="B36" s="68">
         <f>"Взнос на капитальный ремонт, л/с № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;", кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;", за "&amp;"I квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="C36" s="68" t="n"/>
-      <c r="D36" s="68" t="n"/>
-      <c r="E36" s="68" t="n"/>
-      <c r="F36" s="68" t="n"/>
-      <c r="G36" s="69" t="n"/>
-      <c r="H36" s="70" t="n"/>
+      <c r="C36" s="69" t="n"/>
+      <c r="D36" s="69" t="n"/>
+      <c r="E36" s="69" t="n"/>
+      <c r="F36" s="69" t="n"/>
+      <c r="G36" s="70" t="n"/>
+      <c r="H36" s="71" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="B37" s="71">
-        <f>"Срок оплаты: до "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$49&amp;" числа месяца, следующего за расчётным (за "&amp;"I квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — до "&amp;TEXT(DAY(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,3+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49)),"00")&amp;"."&amp;TEXT(MONTH(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,3+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49)),"00")&amp;"."&amp;YEAR(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,3+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49))&amp;")."&amp;CHAR(10)&amp;"Основание: ч. 1 ст. 155, ч. 2 ст. 171 ЖК РФ."</f>
+      <c r="B37" s="72">
+        <f>"Срок оплаты: до "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$50&amp;" числа месяца, следующего за расчётным (за "&amp;"I квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — до "&amp;TEXT(DAY(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,3+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$50)),"00")&amp;"."&amp;TEXT(MONTH(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,3+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$50)),"00")&amp;"."&amp;YEAR(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,3+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$50))&amp;")."&amp;CHAR(10)&amp;"Основание: ч. 1 ст. 155, ч. 2 ст. 171 ЖК РФ."</f>
         <v/>
       </c>
-      <c r="C37" s="72" t="n"/>
-      <c r="D37" s="72" t="n"/>
-      <c r="E37" s="72" t="n"/>
-      <c r="F37" s="72" t="n"/>
-      <c r="G37" s="73" t="n"/>
-      <c r="H37" s="74" t="n"/>
+      <c r="C37" s="73" t="n"/>
+      <c r="D37" s="73" t="n"/>
+      <c r="E37" s="73" t="n"/>
+      <c r="F37" s="73" t="n"/>
+      <c r="G37" s="74" t="n"/>
+      <c r="H37" s="75" t="n"/>
     </row>
     <row r="38" ht="5" customHeight="1"/>
     <row r="39" ht="32" customHeight="1">
-      <c r="B39" s="75">
-        <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
+      <c r="B39" s="76">
+        <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
         <v/>
       </c>
-      <c r="C39" s="75" t="n"/>
-      <c r="D39" s="75" t="n"/>
-      <c r="E39" s="75" t="n"/>
-      <c r="F39" s="75" t="n"/>
-      <c r="G39" s="75" t="n"/>
-      <c r="H39" s="75" t="n"/>
+      <c r="C39" s="76" t="n"/>
+      <c r="D39" s="76" t="n"/>
+      <c r="E39" s="76" t="n"/>
+      <c r="F39" s="76" t="n"/>
+      <c r="G39" s="76" t="n"/>
+      <c r="H39" s="76" t="n"/>
     </row>
     <row r="40" ht="44" customHeight="1">
-      <c r="B40" s="76">
+      <c r="B40" s="77">
         <f>"В отделении банка и в мобильном приложении во вкладках ищите "&amp;"«РФКР МКД_капремонт, оплата по расчётному счёту» и указывайте номер расчётного счёта, приведённый выше. Оплата через общий поиск «Капитальный ремонт» уходит на общий счёт Регионального фонда капитального ремонта и на счёт вашего дома не поступает."&amp;CHAR(10)&amp;"Лицевой счёт № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;" при оплате НЕ вводится — он указан справочно, только для учёта начислений."</f>
         <v/>
       </c>
-      <c r="C40" s="76" t="n"/>
-      <c r="D40" s="76" t="n"/>
-      <c r="E40" s="76" t="n"/>
-      <c r="F40" s="76" t="n"/>
-      <c r="G40" s="76" t="n"/>
-      <c r="H40" s="76" t="n"/>
+      <c r="C40" s="77" t="n"/>
+      <c r="D40" s="77" t="n"/>
+      <c r="E40" s="77" t="n"/>
+      <c r="F40" s="77" t="n"/>
+      <c r="G40" s="77" t="n"/>
+      <c r="H40" s="77" t="n"/>
     </row>
     <row r="41" ht="6" customHeight="1"/>
     <row r="42" ht="24" customHeight="1">
-      <c r="B42" s="77" t="inlineStr">
+      <c r="B42" s="78" t="inlineStr">
         <is>
           <t>Подпись плательщика  ______________________</t>
         </is>
       </c>
-      <c r="C42" s="77" t="n"/>
-      <c r="D42" s="77" t="n"/>
-      <c r="E42" s="77" t="inlineStr">
+      <c r="C42" s="78" t="n"/>
+      <c r="D42" s="78" t="n"/>
+      <c r="E42" s="78" t="inlineStr">
         <is>
           <t>Кассир  ______________</t>
         </is>
       </c>
-      <c r="F42" s="77" t="n"/>
-      <c r="G42" s="77" t="inlineStr">
+      <c r="F42" s="78" t="n"/>
+      <c r="G42" s="78" t="inlineStr">
         <is>
           <t>Дата  ____________</t>
         </is>
       </c>
-      <c r="H42" s="77" t="n"/>
+      <c r="H42" s="78" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="B43" s="78">
+      <c r="B43" s="79">
         <f>"Начисление за "&amp;"I квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;"    По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
       </c>
-      <c r="C43" s="78" t="n"/>
-      <c r="D43" s="78" t="n"/>
-      <c r="E43" s="78" t="n"/>
-      <c r="F43" s="78" t="n"/>
-      <c r="G43" s="78" t="n"/>
-      <c r="H43" s="78" t="n"/>
+      <c r="C43" s="79" t="n"/>
+      <c r="D43" s="79" t="n"/>
+      <c r="E43" s="79" t="n"/>
+      <c r="F43" s="79" t="n"/>
+      <c r="G43" s="79" t="n"/>
+      <c r="H43" s="79" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="48">
@@ -32814,7 +32823,7 @@
   <sheetData>
     <row r="1" ht="6" customHeight="1"/>
     <row r="2" ht="40" customHeight="1">
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32837,462 +32846,462 @@
           </r>
         </is>
       </c>
-      <c r="C2" s="18" t="n"/>
-      <c r="D2" s="18" t="n"/>
-      <c r="E2" s="18" t="n"/>
-      <c r="F2" s="18" t="n"/>
-      <c r="G2" s="18" t="n"/>
-      <c r="H2" s="18" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
+      <c r="H2" s="19" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="B3" s="19">
+      <c r="B3" s="20">
         <f>"Специальный счёт МКД · "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14</f>
         <v/>
       </c>
-      <c r="C3" s="20" t="n"/>
-      <c r="D3" s="20" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="21">
+      <c r="C3" s="21" t="n"/>
+      <c r="D3" s="21" t="n"/>
+      <c r="E3" s="21" t="n"/>
+      <c r="F3" s="22">
         <f>"Расчётный период: "&amp;"II квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G3" s="21" t="n"/>
-      <c r="H3" s="22" t="n"/>
+      <c r="G3" s="22" t="n"/>
+      <c r="H3" s="23" t="n"/>
     </row>
     <row r="4" ht="5" customHeight="1"/>
     <row r="5" ht="16" customHeight="1">
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>1. ПОЛУЧАТЕЛЬ ПЛАТЕЖА — ВЛАДЕЛЕЦ СПЕЦИАЛЬНОГО СЧЁТА</t>
         </is>
       </c>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="24" t="n"/>
-      <c r="G5" s="24" t="n"/>
-      <c r="H5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="26" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>Получатель платежа</t>
         </is>
       </c>
-      <c r="C6" s="27">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$39</f>
-        <v/>
-      </c>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="27" t="n"/>
-      <c r="G6" s="27" t="n"/>
-      <c r="H6" s="28" t="n"/>
-    </row>
-    <row r="7" ht="14" customHeight="1">
-      <c r="B7" s="29" t="inlineStr">
-        <is>
-          <t>Юридический адрес</t>
-        </is>
-      </c>
-      <c r="C7" s="30">
+      <c r="C6" s="28">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$40</f>
         <v/>
       </c>
-      <c r="D7" s="30" t="n"/>
-      <c r="E7" s="30" t="n"/>
-      <c r="F7" s="30" t="n"/>
-      <c r="G7" s="30" t="n"/>
-      <c r="H7" s="31" t="n"/>
+      <c r="D6" s="28" t="n"/>
+      <c r="E6" s="28" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
+      <c r="H6" s="29" t="n"/>
+    </row>
+    <row r="7" ht="14" customHeight="1">
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Юридический адрес</t>
+        </is>
+      </c>
+      <c r="C7" s="31">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$41</f>
+        <v/>
+      </c>
+      <c r="D7" s="31" t="n"/>
+      <c r="E7" s="31" t="n"/>
+      <c r="F7" s="31" t="n"/>
+      <c r="G7" s="31" t="n"/>
+      <c r="H7" s="32" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>ИНН / КПП</t>
         </is>
       </c>
-      <c r="C8" s="30">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$41&amp;" / "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$42</f>
+      <c r="C8" s="31">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$42&amp;" / "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$43</f>
         <v/>
       </c>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="32" t="inlineStr">
+      <c r="D8" s="31" t="n"/>
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>ОГРН</t>
         </is>
       </c>
-      <c r="F8" s="30">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$43</f>
+      <c r="F8" s="31">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$44</f>
         <v/>
       </c>
-      <c r="G8" s="30" t="n"/>
-      <c r="H8" s="31" t="n"/>
+      <c r="G8" s="31" t="n"/>
+      <c r="H8" s="32" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Расчётный счёт</t>
         </is>
       </c>
-      <c r="C9" s="33">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;"   (специальный счёт МКД: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;")"</f>
+      <c r="C9" s="34">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (специальный счёт МКД: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;")"</f>
         <v/>
       </c>
-      <c r="D9" s="33" t="n"/>
-      <c r="E9" s="33" t="n"/>
-      <c r="F9" s="33" t="n"/>
-      <c r="G9" s="33" t="n"/>
-      <c r="H9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="35" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
       </c>
-      <c r="C10" s="30">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45</f>
+      <c r="C10" s="31">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$46</f>
         <v/>
       </c>
-      <c r="D10" s="30" t="n"/>
-      <c r="E10" s="30" t="n"/>
-      <c r="F10" s="30" t="n"/>
-      <c r="G10" s="30" t="n"/>
-      <c r="H10" s="31" t="n"/>
+      <c r="D10" s="31" t="n"/>
+      <c r="E10" s="31" t="n"/>
+      <c r="F10" s="31" t="n"/>
+      <c r="G10" s="31" t="n"/>
+      <c r="H10" s="32" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>Корр. счёт / БИК</t>
         </is>
       </c>
-      <c r="C11" s="36">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$46&amp;" / "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$47</f>
+      <c r="C11" s="37">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$47&amp;" / "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$48</f>
         <v/>
       </c>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="37" t="inlineStr">
+      <c r="D11" s="37" t="n"/>
+      <c r="E11" s="38" t="inlineStr">
         <is>
           <t>ИНН/КПП банка</t>
         </is>
       </c>
-      <c r="F11" s="36">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$48</f>
+      <c r="F11" s="37">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$49</f>
         <v/>
       </c>
-      <c r="G11" s="36" t="n"/>
-      <c r="H11" s="38" t="n"/>
+      <c r="G11" s="37" t="n"/>
+      <c r="H11" s="39" t="n"/>
     </row>
     <row r="12" ht="5" customHeight="1"/>
     <row r="13" ht="16" customHeight="1">
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>2. ПЛАТЕЛЬЩИК И ПОМЕЩЕНИЕ</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
-      <c r="D13" s="24" t="n"/>
-      <c r="E13" s="24" t="n"/>
-      <c r="F13" s="24" t="n"/>
-      <c r="G13" s="24" t="n"/>
-      <c r="H13" s="25" t="n"/>
+      <c r="C13" s="25" t="n"/>
+      <c r="D13" s="25" t="n"/>
+      <c r="E13" s="25" t="n"/>
+      <c r="F13" s="25" t="n"/>
+      <c r="G13" s="25" t="n"/>
+      <c r="H13" s="26" t="n"/>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>Лицевой счёт</t>
         </is>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="40">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$11</f>
         <v/>
       </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>Квартира №</t>
         </is>
       </c>
-      <c r="E14" s="40">
+      <c r="E14" s="41">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$12</f>
         <v/>
       </c>
-      <c r="F14" s="41" t="inlineStr">
+      <c r="F14" s="42" t="inlineStr">
         <is>
           <t>Дата формирования</t>
         </is>
       </c>
-      <c r="G14" s="42">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$E$31</f>
+      <c r="G14" s="43">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$E$32</f>
         <v/>
       </c>
-      <c r="H14" s="43" t="n"/>
+      <c r="H14" s="44" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="B15" s="29" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Плательщик</t>
         </is>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="34">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$13</f>
         <v/>
       </c>
-      <c r="D15" s="33" t="n"/>
-      <c r="E15" s="33" t="n"/>
-      <c r="F15" s="33" t="n"/>
-      <c r="G15" s="33" t="n"/>
-      <c r="H15" s="34" t="n"/>
+      <c r="D15" s="34" t="n"/>
+      <c r="E15" s="34" t="n"/>
+      <c r="F15" s="34" t="n"/>
+      <c r="G15" s="34" t="n"/>
+      <c r="H15" s="35" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>Адрес помещения</t>
         </is>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", кв. "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12</f>
         <v/>
       </c>
-      <c r="D16" s="30" t="n"/>
-      <c r="E16" s="30" t="n"/>
-      <c r="F16" s="30" t="n"/>
-      <c r="G16" s="30" t="n"/>
-      <c r="H16" s="31" t="n"/>
+      <c r="D16" s="31" t="n"/>
+      <c r="E16" s="31" t="n"/>
+      <c r="F16" s="31" t="n"/>
+      <c r="G16" s="31" t="n"/>
+      <c r="H16" s="32" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="B17" s="44" t="inlineStr">
+      <c r="B17" s="45" t="inlineStr">
         <is>
           <t>Площадь помещения, м²</t>
         </is>
       </c>
-      <c r="C17" s="45">
+      <c r="C17" s="46">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$6</f>
         <v/>
       </c>
-      <c r="D17" s="46" t="inlineStr">
+      <c r="D17" s="47" t="inlineStr">
         <is>
           <t>Размер взноса, руб./м²</t>
         </is>
       </c>
-      <c r="E17" s="47">
+      <c r="E17" s="48">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$7</f>
         <v/>
       </c>
-      <c r="F17" s="37" t="inlineStr">
+      <c r="F17" s="38" t="inlineStr">
         <is>
           <t>Период оплаты</t>
         </is>
       </c>
-      <c r="G17" s="48">
+      <c r="G17" s="49">
         <f>"II квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="H17" s="49" t="n"/>
+      <c r="H17" s="50" t="n"/>
     </row>
     <row r="18" ht="5" customHeight="1"/>
     <row r="19" ht="16" customHeight="1">
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>3. РАСЧЁТ РАЗМЕРА ВЗНОСА И СУММЫ К ОПЛАТЕ</t>
         </is>
       </c>
-      <c r="C19" s="24" t="n"/>
-      <c r="D19" s="24" t="n"/>
-      <c r="E19" s="24" t="n"/>
-      <c r="F19" s="24" t="n"/>
-      <c r="G19" s="24" t="n"/>
-      <c r="H19" s="25" t="n"/>
+      <c r="C19" s="25" t="n"/>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="25" t="n"/>
+      <c r="G19" s="25" t="n"/>
+      <c r="H19" s="26" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="50" t="inlineStr">
+      <c r="B20" s="51" t="inlineStr">
         <is>
           <t>Вид платежа</t>
         </is>
       </c>
-      <c r="C20" s="51" t="n"/>
-      <c r="D20" s="51" t="n"/>
-      <c r="E20" s="51" t="n"/>
-      <c r="F20" s="51" t="inlineStr">
+      <c r="C20" s="52" t="n"/>
+      <c r="D20" s="52" t="n"/>
+      <c r="E20" s="52" t="n"/>
+      <c r="F20" s="52" t="inlineStr">
         <is>
           <t>Расчётный период</t>
         </is>
       </c>
-      <c r="G20" s="51" t="n"/>
-      <c r="H20" s="52" t="inlineStr">
+      <c r="G20" s="52" t="n"/>
+      <c r="H20" s="53" t="inlineStr">
         <is>
           <t>Сумма, руб.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="B21" s="53" t="inlineStr">
+      <c r="B21" s="54" t="inlineStr">
         <is>
           <t>Взнос на капитальный ремонт (площадь × размер взноса)</t>
         </is>
       </c>
-      <c r="C21" s="30" t="n"/>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="30" t="n"/>
-      <c r="F21" s="54">
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+      <c r="E21" s="31" t="n"/>
+      <c r="F21" s="55">
         <f>"апрель "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G21" s="54" t="n"/>
-      <c r="H21" s="55">
+      <c r="G21" s="55" t="n"/>
+      <c r="H21" s="56">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$8</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="53" t="inlineStr">
+      <c r="B22" s="54" t="inlineStr">
         <is>
           <t>Взнос на капитальный ремонт (площадь × размер взноса)</t>
         </is>
       </c>
-      <c r="C22" s="30" t="n"/>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="30" t="n"/>
-      <c r="F22" s="54">
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+      <c r="E22" s="31" t="n"/>
+      <c r="F22" s="55">
         <f>"май "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G22" s="54" t="n"/>
-      <c r="H22" s="55">
+      <c r="G22" s="55" t="n"/>
+      <c r="H22" s="56">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$8</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="53" t="inlineStr">
+      <c r="B23" s="54" t="inlineStr">
         <is>
           <t>Взнос на капитальный ремонт (площадь × размер взноса)</t>
         </is>
       </c>
-      <c r="C23" s="30" t="n"/>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="30" t="n"/>
-      <c r="F23" s="54">
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+      <c r="E23" s="31" t="n"/>
+      <c r="F23" s="55">
         <f>"июнь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G23" s="54" t="n"/>
-      <c r="H23" s="55">
+      <c r="G23" s="55" t="n"/>
+      <c r="H23" s="56">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$8</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="B24" s="56" t="inlineStr">
+      <c r="B24" s="57" t="inlineStr">
         <is>
           <t>Итого начислено за квартал</t>
         </is>
       </c>
-      <c r="C24" s="57" t="n"/>
-      <c r="D24" s="57" t="n"/>
-      <c r="E24" s="57" t="n"/>
-      <c r="F24" s="58">
+      <c r="C24" s="58" t="n"/>
+      <c r="D24" s="58" t="n"/>
+      <c r="E24" s="58" t="n"/>
+      <c r="F24" s="59">
         <f>"II квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G24" s="58" t="n"/>
-      <c r="H24" s="59">
+      <c r="G24" s="59" t="n"/>
+      <c r="H24" s="60">
         <f>ROUND(SUM(H21:H23),2)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="B25" s="53" t="inlineStr">
+      <c r="B25" s="54" t="inlineStr">
         <is>
           <t>Задолженность за предыдущие периоды</t>
         </is>
       </c>
-      <c r="C25" s="30" t="n"/>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="30" t="n"/>
-      <c r="F25" s="60">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$D$31="","",'ИСХОДНЫЕ ДАННЫЕ'!$D$31)</f>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+      <c r="E25" s="31" t="n"/>
+      <c r="F25" s="61">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$D$32="","",'ИСХОДНЫЕ ДАННЫЕ'!$D$32)</f>
         <v/>
       </c>
-      <c r="G25" s="60" t="n"/>
-      <c r="H25" s="55">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$31</f>
+      <c r="G25" s="61" t="n"/>
+      <c r="H25" s="56">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$32</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="B26" s="61" t="inlineStr">
+      <c r="B26" s="62" t="inlineStr">
         <is>
           <t>ИТОГО К ОПЛАТЕ</t>
         </is>
       </c>
-      <c r="C26" s="62" t="n"/>
-      <c r="D26" s="62" t="n"/>
-      <c r="E26" s="62" t="n"/>
-      <c r="F26" s="62" t="n"/>
-      <c r="G26" s="62" t="n"/>
-      <c r="H26" s="63">
+      <c r="C26" s="63" t="n"/>
+      <c r="D26" s="63" t="n"/>
+      <c r="E26" s="63" t="n"/>
+      <c r="F26" s="63" t="n"/>
+      <c r="G26" s="63" t="n"/>
+      <c r="H26" s="64">
         <f>ROUND(H24+H25,2)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="5" customHeight="1"/>
     <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>4. СПРАВОЧНАЯ ИНФОРМАЦИЯ ПО СПЕЦИАЛЬНОМУ СЧЁТУ (ч. 7 ст. 177 ЖК РФ)</t>
         </is>
       </c>
-      <c r="C28" s="24" t="n"/>
-      <c r="D28" s="24" t="n"/>
-      <c r="E28" s="24" t="n"/>
-      <c r="F28" s="24" t="n"/>
-      <c r="G28" s="24" t="n"/>
-      <c r="H28" s="25" t="n"/>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="25" t="n"/>
+      <c r="G28" s="25" t="n"/>
+      <c r="H28" s="26" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="64">
+      <c r="B29" s="65">
         <f>"Поступило оплат по лицевому счёту с начала "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года, руб."</f>
         <v/>
       </c>
-      <c r="C29" s="36" t="n"/>
-      <c r="D29" s="36" t="n"/>
-      <c r="E29" s="36" t="n"/>
-      <c r="F29" s="36" t="n"/>
-      <c r="G29" s="65">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$F$31="","—",'ИСХОДНЫЕ ДАННЫЕ'!$F$31)</f>
+      <c r="C29" s="37" t="n"/>
+      <c r="D29" s="37" t="n"/>
+      <c r="E29" s="37" t="n"/>
+      <c r="F29" s="37" t="n"/>
+      <c r="G29" s="66">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$F$32="","—",'ИСХОДНЫЕ ДАННЫЕ'!$F$32)</f>
         <v/>
       </c>
-      <c r="H29" s="66" t="n"/>
+      <c r="H29" s="67" t="n"/>
     </row>
     <row r="30" ht="5" customHeight="1"/>
     <row r="31" ht="16" customHeight="1">
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>5. ПОРЯДОК ОПЛАТЫ</t>
         </is>
       </c>
-      <c r="C31" s="24" t="n"/>
-      <c r="D31" s="24" t="n"/>
-      <c r="E31" s="24" t="n"/>
-      <c r="F31" s="24" t="n"/>
-      <c r="G31" s="24" t="n"/>
-      <c r="H31" s="25" t="n"/>
+      <c r="C31" s="25" t="n"/>
+      <c r="D31" s="25" t="n"/>
+      <c r="E31" s="25" t="n"/>
+      <c r="F31" s="25" t="n"/>
+      <c r="G31" s="25" t="n"/>
+      <c r="H31" s="26" t="n"/>
     </row>
     <row r="32" ht="14" customHeight="1">
-      <c r="B32" s="67" t="inlineStr">
+      <c r="B32" s="68" t="inlineStr">
         <is>
           <t>1) без комиссии — в отделениях АО «Россельхозбанк» (банк, в котором открыт специальный счёт дома);</t>
         </is>
       </c>
-      <c r="C32" s="68" t="n"/>
-      <c r="D32" s="68" t="n"/>
-      <c r="E32" s="68" t="n"/>
-      <c r="F32" s="68" t="n"/>
-      <c r="G32" s="69" t="n"/>
-      <c r="H32" s="70" t="n"/>
+      <c r="C32" s="69" t="n"/>
+      <c r="D32" s="69" t="n"/>
+      <c r="E32" s="69" t="n"/>
+      <c r="F32" s="69" t="n"/>
+      <c r="G32" s="70" t="n"/>
+      <c r="H32" s="71" t="n"/>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="B33" s="67" t="inlineStr">
+      <c r="B33" s="68" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33321,117 +33330,117 @@
           </r>
         </is>
       </c>
-      <c r="C33" s="68" t="n"/>
-      <c r="D33" s="68" t="n"/>
-      <c r="E33" s="68" t="n"/>
-      <c r="F33" s="68" t="n"/>
-      <c r="G33" s="69" t="n"/>
-      <c r="H33" s="70" t="n"/>
+      <c r="C33" s="69" t="n"/>
+      <c r="D33" s="69" t="n"/>
+      <c r="E33" s="69" t="n"/>
+      <c r="F33" s="69" t="n"/>
+      <c r="G33" s="70" t="n"/>
+      <c r="H33" s="71" t="n"/>
     </row>
     <row r="34" ht="14" customHeight="1">
-      <c r="B34" s="67" t="n"/>
-      <c r="C34" s="68" t="n"/>
-      <c r="D34" s="68" t="n"/>
-      <c r="E34" s="68" t="n"/>
-      <c r="F34" s="68" t="n"/>
-      <c r="G34" s="69" t="n"/>
-      <c r="H34" s="70" t="n"/>
+      <c r="B34" s="68" t="n"/>
+      <c r="C34" s="69" t="n"/>
+      <c r="D34" s="69" t="n"/>
+      <c r="E34" s="69" t="n"/>
+      <c r="F34" s="69" t="n"/>
+      <c r="G34" s="70" t="n"/>
+      <c r="H34" s="71" t="n"/>
     </row>
     <row r="35" ht="14" customHeight="1">
-      <c r="B35" s="29" t="inlineStr">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>Назначение платежа:</t>
         </is>
       </c>
-      <c r="C35" s="32" t="n"/>
-      <c r="D35" s="32" t="n"/>
-      <c r="E35" s="32" t="n"/>
-      <c r="F35" s="32" t="n"/>
-      <c r="G35" s="69" t="n"/>
-      <c r="H35" s="70" t="n"/>
+      <c r="C35" s="33" t="n"/>
+      <c r="D35" s="33" t="n"/>
+      <c r="E35" s="33" t="n"/>
+      <c r="F35" s="33" t="n"/>
+      <c r="G35" s="70" t="n"/>
+      <c r="H35" s="71" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="B36" s="67">
+      <c r="B36" s="68">
         <f>"Взнос на капитальный ремонт, л/с № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;", кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;", за "&amp;"II квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="C36" s="68" t="n"/>
-      <c r="D36" s="68" t="n"/>
-      <c r="E36" s="68" t="n"/>
-      <c r="F36" s="68" t="n"/>
-      <c r="G36" s="69" t="n"/>
-      <c r="H36" s="70" t="n"/>
+      <c r="C36" s="69" t="n"/>
+      <c r="D36" s="69" t="n"/>
+      <c r="E36" s="69" t="n"/>
+      <c r="F36" s="69" t="n"/>
+      <c r="G36" s="70" t="n"/>
+      <c r="H36" s="71" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="B37" s="71">
-        <f>"Срок оплаты: до "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$49&amp;" числа месяца, следующего за расчётным (за "&amp;"II квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — до "&amp;TEXT(DAY(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,6+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49)),"00")&amp;"."&amp;TEXT(MONTH(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,6+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49)),"00")&amp;"."&amp;YEAR(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,6+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49))&amp;")."&amp;CHAR(10)&amp;"Основание: ч. 1 ст. 155, ч. 2 ст. 171 ЖК РФ."</f>
+      <c r="B37" s="72">
+        <f>"Срок оплаты: до "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$50&amp;" числа месяца, следующего за расчётным (за "&amp;"II квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — до "&amp;TEXT(DAY(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,6+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$50)),"00")&amp;"."&amp;TEXT(MONTH(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,6+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$50)),"00")&amp;"."&amp;YEAR(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,6+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$50))&amp;")."&amp;CHAR(10)&amp;"Основание: ч. 1 ст. 155, ч. 2 ст. 171 ЖК РФ."</f>
         <v/>
       </c>
-      <c r="C37" s="72" t="n"/>
-      <c r="D37" s="72" t="n"/>
-      <c r="E37" s="72" t="n"/>
-      <c r="F37" s="72" t="n"/>
-      <c r="G37" s="73" t="n"/>
-      <c r="H37" s="74" t="n"/>
+      <c r="C37" s="73" t="n"/>
+      <c r="D37" s="73" t="n"/>
+      <c r="E37" s="73" t="n"/>
+      <c r="F37" s="73" t="n"/>
+      <c r="G37" s="74" t="n"/>
+      <c r="H37" s="75" t="n"/>
     </row>
     <row r="38" ht="5" customHeight="1"/>
     <row r="39" ht="32" customHeight="1">
-      <c r="B39" s="75">
-        <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
+      <c r="B39" s="76">
+        <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
         <v/>
       </c>
-      <c r="C39" s="75" t="n"/>
-      <c r="D39" s="75" t="n"/>
-      <c r="E39" s="75" t="n"/>
-      <c r="F39" s="75" t="n"/>
-      <c r="G39" s="75" t="n"/>
-      <c r="H39" s="75" t="n"/>
+      <c r="C39" s="76" t="n"/>
+      <c r="D39" s="76" t="n"/>
+      <c r="E39" s="76" t="n"/>
+      <c r="F39" s="76" t="n"/>
+      <c r="G39" s="76" t="n"/>
+      <c r="H39" s="76" t="n"/>
     </row>
     <row r="40" ht="44" customHeight="1">
-      <c r="B40" s="76">
+      <c r="B40" s="77">
         <f>"В отделении банка и в мобильном приложении во вкладках ищите "&amp;"«РФКР МКД_капремонт, оплата по расчётному счёту» и указывайте номер расчётного счёта, приведённый выше. Оплата через общий поиск «Капитальный ремонт» уходит на общий счёт Регионального фонда капитального ремонта и на счёт вашего дома не поступает."&amp;CHAR(10)&amp;"Лицевой счёт № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;" при оплате НЕ вводится — он указан справочно, только для учёта начислений."</f>
         <v/>
       </c>
-      <c r="C40" s="76" t="n"/>
-      <c r="D40" s="76" t="n"/>
-      <c r="E40" s="76" t="n"/>
-      <c r="F40" s="76" t="n"/>
-      <c r="G40" s="76" t="n"/>
-      <c r="H40" s="76" t="n"/>
+      <c r="C40" s="77" t="n"/>
+      <c r="D40" s="77" t="n"/>
+      <c r="E40" s="77" t="n"/>
+      <c r="F40" s="77" t="n"/>
+      <c r="G40" s="77" t="n"/>
+      <c r="H40" s="77" t="n"/>
     </row>
     <row r="41" ht="6" customHeight="1"/>
     <row r="42" ht="24" customHeight="1">
-      <c r="B42" s="77" t="inlineStr">
+      <c r="B42" s="78" t="inlineStr">
         <is>
           <t>Подпись плательщика  ______________________</t>
         </is>
       </c>
-      <c r="C42" s="77" t="n"/>
-      <c r="D42" s="77" t="n"/>
-      <c r="E42" s="77" t="inlineStr">
+      <c r="C42" s="78" t="n"/>
+      <c r="D42" s="78" t="n"/>
+      <c r="E42" s="78" t="inlineStr">
         <is>
           <t>Кассир  ______________</t>
         </is>
       </c>
-      <c r="F42" s="77" t="n"/>
-      <c r="G42" s="77" t="inlineStr">
+      <c r="F42" s="78" t="n"/>
+      <c r="G42" s="78" t="inlineStr">
         <is>
           <t>Дата  ____________</t>
         </is>
       </c>
-      <c r="H42" s="77" t="n"/>
+      <c r="H42" s="78" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="B43" s="78">
+      <c r="B43" s="79">
         <f>"Начисление за "&amp;"II квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;"    По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
       </c>
-      <c r="C43" s="78" t="n"/>
-      <c r="D43" s="78" t="n"/>
-      <c r="E43" s="78" t="n"/>
-      <c r="F43" s="78" t="n"/>
-      <c r="G43" s="78" t="n"/>
-      <c r="H43" s="78" t="n"/>
+      <c r="C43" s="79" t="n"/>
+      <c r="D43" s="79" t="n"/>
+      <c r="E43" s="79" t="n"/>
+      <c r="F43" s="79" t="n"/>
+      <c r="G43" s="79" t="n"/>
+      <c r="H43" s="79" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="48">
@@ -33512,7 +33521,7 @@
   <sheetData>
     <row r="1" ht="6" customHeight="1"/>
     <row r="2" ht="40" customHeight="1">
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33535,462 +33544,462 @@
           </r>
         </is>
       </c>
-      <c r="C2" s="18" t="n"/>
-      <c r="D2" s="18" t="n"/>
-      <c r="E2" s="18" t="n"/>
-      <c r="F2" s="18" t="n"/>
-      <c r="G2" s="18" t="n"/>
-      <c r="H2" s="18" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
+      <c r="H2" s="19" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="B3" s="19">
+      <c r="B3" s="20">
         <f>"Специальный счёт МКД · "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14</f>
         <v/>
       </c>
-      <c r="C3" s="20" t="n"/>
-      <c r="D3" s="20" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="21">
+      <c r="C3" s="21" t="n"/>
+      <c r="D3" s="21" t="n"/>
+      <c r="E3" s="21" t="n"/>
+      <c r="F3" s="22">
         <f>"Расчётный период: "&amp;"III квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G3" s="21" t="n"/>
-      <c r="H3" s="22" t="n"/>
+      <c r="G3" s="22" t="n"/>
+      <c r="H3" s="23" t="n"/>
     </row>
     <row r="4" ht="5" customHeight="1"/>
     <row r="5" ht="16" customHeight="1">
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>1. ПОЛУЧАТЕЛЬ ПЛАТЕЖА — ВЛАДЕЛЕЦ СПЕЦИАЛЬНОГО СЧЁТА</t>
         </is>
       </c>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="24" t="n"/>
-      <c r="G5" s="24" t="n"/>
-      <c r="H5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="26" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>Получатель платежа</t>
         </is>
       </c>
-      <c r="C6" s="27">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$39</f>
-        <v/>
-      </c>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="27" t="n"/>
-      <c r="G6" s="27" t="n"/>
-      <c r="H6" s="28" t="n"/>
-    </row>
-    <row r="7" ht="14" customHeight="1">
-      <c r="B7" s="29" t="inlineStr">
-        <is>
-          <t>Юридический адрес</t>
-        </is>
-      </c>
-      <c r="C7" s="30">
+      <c r="C6" s="28">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$40</f>
         <v/>
       </c>
-      <c r="D7" s="30" t="n"/>
-      <c r="E7" s="30" t="n"/>
-      <c r="F7" s="30" t="n"/>
-      <c r="G7" s="30" t="n"/>
-      <c r="H7" s="31" t="n"/>
+      <c r="D6" s="28" t="n"/>
+      <c r="E6" s="28" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
+      <c r="H6" s="29" t="n"/>
+    </row>
+    <row r="7" ht="14" customHeight="1">
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Юридический адрес</t>
+        </is>
+      </c>
+      <c r="C7" s="31">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$41</f>
+        <v/>
+      </c>
+      <c r="D7" s="31" t="n"/>
+      <c r="E7" s="31" t="n"/>
+      <c r="F7" s="31" t="n"/>
+      <c r="G7" s="31" t="n"/>
+      <c r="H7" s="32" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>ИНН / КПП</t>
         </is>
       </c>
-      <c r="C8" s="30">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$41&amp;" / "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$42</f>
+      <c r="C8" s="31">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$42&amp;" / "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$43</f>
         <v/>
       </c>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="32" t="inlineStr">
+      <c r="D8" s="31" t="n"/>
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>ОГРН</t>
         </is>
       </c>
-      <c r="F8" s="30">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$43</f>
+      <c r="F8" s="31">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$44</f>
         <v/>
       </c>
-      <c r="G8" s="30" t="n"/>
-      <c r="H8" s="31" t="n"/>
+      <c r="G8" s="31" t="n"/>
+      <c r="H8" s="32" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Расчётный счёт</t>
         </is>
       </c>
-      <c r="C9" s="33">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;"   (специальный счёт МКД: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;")"</f>
+      <c r="C9" s="34">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (специальный счёт МКД: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;")"</f>
         <v/>
       </c>
-      <c r="D9" s="33" t="n"/>
-      <c r="E9" s="33" t="n"/>
-      <c r="F9" s="33" t="n"/>
-      <c r="G9" s="33" t="n"/>
-      <c r="H9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="35" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
       </c>
-      <c r="C10" s="30">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45</f>
+      <c r="C10" s="31">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$46</f>
         <v/>
       </c>
-      <c r="D10" s="30" t="n"/>
-      <c r="E10" s="30" t="n"/>
-      <c r="F10" s="30" t="n"/>
-      <c r="G10" s="30" t="n"/>
-      <c r="H10" s="31" t="n"/>
+      <c r="D10" s="31" t="n"/>
+      <c r="E10" s="31" t="n"/>
+      <c r="F10" s="31" t="n"/>
+      <c r="G10" s="31" t="n"/>
+      <c r="H10" s="32" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>Корр. счёт / БИК</t>
         </is>
       </c>
-      <c r="C11" s="36">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$46&amp;" / "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$47</f>
+      <c r="C11" s="37">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$47&amp;" / "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$48</f>
         <v/>
       </c>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="37" t="inlineStr">
+      <c r="D11" s="37" t="n"/>
+      <c r="E11" s="38" t="inlineStr">
         <is>
           <t>ИНН/КПП банка</t>
         </is>
       </c>
-      <c r="F11" s="36">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$48</f>
+      <c r="F11" s="37">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$49</f>
         <v/>
       </c>
-      <c r="G11" s="36" t="n"/>
-      <c r="H11" s="38" t="n"/>
+      <c r="G11" s="37" t="n"/>
+      <c r="H11" s="39" t="n"/>
     </row>
     <row r="12" ht="5" customHeight="1"/>
     <row r="13" ht="16" customHeight="1">
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>2. ПЛАТЕЛЬЩИК И ПОМЕЩЕНИЕ</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
-      <c r="D13" s="24" t="n"/>
-      <c r="E13" s="24" t="n"/>
-      <c r="F13" s="24" t="n"/>
-      <c r="G13" s="24" t="n"/>
-      <c r="H13" s="25" t="n"/>
+      <c r="C13" s="25" t="n"/>
+      <c r="D13" s="25" t="n"/>
+      <c r="E13" s="25" t="n"/>
+      <c r="F13" s="25" t="n"/>
+      <c r="G13" s="25" t="n"/>
+      <c r="H13" s="26" t="n"/>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>Лицевой счёт</t>
         </is>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="40">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$11</f>
         <v/>
       </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>Квартира №</t>
         </is>
       </c>
-      <c r="E14" s="40">
+      <c r="E14" s="41">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$12</f>
         <v/>
       </c>
-      <c r="F14" s="41" t="inlineStr">
+      <c r="F14" s="42" t="inlineStr">
         <is>
           <t>Дата формирования</t>
         </is>
       </c>
-      <c r="G14" s="42">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$E$32</f>
+      <c r="G14" s="43">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$E$33</f>
         <v/>
       </c>
-      <c r="H14" s="43" t="n"/>
+      <c r="H14" s="44" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="B15" s="29" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Плательщик</t>
         </is>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="34">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$13</f>
         <v/>
       </c>
-      <c r="D15" s="33" t="n"/>
-      <c r="E15" s="33" t="n"/>
-      <c r="F15" s="33" t="n"/>
-      <c r="G15" s="33" t="n"/>
-      <c r="H15" s="34" t="n"/>
+      <c r="D15" s="34" t="n"/>
+      <c r="E15" s="34" t="n"/>
+      <c r="F15" s="34" t="n"/>
+      <c r="G15" s="34" t="n"/>
+      <c r="H15" s="35" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>Адрес помещения</t>
         </is>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", кв. "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12</f>
         <v/>
       </c>
-      <c r="D16" s="30" t="n"/>
-      <c r="E16" s="30" t="n"/>
-      <c r="F16" s="30" t="n"/>
-      <c r="G16" s="30" t="n"/>
-      <c r="H16" s="31" t="n"/>
+      <c r="D16" s="31" t="n"/>
+      <c r="E16" s="31" t="n"/>
+      <c r="F16" s="31" t="n"/>
+      <c r="G16" s="31" t="n"/>
+      <c r="H16" s="32" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="B17" s="44" t="inlineStr">
+      <c r="B17" s="45" t="inlineStr">
         <is>
           <t>Площадь помещения, м²</t>
         </is>
       </c>
-      <c r="C17" s="45">
+      <c r="C17" s="46">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$6</f>
         <v/>
       </c>
-      <c r="D17" s="46" t="inlineStr">
+      <c r="D17" s="47" t="inlineStr">
         <is>
           <t>Размер взноса, руб./м²</t>
         </is>
       </c>
-      <c r="E17" s="47">
+      <c r="E17" s="48">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$7</f>
         <v/>
       </c>
-      <c r="F17" s="37" t="inlineStr">
+      <c r="F17" s="38" t="inlineStr">
         <is>
           <t>Период оплаты</t>
         </is>
       </c>
-      <c r="G17" s="48">
+      <c r="G17" s="49">
         <f>"III квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="H17" s="49" t="n"/>
+      <c r="H17" s="50" t="n"/>
     </row>
     <row r="18" ht="5" customHeight="1"/>
     <row r="19" ht="16" customHeight="1">
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>3. РАСЧЁТ РАЗМЕРА ВЗНОСА И СУММЫ К ОПЛАТЕ</t>
         </is>
       </c>
-      <c r="C19" s="24" t="n"/>
-      <c r="D19" s="24" t="n"/>
-      <c r="E19" s="24" t="n"/>
-      <c r="F19" s="24" t="n"/>
-      <c r="G19" s="24" t="n"/>
-      <c r="H19" s="25" t="n"/>
+      <c r="C19" s="25" t="n"/>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="25" t="n"/>
+      <c r="G19" s="25" t="n"/>
+      <c r="H19" s="26" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="50" t="inlineStr">
+      <c r="B20" s="51" t="inlineStr">
         <is>
           <t>Вид платежа</t>
         </is>
       </c>
-      <c r="C20" s="51" t="n"/>
-      <c r="D20" s="51" t="n"/>
-      <c r="E20" s="51" t="n"/>
-      <c r="F20" s="51" t="inlineStr">
+      <c r="C20" s="52" t="n"/>
+      <c r="D20" s="52" t="n"/>
+      <c r="E20" s="52" t="n"/>
+      <c r="F20" s="52" t="inlineStr">
         <is>
           <t>Расчётный период</t>
         </is>
       </c>
-      <c r="G20" s="51" t="n"/>
-      <c r="H20" s="52" t="inlineStr">
+      <c r="G20" s="52" t="n"/>
+      <c r="H20" s="53" t="inlineStr">
         <is>
           <t>Сумма, руб.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="B21" s="53" t="inlineStr">
+      <c r="B21" s="54" t="inlineStr">
         <is>
           <t>Взнос на капитальный ремонт (площадь × размер взноса)</t>
         </is>
       </c>
-      <c r="C21" s="30" t="n"/>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="30" t="n"/>
-      <c r="F21" s="54">
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+      <c r="E21" s="31" t="n"/>
+      <c r="F21" s="55">
         <f>"июль "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G21" s="54" t="n"/>
-      <c r="H21" s="55">
+      <c r="G21" s="55" t="n"/>
+      <c r="H21" s="56">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$8</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="53" t="inlineStr">
+      <c r="B22" s="54" t="inlineStr">
         <is>
           <t>Взнос на капитальный ремонт (площадь × размер взноса)</t>
         </is>
       </c>
-      <c r="C22" s="30" t="n"/>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="30" t="n"/>
-      <c r="F22" s="54">
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+      <c r="E22" s="31" t="n"/>
+      <c r="F22" s="55">
         <f>"август "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G22" s="54" t="n"/>
-      <c r="H22" s="55">
+      <c r="G22" s="55" t="n"/>
+      <c r="H22" s="56">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$8</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="53" t="inlineStr">
+      <c r="B23" s="54" t="inlineStr">
         <is>
           <t>Взнос на капитальный ремонт (площадь × размер взноса)</t>
         </is>
       </c>
-      <c r="C23" s="30" t="n"/>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="30" t="n"/>
-      <c r="F23" s="54">
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+      <c r="E23" s="31" t="n"/>
+      <c r="F23" s="55">
         <f>"сентябрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G23" s="54" t="n"/>
-      <c r="H23" s="55">
+      <c r="G23" s="55" t="n"/>
+      <c r="H23" s="56">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$8</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="B24" s="56" t="inlineStr">
+      <c r="B24" s="57" t="inlineStr">
         <is>
           <t>Итого начислено за квартал</t>
         </is>
       </c>
-      <c r="C24" s="57" t="n"/>
-      <c r="D24" s="57" t="n"/>
-      <c r="E24" s="57" t="n"/>
-      <c r="F24" s="58">
+      <c r="C24" s="58" t="n"/>
+      <c r="D24" s="58" t="n"/>
+      <c r="E24" s="58" t="n"/>
+      <c r="F24" s="59">
         <f>"III квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G24" s="58" t="n"/>
-      <c r="H24" s="59">
+      <c r="G24" s="59" t="n"/>
+      <c r="H24" s="60">
         <f>ROUND(SUM(H21:H23),2)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="B25" s="53" t="inlineStr">
+      <c r="B25" s="54" t="inlineStr">
         <is>
           <t>Задолженность за предыдущие периоды</t>
         </is>
       </c>
-      <c r="C25" s="30" t="n"/>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="30" t="n"/>
-      <c r="F25" s="60">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$D$32="","",'ИСХОДНЫЕ ДАННЫЕ'!$D$32)</f>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+      <c r="E25" s="31" t="n"/>
+      <c r="F25" s="61">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$D$33="","",'ИСХОДНЫЕ ДАННЫЕ'!$D$33)</f>
         <v/>
       </c>
-      <c r="G25" s="60" t="n"/>
-      <c r="H25" s="55">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$32</f>
+      <c r="G25" s="61" t="n"/>
+      <c r="H25" s="56">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$33</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="B26" s="61" t="inlineStr">
+      <c r="B26" s="62" t="inlineStr">
         <is>
           <t>ИТОГО К ОПЛАТЕ</t>
         </is>
       </c>
-      <c r="C26" s="62" t="n"/>
-      <c r="D26" s="62" t="n"/>
-      <c r="E26" s="62" t="n"/>
-      <c r="F26" s="62" t="n"/>
-      <c r="G26" s="62" t="n"/>
-      <c r="H26" s="63">
+      <c r="C26" s="63" t="n"/>
+      <c r="D26" s="63" t="n"/>
+      <c r="E26" s="63" t="n"/>
+      <c r="F26" s="63" t="n"/>
+      <c r="G26" s="63" t="n"/>
+      <c r="H26" s="64">
         <f>ROUND(H24+H25,2)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="5" customHeight="1"/>
     <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>4. СПРАВОЧНАЯ ИНФОРМАЦИЯ ПО СПЕЦИАЛЬНОМУ СЧЁТУ (ч. 7 ст. 177 ЖК РФ)</t>
         </is>
       </c>
-      <c r="C28" s="24" t="n"/>
-      <c r="D28" s="24" t="n"/>
-      <c r="E28" s="24" t="n"/>
-      <c r="F28" s="24" t="n"/>
-      <c r="G28" s="24" t="n"/>
-      <c r="H28" s="25" t="n"/>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="25" t="n"/>
+      <c r="G28" s="25" t="n"/>
+      <c r="H28" s="26" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="64">
+      <c r="B29" s="65">
         <f>"Поступило оплат по лицевому счёту с начала "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года, руб."</f>
         <v/>
       </c>
-      <c r="C29" s="36" t="n"/>
-      <c r="D29" s="36" t="n"/>
-      <c r="E29" s="36" t="n"/>
-      <c r="F29" s="36" t="n"/>
-      <c r="G29" s="65">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$F$32="","—",'ИСХОДНЫЕ ДАННЫЕ'!$F$32)</f>
+      <c r="C29" s="37" t="n"/>
+      <c r="D29" s="37" t="n"/>
+      <c r="E29" s="37" t="n"/>
+      <c r="F29" s="37" t="n"/>
+      <c r="G29" s="66">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$F$33="","—",'ИСХОДНЫЕ ДАННЫЕ'!$F$33)</f>
         <v/>
       </c>
-      <c r="H29" s="66" t="n"/>
+      <c r="H29" s="67" t="n"/>
     </row>
     <row r="30" ht="5" customHeight="1"/>
     <row r="31" ht="16" customHeight="1">
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>5. ПОРЯДОК ОПЛАТЫ</t>
         </is>
       </c>
-      <c r="C31" s="24" t="n"/>
-      <c r="D31" s="24" t="n"/>
-      <c r="E31" s="24" t="n"/>
-      <c r="F31" s="24" t="n"/>
-      <c r="G31" s="24" t="n"/>
-      <c r="H31" s="25" t="n"/>
+      <c r="C31" s="25" t="n"/>
+      <c r="D31" s="25" t="n"/>
+      <c r="E31" s="25" t="n"/>
+      <c r="F31" s="25" t="n"/>
+      <c r="G31" s="25" t="n"/>
+      <c r="H31" s="26" t="n"/>
     </row>
     <row r="32" ht="14" customHeight="1">
-      <c r="B32" s="67" t="inlineStr">
+      <c r="B32" s="68" t="inlineStr">
         <is>
           <t>1) без комиссии — в отделениях АО «Россельхозбанк» (банк, в котором открыт специальный счёт дома);</t>
         </is>
       </c>
-      <c r="C32" s="68" t="n"/>
-      <c r="D32" s="68" t="n"/>
-      <c r="E32" s="68" t="n"/>
-      <c r="F32" s="68" t="n"/>
-      <c r="G32" s="69" t="n"/>
-      <c r="H32" s="70" t="n"/>
+      <c r="C32" s="69" t="n"/>
+      <c r="D32" s="69" t="n"/>
+      <c r="E32" s="69" t="n"/>
+      <c r="F32" s="69" t="n"/>
+      <c r="G32" s="70" t="n"/>
+      <c r="H32" s="71" t="n"/>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="B33" s="67" t="inlineStr">
+      <c r="B33" s="68" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34019,117 +34028,117 @@
           </r>
         </is>
       </c>
-      <c r="C33" s="68" t="n"/>
-      <c r="D33" s="68" t="n"/>
-      <c r="E33" s="68" t="n"/>
-      <c r="F33" s="68" t="n"/>
-      <c r="G33" s="69" t="n"/>
-      <c r="H33" s="70" t="n"/>
+      <c r="C33" s="69" t="n"/>
+      <c r="D33" s="69" t="n"/>
+      <c r="E33" s="69" t="n"/>
+      <c r="F33" s="69" t="n"/>
+      <c r="G33" s="70" t="n"/>
+      <c r="H33" s="71" t="n"/>
     </row>
     <row r="34" ht="14" customHeight="1">
-      <c r="B34" s="67" t="n"/>
-      <c r="C34" s="68" t="n"/>
-      <c r="D34" s="68" t="n"/>
-      <c r="E34" s="68" t="n"/>
-      <c r="F34" s="68" t="n"/>
-      <c r="G34" s="69" t="n"/>
-      <c r="H34" s="70" t="n"/>
+      <c r="B34" s="68" t="n"/>
+      <c r="C34" s="69" t="n"/>
+      <c r="D34" s="69" t="n"/>
+      <c r="E34" s="69" t="n"/>
+      <c r="F34" s="69" t="n"/>
+      <c r="G34" s="70" t="n"/>
+      <c r="H34" s="71" t="n"/>
     </row>
     <row r="35" ht="14" customHeight="1">
-      <c r="B35" s="29" t="inlineStr">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>Назначение платежа:</t>
         </is>
       </c>
-      <c r="C35" s="32" t="n"/>
-      <c r="D35" s="32" t="n"/>
-      <c r="E35" s="32" t="n"/>
-      <c r="F35" s="32" t="n"/>
-      <c r="G35" s="69" t="n"/>
-      <c r="H35" s="70" t="n"/>
+      <c r="C35" s="33" t="n"/>
+      <c r="D35" s="33" t="n"/>
+      <c r="E35" s="33" t="n"/>
+      <c r="F35" s="33" t="n"/>
+      <c r="G35" s="70" t="n"/>
+      <c r="H35" s="71" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="B36" s="67">
+      <c r="B36" s="68">
         <f>"Взнос на капитальный ремонт, л/с № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;", кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;", за "&amp;"III квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="C36" s="68" t="n"/>
-      <c r="D36" s="68" t="n"/>
-      <c r="E36" s="68" t="n"/>
-      <c r="F36" s="68" t="n"/>
-      <c r="G36" s="69" t="n"/>
-      <c r="H36" s="70" t="n"/>
+      <c r="C36" s="69" t="n"/>
+      <c r="D36" s="69" t="n"/>
+      <c r="E36" s="69" t="n"/>
+      <c r="F36" s="69" t="n"/>
+      <c r="G36" s="70" t="n"/>
+      <c r="H36" s="71" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="B37" s="71">
-        <f>"Срок оплаты: до "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$49&amp;" числа месяца, следующего за расчётным (за "&amp;"III квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — до "&amp;TEXT(DAY(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,9+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49)),"00")&amp;"."&amp;TEXT(MONTH(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,9+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49)),"00")&amp;"."&amp;YEAR(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,9+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49))&amp;")."&amp;CHAR(10)&amp;"Основание: ч. 1 ст. 155, ч. 2 ст. 171 ЖК РФ."</f>
+      <c r="B37" s="72">
+        <f>"Срок оплаты: до "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$50&amp;" числа месяца, следующего за расчётным (за "&amp;"III квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — до "&amp;TEXT(DAY(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,9+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$50)),"00")&amp;"."&amp;TEXT(MONTH(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,9+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$50)),"00")&amp;"."&amp;YEAR(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,9+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$50))&amp;")."&amp;CHAR(10)&amp;"Основание: ч. 1 ст. 155, ч. 2 ст. 171 ЖК РФ."</f>
         <v/>
       </c>
-      <c r="C37" s="72" t="n"/>
-      <c r="D37" s="72" t="n"/>
-      <c r="E37" s="72" t="n"/>
-      <c r="F37" s="72" t="n"/>
-      <c r="G37" s="73" t="n"/>
-      <c r="H37" s="74" t="n"/>
+      <c r="C37" s="73" t="n"/>
+      <c r="D37" s="73" t="n"/>
+      <c r="E37" s="73" t="n"/>
+      <c r="F37" s="73" t="n"/>
+      <c r="G37" s="74" t="n"/>
+      <c r="H37" s="75" t="n"/>
     </row>
     <row r="38" ht="5" customHeight="1"/>
     <row r="39" ht="32" customHeight="1">
-      <c r="B39" s="75">
-        <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
+      <c r="B39" s="76">
+        <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
         <v/>
       </c>
-      <c r="C39" s="75" t="n"/>
-      <c r="D39" s="75" t="n"/>
-      <c r="E39" s="75" t="n"/>
-      <c r="F39" s="75" t="n"/>
-      <c r="G39" s="75" t="n"/>
-      <c r="H39" s="75" t="n"/>
+      <c r="C39" s="76" t="n"/>
+      <c r="D39" s="76" t="n"/>
+      <c r="E39" s="76" t="n"/>
+      <c r="F39" s="76" t="n"/>
+      <c r="G39" s="76" t="n"/>
+      <c r="H39" s="76" t="n"/>
     </row>
     <row r="40" ht="44" customHeight="1">
-      <c r="B40" s="76">
+      <c r="B40" s="77">
         <f>"В отделении банка и в мобильном приложении во вкладках ищите "&amp;"«РФКР МКД_капремонт, оплата по расчётному счёту» и указывайте номер расчётного счёта, приведённый выше. Оплата через общий поиск «Капитальный ремонт» уходит на общий счёт Регионального фонда капитального ремонта и на счёт вашего дома не поступает."&amp;CHAR(10)&amp;"Лицевой счёт № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;" при оплате НЕ вводится — он указан справочно, только для учёта начислений."</f>
         <v/>
       </c>
-      <c r="C40" s="76" t="n"/>
-      <c r="D40" s="76" t="n"/>
-      <c r="E40" s="76" t="n"/>
-      <c r="F40" s="76" t="n"/>
-      <c r="G40" s="76" t="n"/>
-      <c r="H40" s="76" t="n"/>
+      <c r="C40" s="77" t="n"/>
+      <c r="D40" s="77" t="n"/>
+      <c r="E40" s="77" t="n"/>
+      <c r="F40" s="77" t="n"/>
+      <c r="G40" s="77" t="n"/>
+      <c r="H40" s="77" t="n"/>
     </row>
     <row r="41" ht="6" customHeight="1"/>
     <row r="42" ht="24" customHeight="1">
-      <c r="B42" s="77" t="inlineStr">
+      <c r="B42" s="78" t="inlineStr">
         <is>
           <t>Подпись плательщика  ______________________</t>
         </is>
       </c>
-      <c r="C42" s="77" t="n"/>
-      <c r="D42" s="77" t="n"/>
-      <c r="E42" s="77" t="inlineStr">
+      <c r="C42" s="78" t="n"/>
+      <c r="D42" s="78" t="n"/>
+      <c r="E42" s="78" t="inlineStr">
         <is>
           <t>Кассир  ______________</t>
         </is>
       </c>
-      <c r="F42" s="77" t="n"/>
-      <c r="G42" s="77" t="inlineStr">
+      <c r="F42" s="78" t="n"/>
+      <c r="G42" s="78" t="inlineStr">
         <is>
           <t>Дата  ____________</t>
         </is>
       </c>
-      <c r="H42" s="77" t="n"/>
+      <c r="H42" s="78" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="B43" s="78">
+      <c r="B43" s="79">
         <f>"Начисление за "&amp;"III квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;"    По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
       </c>
-      <c r="C43" s="78" t="n"/>
-      <c r="D43" s="78" t="n"/>
-      <c r="E43" s="78" t="n"/>
-      <c r="F43" s="78" t="n"/>
-      <c r="G43" s="78" t="n"/>
-      <c r="H43" s="78" t="n"/>
+      <c r="C43" s="79" t="n"/>
+      <c r="D43" s="79" t="n"/>
+      <c r="E43" s="79" t="n"/>
+      <c r="F43" s="79" t="n"/>
+      <c r="G43" s="79" t="n"/>
+      <c r="H43" s="79" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="48">
@@ -34210,7 +34219,7 @@
   <sheetData>
     <row r="1" ht="6" customHeight="1"/>
     <row r="2" ht="40" customHeight="1">
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34233,462 +34242,462 @@
           </r>
         </is>
       </c>
-      <c r="C2" s="18" t="n"/>
-      <c r="D2" s="18" t="n"/>
-      <c r="E2" s="18" t="n"/>
-      <c r="F2" s="18" t="n"/>
-      <c r="G2" s="18" t="n"/>
-      <c r="H2" s="18" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
+      <c r="H2" s="19" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="B3" s="19">
+      <c r="B3" s="20">
         <f>"Специальный счёт МКД · "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14</f>
         <v/>
       </c>
-      <c r="C3" s="20" t="n"/>
-      <c r="D3" s="20" t="n"/>
-      <c r="E3" s="20" t="n"/>
-      <c r="F3" s="21">
+      <c r="C3" s="21" t="n"/>
+      <c r="D3" s="21" t="n"/>
+      <c r="E3" s="21" t="n"/>
+      <c r="F3" s="22">
         <f>"Расчётный период: "&amp;"IV квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G3" s="21" t="n"/>
-      <c r="H3" s="22" t="n"/>
+      <c r="G3" s="22" t="n"/>
+      <c r="H3" s="23" t="n"/>
     </row>
     <row r="4" ht="5" customHeight="1"/>
     <row r="5" ht="16" customHeight="1">
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>1. ПОЛУЧАТЕЛЬ ПЛАТЕЖА — ВЛАДЕЛЕЦ СПЕЦИАЛЬНОГО СЧЁТА</t>
         </is>
       </c>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="24" t="n"/>
-      <c r="G5" s="24" t="n"/>
-      <c r="H5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="26" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>Получатель платежа</t>
         </is>
       </c>
-      <c r="C6" s="27">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$39</f>
-        <v/>
-      </c>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="27" t="n"/>
-      <c r="G6" s="27" t="n"/>
-      <c r="H6" s="28" t="n"/>
-    </row>
-    <row r="7" ht="14" customHeight="1">
-      <c r="B7" s="29" t="inlineStr">
-        <is>
-          <t>Юридический адрес</t>
-        </is>
-      </c>
-      <c r="C7" s="30">
+      <c r="C6" s="28">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$40</f>
         <v/>
       </c>
-      <c r="D7" s="30" t="n"/>
-      <c r="E7" s="30" t="n"/>
-      <c r="F7" s="30" t="n"/>
-      <c r="G7" s="30" t="n"/>
-      <c r="H7" s="31" t="n"/>
+      <c r="D6" s="28" t="n"/>
+      <c r="E6" s="28" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="28" t="n"/>
+      <c r="H6" s="29" t="n"/>
+    </row>
+    <row r="7" ht="14" customHeight="1">
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Юридический адрес</t>
+        </is>
+      </c>
+      <c r="C7" s="31">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$41</f>
+        <v/>
+      </c>
+      <c r="D7" s="31" t="n"/>
+      <c r="E7" s="31" t="n"/>
+      <c r="F7" s="31" t="n"/>
+      <c r="G7" s="31" t="n"/>
+      <c r="H7" s="32" t="n"/>
     </row>
     <row r="8" ht="14" customHeight="1">
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>ИНН / КПП</t>
         </is>
       </c>
-      <c r="C8" s="30">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$41&amp;" / "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$42</f>
+      <c r="C8" s="31">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$42&amp;" / "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$43</f>
         <v/>
       </c>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="32" t="inlineStr">
+      <c r="D8" s="31" t="n"/>
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>ОГРН</t>
         </is>
       </c>
-      <c r="F8" s="30">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$43</f>
+      <c r="F8" s="31">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$44</f>
         <v/>
       </c>
-      <c r="G8" s="30" t="n"/>
-      <c r="H8" s="31" t="n"/>
+      <c r="G8" s="31" t="n"/>
+      <c r="H8" s="32" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Расчётный счёт</t>
         </is>
       </c>
-      <c r="C9" s="33">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;"   (специальный счёт МКД: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;")"</f>
+      <c r="C9" s="34">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;"   (специальный счёт МКД: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;")"</f>
         <v/>
       </c>
-      <c r="D9" s="33" t="n"/>
-      <c r="E9" s="33" t="n"/>
-      <c r="F9" s="33" t="n"/>
-      <c r="G9" s="33" t="n"/>
-      <c r="H9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="34" t="n"/>
+      <c r="H9" s="35" t="n"/>
     </row>
     <row r="10" ht="14" customHeight="1">
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Банк</t>
         </is>
       </c>
-      <c r="C10" s="30">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$45</f>
+      <c r="C10" s="31">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$46</f>
         <v/>
       </c>
-      <c r="D10" s="30" t="n"/>
-      <c r="E10" s="30" t="n"/>
-      <c r="F10" s="30" t="n"/>
-      <c r="G10" s="30" t="n"/>
-      <c r="H10" s="31" t="n"/>
+      <c r="D10" s="31" t="n"/>
+      <c r="E10" s="31" t="n"/>
+      <c r="F10" s="31" t="n"/>
+      <c r="G10" s="31" t="n"/>
+      <c r="H10" s="32" t="n"/>
     </row>
     <row r="11" ht="14" customHeight="1">
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>Корр. счёт / БИК</t>
         </is>
       </c>
-      <c r="C11" s="36">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$46&amp;" / "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$47</f>
+      <c r="C11" s="37">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$47&amp;" / "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$48</f>
         <v/>
       </c>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="37" t="inlineStr">
+      <c r="D11" s="37" t="n"/>
+      <c r="E11" s="38" t="inlineStr">
         <is>
           <t>ИНН/КПП банка</t>
         </is>
       </c>
-      <c r="F11" s="36">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$48</f>
+      <c r="F11" s="37">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$49</f>
         <v/>
       </c>
-      <c r="G11" s="36" t="n"/>
-      <c r="H11" s="38" t="n"/>
+      <c r="G11" s="37" t="n"/>
+      <c r="H11" s="39" t="n"/>
     </row>
     <row r="12" ht="5" customHeight="1"/>
     <row r="13" ht="16" customHeight="1">
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>2. ПЛАТЕЛЬЩИК И ПОМЕЩЕНИЕ</t>
         </is>
       </c>
-      <c r="C13" s="24" t="n"/>
-      <c r="D13" s="24" t="n"/>
-      <c r="E13" s="24" t="n"/>
-      <c r="F13" s="24" t="n"/>
-      <c r="G13" s="24" t="n"/>
-      <c r="H13" s="25" t="n"/>
+      <c r="C13" s="25" t="n"/>
+      <c r="D13" s="25" t="n"/>
+      <c r="E13" s="25" t="n"/>
+      <c r="F13" s="25" t="n"/>
+      <c r="G13" s="25" t="n"/>
+      <c r="H13" s="26" t="n"/>
     </row>
     <row r="14" ht="19" customHeight="1">
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>Лицевой счёт</t>
         </is>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="40">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$11</f>
         <v/>
       </c>
-      <c r="D14" s="32" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>Квартира №</t>
         </is>
       </c>
-      <c r="E14" s="40">
+      <c r="E14" s="41">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$12</f>
         <v/>
       </c>
-      <c r="F14" s="41" t="inlineStr">
+      <c r="F14" s="42" t="inlineStr">
         <is>
           <t>Дата формирования</t>
         </is>
       </c>
-      <c r="G14" s="42">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$E$33</f>
+      <c r="G14" s="43">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$E$34</f>
         <v/>
       </c>
-      <c r="H14" s="43" t="n"/>
+      <c r="H14" s="44" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="B15" s="29" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>Плательщик</t>
         </is>
       </c>
-      <c r="C15" s="33">
+      <c r="C15" s="34">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$13</f>
         <v/>
       </c>
-      <c r="D15" s="33" t="n"/>
-      <c r="E15" s="33" t="n"/>
-      <c r="F15" s="33" t="n"/>
-      <c r="G15" s="33" t="n"/>
-      <c r="H15" s="34" t="n"/>
+      <c r="D15" s="34" t="n"/>
+      <c r="E15" s="34" t="n"/>
+      <c r="F15" s="34" t="n"/>
+      <c r="G15" s="34" t="n"/>
+      <c r="H15" s="35" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>Адрес помещения</t>
         </is>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", кв. "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12</f>
         <v/>
       </c>
-      <c r="D16" s="30" t="n"/>
-      <c r="E16" s="30" t="n"/>
-      <c r="F16" s="30" t="n"/>
-      <c r="G16" s="30" t="n"/>
-      <c r="H16" s="31" t="n"/>
+      <c r="D16" s="31" t="n"/>
+      <c r="E16" s="31" t="n"/>
+      <c r="F16" s="31" t="n"/>
+      <c r="G16" s="31" t="n"/>
+      <c r="H16" s="32" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="B17" s="44" t="inlineStr">
+      <c r="B17" s="45" t="inlineStr">
         <is>
           <t>Площадь помещения, м²</t>
         </is>
       </c>
-      <c r="C17" s="45">
+      <c r="C17" s="46">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$6</f>
         <v/>
       </c>
-      <c r="D17" s="46" t="inlineStr">
+      <c r="D17" s="47" t="inlineStr">
         <is>
           <t>Размер взноса, руб./м²</t>
         </is>
       </c>
-      <c r="E17" s="47">
+      <c r="E17" s="48">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$7</f>
         <v/>
       </c>
-      <c r="F17" s="37" t="inlineStr">
+      <c r="F17" s="38" t="inlineStr">
         <is>
           <t>Период оплаты</t>
         </is>
       </c>
-      <c r="G17" s="48">
+      <c r="G17" s="49">
         <f>"IV квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="H17" s="49" t="n"/>
+      <c r="H17" s="50" t="n"/>
     </row>
     <row r="18" ht="5" customHeight="1"/>
     <row r="19" ht="16" customHeight="1">
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>3. РАСЧЁТ РАЗМЕРА ВЗНОСА И СУММЫ К ОПЛАТЕ</t>
         </is>
       </c>
-      <c r="C19" s="24" t="n"/>
-      <c r="D19" s="24" t="n"/>
-      <c r="E19" s="24" t="n"/>
-      <c r="F19" s="24" t="n"/>
-      <c r="G19" s="24" t="n"/>
-      <c r="H19" s="25" t="n"/>
+      <c r="C19" s="25" t="n"/>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="25" t="n"/>
+      <c r="G19" s="25" t="n"/>
+      <c r="H19" s="26" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="50" t="inlineStr">
+      <c r="B20" s="51" t="inlineStr">
         <is>
           <t>Вид платежа</t>
         </is>
       </c>
-      <c r="C20" s="51" t="n"/>
-      <c r="D20" s="51" t="n"/>
-      <c r="E20" s="51" t="n"/>
-      <c r="F20" s="51" t="inlineStr">
+      <c r="C20" s="52" t="n"/>
+      <c r="D20" s="52" t="n"/>
+      <c r="E20" s="52" t="n"/>
+      <c r="F20" s="52" t="inlineStr">
         <is>
           <t>Расчётный период</t>
         </is>
       </c>
-      <c r="G20" s="51" t="n"/>
-      <c r="H20" s="52" t="inlineStr">
+      <c r="G20" s="52" t="n"/>
+      <c r="H20" s="53" t="inlineStr">
         <is>
           <t>Сумма, руб.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="B21" s="53" t="inlineStr">
+      <c r="B21" s="54" t="inlineStr">
         <is>
           <t>Взнос на капитальный ремонт (площадь × размер взноса)</t>
         </is>
       </c>
-      <c r="C21" s="30" t="n"/>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="30" t="n"/>
-      <c r="F21" s="54">
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+      <c r="E21" s="31" t="n"/>
+      <c r="F21" s="55">
         <f>"октябрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G21" s="54" t="n"/>
-      <c r="H21" s="55">
+      <c r="G21" s="55" t="n"/>
+      <c r="H21" s="56">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$8</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="B22" s="53" t="inlineStr">
+      <c r="B22" s="54" t="inlineStr">
         <is>
           <t>Взнос на капитальный ремонт (площадь × размер взноса)</t>
         </is>
       </c>
-      <c r="C22" s="30" t="n"/>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="30" t="n"/>
-      <c r="F22" s="54">
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+      <c r="E22" s="31" t="n"/>
+      <c r="F22" s="55">
         <f>"ноябрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G22" s="54" t="n"/>
-      <c r="H22" s="55">
+      <c r="G22" s="55" t="n"/>
+      <c r="H22" s="56">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$8</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="B23" s="53" t="inlineStr">
+      <c r="B23" s="54" t="inlineStr">
         <is>
           <t>Взнос на капитальный ремонт (площадь × размер взноса)</t>
         </is>
       </c>
-      <c r="C23" s="30" t="n"/>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="30" t="n"/>
-      <c r="F23" s="54">
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+      <c r="E23" s="31" t="n"/>
+      <c r="F23" s="55">
         <f>"декабрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G23" s="54" t="n"/>
-      <c r="H23" s="55">
+      <c r="G23" s="55" t="n"/>
+      <c r="H23" s="56">
         <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$8</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="B24" s="56" t="inlineStr">
+      <c r="B24" s="57" t="inlineStr">
         <is>
           <t>Итого начислено за квартал</t>
         </is>
       </c>
-      <c r="C24" s="57" t="n"/>
-      <c r="D24" s="57" t="n"/>
-      <c r="E24" s="57" t="n"/>
-      <c r="F24" s="58">
+      <c r="C24" s="58" t="n"/>
+      <c r="D24" s="58" t="n"/>
+      <c r="E24" s="58" t="n"/>
+      <c r="F24" s="59">
         <f>"IV квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="G24" s="58" t="n"/>
-      <c r="H24" s="59">
+      <c r="G24" s="59" t="n"/>
+      <c r="H24" s="60">
         <f>ROUND(SUM(H21:H23),2)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="B25" s="53" t="inlineStr">
+      <c r="B25" s="54" t="inlineStr">
         <is>
           <t>Задолженность за предыдущие периоды</t>
         </is>
       </c>
-      <c r="C25" s="30" t="n"/>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="30" t="n"/>
-      <c r="F25" s="60">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$D$33="","",'ИСХОДНЫЕ ДАННЫЕ'!$D$33)</f>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+      <c r="E25" s="31" t="n"/>
+      <c r="F25" s="61">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$D$34="","",'ИСХОДНЫЕ ДАННЫЕ'!$D$34)</f>
         <v/>
       </c>
-      <c r="G25" s="60" t="n"/>
-      <c r="H25" s="55">
-        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$33</f>
+      <c r="G25" s="61" t="n"/>
+      <c r="H25" s="56">
+        <f>'ИСХОДНЫЕ ДАННЫЕ'!$C$34</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="B26" s="61" t="inlineStr">
+      <c r="B26" s="62" t="inlineStr">
         <is>
           <t>ИТОГО К ОПЛАТЕ</t>
         </is>
       </c>
-      <c r="C26" s="62" t="n"/>
-      <c r="D26" s="62" t="n"/>
-      <c r="E26" s="62" t="n"/>
-      <c r="F26" s="62" t="n"/>
-      <c r="G26" s="62" t="n"/>
-      <c r="H26" s="63">
+      <c r="C26" s="63" t="n"/>
+      <c r="D26" s="63" t="n"/>
+      <c r="E26" s="63" t="n"/>
+      <c r="F26" s="63" t="n"/>
+      <c r="G26" s="63" t="n"/>
+      <c r="H26" s="64">
         <f>ROUND(H24+H25,2)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="5" customHeight="1"/>
     <row r="28" ht="16" customHeight="1">
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>4. СПРАВОЧНАЯ ИНФОРМАЦИЯ ПО СПЕЦИАЛЬНОМУ СЧЁТУ (ч. 7 ст. 177 ЖК РФ)</t>
         </is>
       </c>
-      <c r="C28" s="24" t="n"/>
-      <c r="D28" s="24" t="n"/>
-      <c r="E28" s="24" t="n"/>
-      <c r="F28" s="24" t="n"/>
-      <c r="G28" s="24" t="n"/>
-      <c r="H28" s="25" t="n"/>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="25" t="n"/>
+      <c r="G28" s="25" t="n"/>
+      <c r="H28" s="26" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
-      <c r="B29" s="64">
+      <c r="B29" s="65">
         <f>"Поступило оплат по лицевому счёту с начала "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года, руб."</f>
         <v/>
       </c>
-      <c r="C29" s="36" t="n"/>
-      <c r="D29" s="36" t="n"/>
-      <c r="E29" s="36" t="n"/>
-      <c r="F29" s="36" t="n"/>
-      <c r="G29" s="65">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$F$33="","—",'ИСХОДНЫЕ ДАННЫЕ'!$F$33)</f>
+      <c r="C29" s="37" t="n"/>
+      <c r="D29" s="37" t="n"/>
+      <c r="E29" s="37" t="n"/>
+      <c r="F29" s="37" t="n"/>
+      <c r="G29" s="66">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$F$34="","—",'ИСХОДНЫЕ ДАННЫЕ'!$F$34)</f>
         <v/>
       </c>
-      <c r="H29" s="66" t="n"/>
+      <c r="H29" s="67" t="n"/>
     </row>
     <row r="30" ht="5" customHeight="1"/>
     <row r="31" ht="16" customHeight="1">
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>5. ПОРЯДОК ОПЛАТЫ</t>
         </is>
       </c>
-      <c r="C31" s="24" t="n"/>
-      <c r="D31" s="24" t="n"/>
-      <c r="E31" s="24" t="n"/>
-      <c r="F31" s="24" t="n"/>
-      <c r="G31" s="24" t="n"/>
-      <c r="H31" s="25" t="n"/>
+      <c r="C31" s="25" t="n"/>
+      <c r="D31" s="25" t="n"/>
+      <c r="E31" s="25" t="n"/>
+      <c r="F31" s="25" t="n"/>
+      <c r="G31" s="25" t="n"/>
+      <c r="H31" s="26" t="n"/>
     </row>
     <row r="32" ht="14" customHeight="1">
-      <c r="B32" s="67" t="inlineStr">
+      <c r="B32" s="68" t="inlineStr">
         <is>
           <t>1) без комиссии — в отделениях АО «Россельхозбанк» (банк, в котором открыт специальный счёт дома);</t>
         </is>
       </c>
-      <c r="C32" s="68" t="n"/>
-      <c r="D32" s="68" t="n"/>
-      <c r="E32" s="68" t="n"/>
-      <c r="F32" s="68" t="n"/>
-      <c r="G32" s="69" t="n"/>
-      <c r="H32" s="70" t="n"/>
+      <c r="C32" s="69" t="n"/>
+      <c r="D32" s="69" t="n"/>
+      <c r="E32" s="69" t="n"/>
+      <c r="F32" s="69" t="n"/>
+      <c r="G32" s="70" t="n"/>
+      <c r="H32" s="71" t="n"/>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="B33" s="67" t="inlineStr">
+      <c r="B33" s="68" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34717,117 +34726,117 @@
           </r>
         </is>
       </c>
-      <c r="C33" s="68" t="n"/>
-      <c r="D33" s="68" t="n"/>
-      <c r="E33" s="68" t="n"/>
-      <c r="F33" s="68" t="n"/>
-      <c r="G33" s="69" t="n"/>
-      <c r="H33" s="70" t="n"/>
+      <c r="C33" s="69" t="n"/>
+      <c r="D33" s="69" t="n"/>
+      <c r="E33" s="69" t="n"/>
+      <c r="F33" s="69" t="n"/>
+      <c r="G33" s="70" t="n"/>
+      <c r="H33" s="71" t="n"/>
     </row>
     <row r="34" ht="14" customHeight="1">
-      <c r="B34" s="67" t="n"/>
-      <c r="C34" s="68" t="n"/>
-      <c r="D34" s="68" t="n"/>
-      <c r="E34" s="68" t="n"/>
-      <c r="F34" s="68" t="n"/>
-      <c r="G34" s="69" t="n"/>
-      <c r="H34" s="70" t="n"/>
+      <c r="B34" s="68" t="n"/>
+      <c r="C34" s="69" t="n"/>
+      <c r="D34" s="69" t="n"/>
+      <c r="E34" s="69" t="n"/>
+      <c r="F34" s="69" t="n"/>
+      <c r="G34" s="70" t="n"/>
+      <c r="H34" s="71" t="n"/>
     </row>
     <row r="35" ht="14" customHeight="1">
-      <c r="B35" s="29" t="inlineStr">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>Назначение платежа:</t>
         </is>
       </c>
-      <c r="C35" s="32" t="n"/>
-      <c r="D35" s="32" t="n"/>
-      <c r="E35" s="32" t="n"/>
-      <c r="F35" s="32" t="n"/>
-      <c r="G35" s="69" t="n"/>
-      <c r="H35" s="70" t="n"/>
+      <c r="C35" s="33" t="n"/>
+      <c r="D35" s="33" t="n"/>
+      <c r="E35" s="33" t="n"/>
+      <c r="F35" s="33" t="n"/>
+      <c r="G35" s="70" t="n"/>
+      <c r="H35" s="71" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="B36" s="67">
+      <c r="B36" s="68">
         <f>"Взнос на капитальный ремонт, л/с № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;", кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;", за "&amp;"IV квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="C36" s="68" t="n"/>
-      <c r="D36" s="68" t="n"/>
-      <c r="E36" s="68" t="n"/>
-      <c r="F36" s="68" t="n"/>
-      <c r="G36" s="69" t="n"/>
-      <c r="H36" s="70" t="n"/>
+      <c r="C36" s="69" t="n"/>
+      <c r="D36" s="69" t="n"/>
+      <c r="E36" s="69" t="n"/>
+      <c r="F36" s="69" t="n"/>
+      <c r="G36" s="70" t="n"/>
+      <c r="H36" s="71" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="B37" s="71">
-        <f>"Срок оплаты: до "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$49&amp;" числа месяца, следующего за расчётным (за "&amp;"IV квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — до "&amp;TEXT(DAY(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,12+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49)),"00")&amp;"."&amp;TEXT(MONTH(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,12+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49)),"00")&amp;"."&amp;YEAR(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,12+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$49))&amp;")."&amp;CHAR(10)&amp;"Основание: ч. 1 ст. 155, ч. 2 ст. 171 ЖК РФ."</f>
+      <c r="B37" s="72">
+        <f>"Срок оплаты: до "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$50&amp;" числа месяца, следующего за расчётным (за "&amp;"IV квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — до "&amp;TEXT(DAY(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,12+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$50)),"00")&amp;"."&amp;TEXT(MONTH(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,12+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$50)),"00")&amp;"."&amp;YEAR(DATE('ИСХОДНЫЕ ДАННЫЕ'!$C$5,12+1,'ИСХОДНЫЕ ДАННЫЕ'!$C$50))&amp;")."&amp;CHAR(10)&amp;"Основание: ч. 1 ст. 155, ч. 2 ст. 171 ЖК РФ."</f>
         <v/>
       </c>
-      <c r="C37" s="72" t="n"/>
-      <c r="D37" s="72" t="n"/>
-      <c r="E37" s="72" t="n"/>
-      <c r="F37" s="72" t="n"/>
-      <c r="G37" s="73" t="n"/>
-      <c r="H37" s="74" t="n"/>
+      <c r="C37" s="73" t="n"/>
+      <c r="D37" s="73" t="n"/>
+      <c r="E37" s="73" t="n"/>
+      <c r="F37" s="73" t="n"/>
+      <c r="G37" s="74" t="n"/>
+      <c r="H37" s="75" t="n"/>
     </row>
     <row r="38" ht="5" customHeight="1"/>
     <row r="39" ht="32" customHeight="1">
-      <c r="B39" s="75">
-        <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
+      <c r="B39" s="76">
+        <f>"ВНИМАНИЕ! ПЛАТИТЕ ТОЛЬКО ПО НОМЕРУ РАСЧЁТНОГО СЧЁТА "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;" — ЭТО СПЕЦИАЛЬНЫЙ СЧЁТ ВАШЕГО ДОМА"</f>
         <v/>
       </c>
-      <c r="C39" s="75" t="n"/>
-      <c r="D39" s="75" t="n"/>
-      <c r="E39" s="75" t="n"/>
-      <c r="F39" s="75" t="n"/>
-      <c r="G39" s="75" t="n"/>
-      <c r="H39" s="75" t="n"/>
+      <c r="C39" s="76" t="n"/>
+      <c r="D39" s="76" t="n"/>
+      <c r="E39" s="76" t="n"/>
+      <c r="F39" s="76" t="n"/>
+      <c r="G39" s="76" t="n"/>
+      <c r="H39" s="76" t="n"/>
     </row>
     <row r="40" ht="44" customHeight="1">
-      <c r="B40" s="76">
+      <c r="B40" s="77">
         <f>"В отделении банка и в мобильном приложении во вкладках ищите "&amp;"«РФКР МКД_капремонт, оплата по расчётному счёту» и указывайте номер расчётного счёта, приведённый выше. Оплата через общий поиск «Капитальный ремонт» уходит на общий счёт Регионального фонда капитального ремонта и на счёт вашего дома не поступает."&amp;CHAR(10)&amp;"Лицевой счёт № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$11&amp;" при оплате НЕ вводится — он указан справочно, только для учёта начислений."</f>
         <v/>
       </c>
-      <c r="C40" s="76" t="n"/>
-      <c r="D40" s="76" t="n"/>
-      <c r="E40" s="76" t="n"/>
-      <c r="F40" s="76" t="n"/>
-      <c r="G40" s="76" t="n"/>
-      <c r="H40" s="76" t="n"/>
+      <c r="C40" s="77" t="n"/>
+      <c r="D40" s="77" t="n"/>
+      <c r="E40" s="77" t="n"/>
+      <c r="F40" s="77" t="n"/>
+      <c r="G40" s="77" t="n"/>
+      <c r="H40" s="77" t="n"/>
     </row>
     <row r="41" ht="6" customHeight="1"/>
     <row r="42" ht="24" customHeight="1">
-      <c r="B42" s="77" t="inlineStr">
+      <c r="B42" s="78" t="inlineStr">
         <is>
           <t>Подпись плательщика  ______________________</t>
         </is>
       </c>
-      <c r="C42" s="77" t="n"/>
-      <c r="D42" s="77" t="n"/>
-      <c r="E42" s="77" t="inlineStr">
+      <c r="C42" s="78" t="n"/>
+      <c r="D42" s="78" t="n"/>
+      <c r="E42" s="78" t="inlineStr">
         <is>
           <t>Кассир  ______________</t>
         </is>
       </c>
-      <c r="F42" s="77" t="n"/>
-      <c r="G42" s="77" t="inlineStr">
+      <c r="F42" s="78" t="n"/>
+      <c r="G42" s="78" t="inlineStr">
         <is>
           <t>Дата  ____________</t>
         </is>
       </c>
-      <c r="H42" s="77" t="n"/>
+      <c r="H42" s="78" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="B43" s="78">
+      <c r="B43" s="79">
         <f>"Начисление за "&amp;"IV квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;"    По вопросам начислений обращайтесь к председателю совета дома, тел. "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
       </c>
-      <c r="C43" s="78" t="n"/>
-      <c r="D43" s="78" t="n"/>
-      <c r="E43" s="78" t="n"/>
-      <c r="F43" s="78" t="n"/>
-      <c r="G43" s="78" t="n"/>
-      <c r="H43" s="78" t="n"/>
+      <c r="C43" s="79" t="n"/>
+      <c r="D43" s="79" t="n"/>
+      <c r="E43" s="79" t="n"/>
+      <c r="F43" s="79" t="n"/>
+      <c r="G43" s="79" t="n"/>
+      <c r="H43" s="79" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="48">
@@ -34896,198 +34905,198 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="0.8" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="0.8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="D1" s="79">
-        <f>"В "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$24</f>
+      <c r="D1" s="80">
+        <f>"В "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$25</f>
         <v/>
       </c>
-      <c r="E1" s="79" t="n"/>
-      <c r="F1" s="79" t="n"/>
+      <c r="E1" s="80" t="n"/>
+      <c r="F1" s="80" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="D2" s="79">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$26="","",'ИСХОДНЫЕ ДАННЫЕ'!$C$25&amp;" "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$26)</f>
+      <c r="D2" s="80">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$27="","",'ИСХОДНЫЕ ДАННЫЕ'!$C$26&amp;" "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$27)</f>
         <v/>
       </c>
-      <c r="E2" s="79" t="n"/>
-      <c r="F2" s="79" t="n"/>
+      <c r="E2" s="80" t="n"/>
+      <c r="F2" s="80" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="D3" s="80">
+      <c r="D3" s="81">
         <f>"от Председателя МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;", "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$18</f>
         <v/>
       </c>
-      <c r="E3" s="80" t="n"/>
-      <c r="F3" s="80" t="n"/>
+      <c r="E3" s="81" t="n"/>
+      <c r="F3" s="81" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="D4" s="80">
+      <c r="D4" s="81">
         <f>"проживающей по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$20</f>
         <v/>
       </c>
-      <c r="E4" s="80" t="n"/>
-      <c r="F4" s="80" t="n"/>
+      <c r="E4" s="81" t="n"/>
+      <c r="F4" s="81" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="D5" s="80">
+      <c r="D5" s="81">
         <f>"Конт. тел.: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21</f>
         <v/>
       </c>
-      <c r="E5" s="80" t="n"/>
-      <c r="F5" s="80" t="n"/>
+      <c r="E5" s="81" t="n"/>
+      <c r="F5" s="81" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="D6" s="80">
+      <c r="D6" s="81">
         <f>"Эл. почта: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22</f>
         <v/>
       </c>
-      <c r="E6" s="80" t="n"/>
-      <c r="F6" s="80" t="n"/>
+      <c r="E6" s="81" t="n"/>
+      <c r="F6" s="81" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1"/>
     <row r="8" ht="54" customHeight="1">
-      <c r="B8" s="80">
-        <f>"В связи с тем, что на балансе департамента числится кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", сообщаю Вам о необходимости оплатить "&amp;IF(INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2)*100,0)-INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$30,2),2))*100),"00")&amp;" руб., в том числе:"</f>
+      <c r="B8" s="81">
+        <f>"В связи с тем, что на балансе департамента числится кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", сообщаю Вам о необходимости оплатить "&amp;IF(INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2)*100,0)-INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))*100),"00")&amp;" руб., в том числе:"</f>
         <v/>
       </c>
-      <c r="C8" s="80" t="n"/>
-      <c r="D8" s="80" t="n"/>
-      <c r="E8" s="80" t="n"/>
-      <c r="F8" s="80" t="n"/>
+      <c r="C8" s="81" t="n"/>
+      <c r="D8" s="81" t="n"/>
+      <c r="E8" s="81" t="n"/>
+      <c r="F8" s="81" t="n"/>
     </row>
     <row r="9" ht="8" customHeight="1"/>
     <row r="10" ht="38" customHeight="1">
-      <c r="B10" s="80">
+      <c r="B10" s="81">
         <f>"— текущий платёж за период с января по март "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года ("&amp;"I квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;") в размере "&amp;IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100),"00")&amp;" рублей"</f>
         <v/>
       </c>
-      <c r="C10" s="80" t="n"/>
-      <c r="D10" s="80" t="n"/>
-      <c r="E10" s="80" t="n"/>
-      <c r="F10" s="80" t="n"/>
+      <c r="C10" s="81" t="n"/>
+      <c r="D10" s="81" t="n"/>
+      <c r="E10" s="81" t="n"/>
+      <c r="F10" s="81" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="81">
+      <c r="B11" s="82">
         <f>"("&amp;UPPER(LEFT(IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)=0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)=0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1),2,300)&amp;")."</f>
         <v/>
       </c>
-      <c r="C11" s="81" t="n"/>
-      <c r="D11" s="81" t="n"/>
-      <c r="E11" s="81" t="n"/>
-      <c r="F11" s="81" t="n"/>
+      <c r="C11" s="82" t="n"/>
+      <c r="D11" s="82" t="n"/>
+      <c r="E11" s="82" t="n"/>
+      <c r="F11" s="82" t="n"/>
     </row>
     <row r="12" ht="6" customHeight="1"/>
     <row r="13" ht="32" customHeight="1">
-      <c r="B13" s="80">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$30=0,"— задолженности за предыдущие периоды нет.","— задолженность "&amp;IF('ИСХОДНЫЕ ДАННЫЕ'!$D$30="","за предыдущие периоды",'ИСХОДНЫЕ ДАННЫЕ'!$D$30)&amp;" в размере "&amp;IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)&gt;0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)&amp;" "&amp;TEXT((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)*1000),"000"),(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))*100),"00")&amp;" рублей")</f>
+      <c r="B13" s="81">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$31=0,"— задолженности за предыдущие периоды нет.","— задолженность "&amp;IF('ИСХОДНЫЕ ДАННЫЕ'!$D$31="","за предыдущие периоды",'ИСХОДНЫЕ ДАННЫЕ'!$D$31)&amp;" в размере "&amp;IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)&gt;0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)&amp;" "&amp;TEXT((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000),"000"),(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))*100),"00")&amp;" рублей")</f>
         <v/>
       </c>
-      <c r="C13" s="80" t="n"/>
-      <c r="D13" s="80" t="n"/>
-      <c r="E13" s="80" t="n"/>
-      <c r="F13" s="80" t="n"/>
+      <c r="C13" s="81" t="n"/>
+      <c r="D13" s="81" t="n"/>
+      <c r="E13" s="81" t="n"/>
+      <c r="F13" s="81" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="81">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$30=0,"","("&amp;UPPER(LEFT(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$30,2))*100)+1),2,300)&amp;").")</f>
+      <c r="B14" s="82">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$31=0,"","("&amp;UPPER(LEFT(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))*100)+1),2,300)&amp;").")</f>
         <v/>
       </c>
-      <c r="C14" s="81" t="n"/>
-      <c r="D14" s="81" t="n"/>
-      <c r="E14" s="81" t="n"/>
-      <c r="F14" s="81" t="n"/>
+      <c r="C14" s="82" t="n"/>
+      <c r="D14" s="82" t="n"/>
+      <c r="E14" s="82" t="n"/>
+      <c r="F14" s="82" t="n"/>
     </row>
     <row r="15" ht="10" customHeight="1"/>
     <row r="16" ht="90" customHeight="1">
-      <c r="B16" s="80">
-        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$30),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$30),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$30)&amp;" и с учётом начислений по "&amp;"март "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
+      <c r="B16" s="81">
+        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$31)&amp;" и с учётом начислений по "&amp;"март "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
       </c>
-      <c r="C16" s="80" t="n"/>
-      <c r="D16" s="80" t="n"/>
-      <c r="E16" s="80" t="n"/>
-      <c r="F16" s="80" t="n"/>
+      <c r="C16" s="81" t="n"/>
+      <c r="D16" s="81" t="n"/>
+      <c r="E16" s="81" t="n"/>
+      <c r="F16" s="81" t="n"/>
     </row>
     <row r="17" ht="10" customHeight="1"/>
     <row r="18" ht="54" customHeight="1">
-      <c r="B18" s="80">
+      <c r="B18" s="81">
         <f>"В случае возникновения дополнительных вопросов прошу связаться со мной по электронной почте "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22&amp;" или по телефону "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
       </c>
-      <c r="C18" s="80" t="n"/>
-      <c r="D18" s="80" t="n"/>
-      <c r="E18" s="80" t="n"/>
-      <c r="F18" s="80" t="n"/>
+      <c r="C18" s="81" t="n"/>
+      <c r="D18" s="81" t="n"/>
+      <c r="E18" s="81" t="n"/>
+      <c r="F18" s="81" t="n"/>
     </row>
     <row r="19" ht="14" customHeight="1"/>
     <row r="20" ht="20" customHeight="1">
-      <c r="B20" s="79" t="inlineStr">
+      <c r="B20" s="80" t="inlineStr">
         <is>
           <t>ПРИЛОЖЕНИЯ:</t>
         </is>
       </c>
-      <c r="C20" s="79" t="n"/>
-      <c r="D20" s="79" t="n"/>
-      <c r="E20" s="79" t="n"/>
-      <c r="F20" s="79" t="n"/>
+      <c r="C20" s="80" t="n"/>
+      <c r="D20" s="80" t="n"/>
+      <c r="E20" s="80" t="n"/>
+      <c r="F20" s="80" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="80">
-        <f>"1) Акт взаимных расчётов по состоянию на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$30),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$30),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$30)&amp;" — один экземпляр на 1 л."</f>
+      <c r="B21" s="81">
+        <f>"1) Акт взаимных расчётов по состоянию на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$31)&amp;" — один экземпляр на 1 л."</f>
         <v/>
       </c>
-      <c r="C21" s="80" t="n"/>
-      <c r="D21" s="80" t="n"/>
-      <c r="E21" s="80" t="n"/>
-      <c r="F21" s="80" t="n"/>
+      <c r="C21" s="81" t="n"/>
+      <c r="D21" s="81" t="n"/>
+      <c r="E21" s="81" t="n"/>
+      <c r="F21" s="81" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="80">
+      <c r="B22" s="81">
         <f>"2) Квитанция для оплаты за "&amp;"I квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — один экземпляр на 1 л."</f>
         <v/>
       </c>
-      <c r="C22" s="80" t="n"/>
-      <c r="D22" s="80" t="n"/>
-      <c r="E22" s="80" t="n"/>
-      <c r="F22" s="80" t="n"/>
+      <c r="C22" s="81" t="n"/>
+      <c r="D22" s="81" t="n"/>
+      <c r="E22" s="81" t="n"/>
+      <c r="F22" s="81" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1"/>
     <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="80">
+      <c r="B24" s="81">
         <f>"«______» ______________ "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="C24" s="80" t="n"/>
+      <c r="C24" s="81" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1"/>
     <row r="26" ht="16" customHeight="1">
-      <c r="B26" s="80" t="inlineStr">
+      <c r="B26" s="81" t="inlineStr">
         <is>
           <t>Председатель</t>
         </is>
       </c>
-      <c r="C26" s="80" t="n"/>
+      <c r="C26" s="81" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="B27" s="80">
+      <c r="B27" s="81">
         <f>"МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15</f>
         <v/>
       </c>
-      <c r="C27" s="80" t="n"/>
-      <c r="D27" s="82">
+      <c r="C27" s="81" t="n"/>
+      <c r="D27" s="83">
         <f>"___________________  /"&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$19&amp;"/"</f>
         <v/>
       </c>
-      <c r="E27" s="82" t="n"/>
-      <c r="F27" s="82" t="n"/>
+      <c r="E27" s="83" t="n"/>
+      <c r="F27" s="83" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -35112,7 +35121,7 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="D6:F6"/>
   </mergeCells>
-  <pageMargins left="0.79" right="0.39" top="0.59" bottom="0.59" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.39" top="0.51" bottom="0.51" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
@@ -35127,198 +35136,198 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="0.8" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="0.8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="D1" s="79">
-        <f>"В "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$24</f>
+      <c r="D1" s="80">
+        <f>"В "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$25</f>
         <v/>
       </c>
-      <c r="E1" s="79" t="n"/>
-      <c r="F1" s="79" t="n"/>
+      <c r="E1" s="80" t="n"/>
+      <c r="F1" s="80" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="D2" s="79">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$26="","",'ИСХОДНЫЕ ДАННЫЕ'!$C$25&amp;" "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$26)</f>
+      <c r="D2" s="80">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$27="","",'ИСХОДНЫЕ ДАННЫЕ'!$C$26&amp;" "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$27)</f>
         <v/>
       </c>
-      <c r="E2" s="79" t="n"/>
-      <c r="F2" s="79" t="n"/>
+      <c r="E2" s="80" t="n"/>
+      <c r="F2" s="80" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="D3" s="80">
+      <c r="D3" s="81">
         <f>"от Председателя МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;", "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$18</f>
         <v/>
       </c>
-      <c r="E3" s="80" t="n"/>
-      <c r="F3" s="80" t="n"/>
+      <c r="E3" s="81" t="n"/>
+      <c r="F3" s="81" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="D4" s="80">
+      <c r="D4" s="81">
         <f>"проживающей по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$20</f>
         <v/>
       </c>
-      <c r="E4" s="80" t="n"/>
-      <c r="F4" s="80" t="n"/>
+      <c r="E4" s="81" t="n"/>
+      <c r="F4" s="81" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="D5" s="80">
+      <c r="D5" s="81">
         <f>"Конт. тел.: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21</f>
         <v/>
       </c>
-      <c r="E5" s="80" t="n"/>
-      <c r="F5" s="80" t="n"/>
+      <c r="E5" s="81" t="n"/>
+      <c r="F5" s="81" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="D6" s="80">
+      <c r="D6" s="81">
         <f>"Эл. почта: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22</f>
         <v/>
       </c>
-      <c r="E6" s="80" t="n"/>
-      <c r="F6" s="80" t="n"/>
+      <c r="E6" s="81" t="n"/>
+      <c r="F6" s="81" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1"/>
     <row r="8" ht="54" customHeight="1">
-      <c r="B8" s="80">
-        <f>"В связи с тем, что на балансе департамента числится кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", сообщаю Вам о необходимости оплатить "&amp;IF(INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2)*100,0)-INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$31,2),2))*100),"00")&amp;" руб., в том числе:"</f>
+      <c r="B8" s="81">
+        <f>"В связи с тем, что на балансе департамента числится кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", сообщаю Вам о необходимости оплатить "&amp;IF(INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2)*100,0)-INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))*100),"00")&amp;" руб., в том числе:"</f>
         <v/>
       </c>
-      <c r="C8" s="80" t="n"/>
-      <c r="D8" s="80" t="n"/>
-      <c r="E8" s="80" t="n"/>
-      <c r="F8" s="80" t="n"/>
+      <c r="C8" s="81" t="n"/>
+      <c r="D8" s="81" t="n"/>
+      <c r="E8" s="81" t="n"/>
+      <c r="F8" s="81" t="n"/>
     </row>
     <row r="9" ht="8" customHeight="1"/>
     <row r="10" ht="38" customHeight="1">
-      <c r="B10" s="80">
+      <c r="B10" s="81">
         <f>"— текущий платёж за период с апреля по июнь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года ("&amp;"II квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;") в размере "&amp;IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100),"00")&amp;" рублей"</f>
         <v/>
       </c>
-      <c r="C10" s="80" t="n"/>
-      <c r="D10" s="80" t="n"/>
-      <c r="E10" s="80" t="n"/>
-      <c r="F10" s="80" t="n"/>
+      <c r="C10" s="81" t="n"/>
+      <c r="D10" s="81" t="n"/>
+      <c r="E10" s="81" t="n"/>
+      <c r="F10" s="81" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="81">
+      <c r="B11" s="82">
         <f>"("&amp;UPPER(LEFT(IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)=0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)=0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1),2,300)&amp;")."</f>
         <v/>
       </c>
-      <c r="C11" s="81" t="n"/>
-      <c r="D11" s="81" t="n"/>
-      <c r="E11" s="81" t="n"/>
-      <c r="F11" s="81" t="n"/>
+      <c r="C11" s="82" t="n"/>
+      <c r="D11" s="82" t="n"/>
+      <c r="E11" s="82" t="n"/>
+      <c r="F11" s="82" t="n"/>
     </row>
     <row r="12" ht="6" customHeight="1"/>
     <row r="13" ht="32" customHeight="1">
-      <c r="B13" s="80">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$31=0,"— задолженности за предыдущие периоды нет.","— задолженность "&amp;IF('ИСХОДНЫЕ ДАННЫЕ'!$D$31="","за предыдущие периоды",'ИСХОДНЫЕ ДАННЫЕ'!$D$31)&amp;" в размере "&amp;IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)&gt;0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)&amp;" "&amp;TEXT((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000),"000"),(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))*100),"00")&amp;" рублей")</f>
+      <c r="B13" s="81">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$32=0,"— задолженности за предыдущие периоды нет.","— задолженность "&amp;IF('ИСХОДНЫЕ ДАННЫЕ'!$D$32="","за предыдущие периоды",'ИСХОДНЫЕ ДАННЫЕ'!$D$32)&amp;" в размере "&amp;IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)&gt;0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)&amp;" "&amp;TEXT((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000),"000"),(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))*100),"00")&amp;" рублей")</f>
         <v/>
       </c>
-      <c r="C13" s="80" t="n"/>
-      <c r="D13" s="80" t="n"/>
-      <c r="E13" s="80" t="n"/>
-      <c r="F13" s="80" t="n"/>
+      <c r="C13" s="81" t="n"/>
+      <c r="D13" s="81" t="n"/>
+      <c r="E13" s="81" t="n"/>
+      <c r="F13" s="81" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="81">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$31=0,"","("&amp;UPPER(LEFT(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$31,2))*100)+1),2,300)&amp;").")</f>
+      <c r="B14" s="82">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$32=0,"","("&amp;UPPER(LEFT(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))*100)+1),2,300)&amp;").")</f>
         <v/>
       </c>
-      <c r="C14" s="81" t="n"/>
-      <c r="D14" s="81" t="n"/>
-      <c r="E14" s="81" t="n"/>
-      <c r="F14" s="81" t="n"/>
+      <c r="C14" s="82" t="n"/>
+      <c r="D14" s="82" t="n"/>
+      <c r="E14" s="82" t="n"/>
+      <c r="F14" s="82" t="n"/>
     </row>
     <row r="15" ht="10" customHeight="1"/>
     <row r="16" ht="90" customHeight="1">
-      <c r="B16" s="80">
-        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$31)&amp;" и с учётом начислений по "&amp;"июнь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
+      <c r="B16" s="81">
+        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$32)&amp;" и с учётом начислений по "&amp;"июнь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
       </c>
-      <c r="C16" s="80" t="n"/>
-      <c r="D16" s="80" t="n"/>
-      <c r="E16" s="80" t="n"/>
-      <c r="F16" s="80" t="n"/>
+      <c r="C16" s="81" t="n"/>
+      <c r="D16" s="81" t="n"/>
+      <c r="E16" s="81" t="n"/>
+      <c r="F16" s="81" t="n"/>
     </row>
     <row r="17" ht="10" customHeight="1"/>
     <row r="18" ht="54" customHeight="1">
-      <c r="B18" s="80">
+      <c r="B18" s="81">
         <f>"В случае возникновения дополнительных вопросов прошу связаться со мной по электронной почте "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22&amp;" или по телефону "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
       </c>
-      <c r="C18" s="80" t="n"/>
-      <c r="D18" s="80" t="n"/>
-      <c r="E18" s="80" t="n"/>
-      <c r="F18" s="80" t="n"/>
+      <c r="C18" s="81" t="n"/>
+      <c r="D18" s="81" t="n"/>
+      <c r="E18" s="81" t="n"/>
+      <c r="F18" s="81" t="n"/>
     </row>
     <row r="19" ht="14" customHeight="1"/>
     <row r="20" ht="20" customHeight="1">
-      <c r="B20" s="79" t="inlineStr">
+      <c r="B20" s="80" t="inlineStr">
         <is>
           <t>ПРИЛОЖЕНИЯ:</t>
         </is>
       </c>
-      <c r="C20" s="79" t="n"/>
-      <c r="D20" s="79" t="n"/>
-      <c r="E20" s="79" t="n"/>
-      <c r="F20" s="79" t="n"/>
+      <c r="C20" s="80" t="n"/>
+      <c r="D20" s="80" t="n"/>
+      <c r="E20" s="80" t="n"/>
+      <c r="F20" s="80" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="80">
-        <f>"1) Акт взаимных расчётов по состоянию на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$31),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$31)&amp;" — один экземпляр на 1 л."</f>
+      <c r="B21" s="81">
+        <f>"1) Акт взаимных расчётов по состоянию на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$32)&amp;" — один экземпляр на 1 л."</f>
         <v/>
       </c>
-      <c r="C21" s="80" t="n"/>
-      <c r="D21" s="80" t="n"/>
-      <c r="E21" s="80" t="n"/>
-      <c r="F21" s="80" t="n"/>
+      <c r="C21" s="81" t="n"/>
+      <c r="D21" s="81" t="n"/>
+      <c r="E21" s="81" t="n"/>
+      <c r="F21" s="81" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="80">
+      <c r="B22" s="81">
         <f>"2) Квитанция для оплаты за "&amp;"II квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — один экземпляр на 1 л."</f>
         <v/>
       </c>
-      <c r="C22" s="80" t="n"/>
-      <c r="D22" s="80" t="n"/>
-      <c r="E22" s="80" t="n"/>
-      <c r="F22" s="80" t="n"/>
+      <c r="C22" s="81" t="n"/>
+      <c r="D22" s="81" t="n"/>
+      <c r="E22" s="81" t="n"/>
+      <c r="F22" s="81" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1"/>
     <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="80">
+      <c r="B24" s="81">
         <f>"«______» ______________ "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="C24" s="80" t="n"/>
+      <c r="C24" s="81" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1"/>
     <row r="26" ht="16" customHeight="1">
-      <c r="B26" s="80" t="inlineStr">
+      <c r="B26" s="81" t="inlineStr">
         <is>
           <t>Председатель</t>
         </is>
       </c>
-      <c r="C26" s="80" t="n"/>
+      <c r="C26" s="81" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="B27" s="80">
+      <c r="B27" s="81">
         <f>"МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15</f>
         <v/>
       </c>
-      <c r="C27" s="80" t="n"/>
-      <c r="D27" s="82">
+      <c r="C27" s="81" t="n"/>
+      <c r="D27" s="83">
         <f>"___________________  /"&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$19&amp;"/"</f>
         <v/>
       </c>
-      <c r="E27" s="82" t="n"/>
-      <c r="F27" s="82" t="n"/>
+      <c r="E27" s="83" t="n"/>
+      <c r="F27" s="83" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -35343,7 +35352,7 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="D6:F6"/>
   </mergeCells>
-  <pageMargins left="0.79" right="0.39" top="0.59" bottom="0.59" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.39" top="0.51" bottom="0.51" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
@@ -35358,198 +35367,198 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="0.8" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="0.8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="D1" s="79">
-        <f>"В "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$24</f>
+      <c r="D1" s="80">
+        <f>"В "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$25</f>
         <v/>
       </c>
-      <c r="E1" s="79" t="n"/>
-      <c r="F1" s="79" t="n"/>
+      <c r="E1" s="80" t="n"/>
+      <c r="F1" s="80" t="n"/>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="D2" s="79">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$26="","",'ИСХОДНЫЕ ДАННЫЕ'!$C$25&amp;" "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$26)</f>
+      <c r="D2" s="80">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$27="","",'ИСХОДНЫЕ ДАННЫЕ'!$C$26&amp;" "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$27)</f>
         <v/>
       </c>
-      <c r="E2" s="79" t="n"/>
-      <c r="F2" s="79" t="n"/>
+      <c r="E2" s="80" t="n"/>
+      <c r="F2" s="80" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="D3" s="80">
+      <c r="D3" s="81">
         <f>"от Председателя МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15&amp;", "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$18</f>
         <v/>
       </c>
-      <c r="E3" s="80" t="n"/>
-      <c r="F3" s="80" t="n"/>
+      <c r="E3" s="81" t="n"/>
+      <c r="F3" s="81" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="D4" s="80">
+      <c r="D4" s="81">
         <f>"проживающей по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$20</f>
         <v/>
       </c>
-      <c r="E4" s="80" t="n"/>
-      <c r="F4" s="80" t="n"/>
+      <c r="E4" s="81" t="n"/>
+      <c r="F4" s="81" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="D5" s="80">
+      <c r="D5" s="81">
         <f>"Конт. тел.: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21</f>
         <v/>
       </c>
-      <c r="E5" s="80" t="n"/>
-      <c r="F5" s="80" t="n"/>
+      <c r="E5" s="81" t="n"/>
+      <c r="F5" s="81" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="D6" s="80">
+      <c r="D6" s="81">
         <f>"Эл. почта: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22</f>
         <v/>
       </c>
-      <c r="E6" s="80" t="n"/>
-      <c r="F6" s="80" t="n"/>
+      <c r="E6" s="81" t="n"/>
+      <c r="F6" s="81" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1"/>
     <row r="8" ht="54" customHeight="1">
-      <c r="B8" s="80">
-        <f>"В связи с тем, что на балансе департамента числится кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", сообщаю Вам о необходимости оплатить "&amp;IF(INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2)*100,0)-INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$32,2),2))*100),"00")&amp;" руб., в том числе:"</f>
+      <c r="B8" s="81">
+        <f>"В связи с тем, что на балансе департамента числится кв. № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" по адресу: "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;", сообщаю Вам о необходимости оплатить "&amp;IF(INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))-INT(INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2)*100,0)-INT(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2)+'ИСХОДНЫЕ ДАННЫЕ'!$C$33,2),2))*100),"00")&amp;" руб., в том числе:"</f>
         <v/>
       </c>
-      <c r="C8" s="80" t="n"/>
-      <c r="D8" s="80" t="n"/>
-      <c r="E8" s="80" t="n"/>
-      <c r="F8" s="80" t="n"/>
+      <c r="C8" s="81" t="n"/>
+      <c r="D8" s="81" t="n"/>
+      <c r="E8" s="81" t="n"/>
+      <c r="F8" s="81" t="n"/>
     </row>
     <row r="9" ht="8" customHeight="1"/>
     <row r="10" ht="38" customHeight="1">
-      <c r="B10" s="80">
+      <c r="B10" s="81">
         <f>"— текущий платёж за период с июля по сентябрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года ("&amp;"III квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;") в размере "&amp;IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&amp;" "&amp;TEXT((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000),"000"),(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100),"00")&amp;" рублей"</f>
         <v/>
       </c>
-      <c r="C10" s="80" t="n"/>
-      <c r="D10" s="80" t="n"/>
-      <c r="E10" s="80" t="n"/>
-      <c r="F10" s="80" t="n"/>
+      <c r="C10" s="81" t="n"/>
+      <c r="D10" s="81" t="n"/>
+      <c r="E10" s="81" t="n"/>
+      <c r="F10" s="81" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="81">
+      <c r="B11" s="82">
         <f>"("&amp;UPPER(LEFT(IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)=0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)=0,INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))-INT(INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2)*100,0)-INT(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$8*3,2),2))*100)+1),2,300)&amp;")."</f>
         <v/>
       </c>
-      <c r="C11" s="81" t="n"/>
-      <c r="D11" s="81" t="n"/>
-      <c r="E11" s="81" t="n"/>
-      <c r="F11" s="81" t="n"/>
+      <c r="C11" s="82" t="n"/>
+      <c r="D11" s="82" t="n"/>
+      <c r="E11" s="82" t="n"/>
+      <c r="F11" s="82" t="n"/>
     </row>
     <row r="12" ht="6" customHeight="1"/>
     <row r="13" ht="32" customHeight="1">
-      <c r="B13" s="80">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$32=0,"— задолженности за предыдущие периоды нет.","— задолженность "&amp;IF('ИСХОДНЫЕ ДАННЫЕ'!$D$32="","за предыдущие периоды",'ИСХОДНЫЕ ДАННЫЕ'!$D$32)&amp;" в размере "&amp;IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)&gt;0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)&amp;" "&amp;TEXT((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000),"000"),(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))*100),"00")&amp;" рублей")</f>
+      <c r="B13" s="81">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$33=0,"— задолженности за предыдущие периоды нет.","— задолженность "&amp;IF('ИСХОДНЫЕ ДАННЫЕ'!$D$33="","за предыдущие периоды",'ИСХОДНЫЕ ДАННЫЕ'!$D$33)&amp;" в размере "&amp;IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)&gt;0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)&amp;" "&amp;TEXT((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000),"000"),(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)&amp;"")&amp;","&amp;TEXT((ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))*100),"00")&amp;" рублей")</f>
         <v/>
       </c>
-      <c r="C13" s="80" t="n"/>
-      <c r="D13" s="80" t="n"/>
-      <c r="E13" s="80" t="n"/>
-      <c r="F13" s="80" t="n"/>
+      <c r="C13" s="81" t="n"/>
+      <c r="D13" s="81" t="n"/>
+      <c r="E13" s="81" t="n"/>
+      <c r="F13" s="81" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="81">
-        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$32=0,"","("&amp;UPPER(LEFT(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$32,2))*100)+1),2,300)&amp;").")</f>
+      <c r="B14" s="82">
+        <f>IF('ИСХОДНЫЕ ДАННЫЕ'!$C$33=0,"","("&amp;UPPER(LEFT(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))*100)+1),1))&amp;MID(IF(INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)&gt;0,INDEX('ПРОПИСЬ'!$D$2:$D$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$E$2:$E$1001,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)+1)&amp;" ","")&amp;IF(AND((INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)=0,INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)&gt;0),"",INDEX('ПРОПИСЬ'!$B$2:$B$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)+1)&amp;" ")&amp;INDEX('ПРОПИСЬ'!$C$2:$C$1001,(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))-INT(INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))/1000)*1000)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$D$2:$D$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))*100)+1)&amp;" "&amp;INDEX('ПРОПИСЬ'!$F$2:$F$1001,(ROUND(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2)*100,0)-INT(ROUND('ИСХОДНЫЕ ДАННЫЕ'!$C$33,2))*100)+1),2,300)&amp;").")</f>
         <v/>
       </c>
-      <c r="C14" s="81" t="n"/>
-      <c r="D14" s="81" t="n"/>
-      <c r="E14" s="81" t="n"/>
-      <c r="F14" s="81" t="n"/>
+      <c r="C14" s="82" t="n"/>
+      <c r="D14" s="82" t="n"/>
+      <c r="E14" s="82" t="n"/>
+      <c r="F14" s="82" t="n"/>
     </row>
     <row r="15" ht="10" customHeight="1"/>
     <row r="16" ht="90" customHeight="1">
-      <c r="B16" s="80">
-        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$44&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$32)&amp;" и с учётом начислений по "&amp;"сентябрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
+      <c r="B16" s="81">
+        <f>"Для сведения и сверки оплат направляю акт взаимных расчётов по взносам на капитальный ремонт по квартире № "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$12&amp;" с учётом всех поступивших платежей на специальный счёт МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$14&amp;" (р/счёт "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$45&amp;") по состоянию расчётов на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$33)&amp;" и с учётом начислений по "&amp;"сентябрь "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" года включительно."</f>
         <v/>
       </c>
-      <c r="C16" s="80" t="n"/>
-      <c r="D16" s="80" t="n"/>
-      <c r="E16" s="80" t="n"/>
-      <c r="F16" s="80" t="n"/>
+      <c r="C16" s="81" t="n"/>
+      <c r="D16" s="81" t="n"/>
+      <c r="E16" s="81" t="n"/>
+      <c r="F16" s="81" t="n"/>
     </row>
     <row r="17" ht="10" customHeight="1"/>
     <row r="18" ht="54" customHeight="1">
-      <c r="B18" s="80">
+      <c r="B18" s="81">
         <f>"В случае возникновения дополнительных вопросов прошу связаться со мной по электронной почте "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$22&amp;" или по телефону "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$21&amp;"."</f>
         <v/>
       </c>
-      <c r="C18" s="80" t="n"/>
-      <c r="D18" s="80" t="n"/>
-      <c r="E18" s="80" t="n"/>
-      <c r="F18" s="80" t="n"/>
+      <c r="C18" s="81" t="n"/>
+      <c r="D18" s="81" t="n"/>
+      <c r="E18" s="81" t="n"/>
+      <c r="F18" s="81" t="n"/>
     </row>
     <row r="19" ht="14" customHeight="1"/>
     <row r="20" ht="20" customHeight="1">
-      <c r="B20" s="79" t="inlineStr">
+      <c r="B20" s="80" t="inlineStr">
         <is>
           <t>ПРИЛОЖЕНИЯ:</t>
         </is>
       </c>
-      <c r="C20" s="79" t="n"/>
-      <c r="D20" s="79" t="n"/>
-      <c r="E20" s="79" t="n"/>
-      <c r="F20" s="79" t="n"/>
+      <c r="C20" s="80" t="n"/>
+      <c r="D20" s="80" t="n"/>
+      <c r="E20" s="80" t="n"/>
+      <c r="F20" s="80" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="80">
-        <f>"1) Акт взаимных расчётов по состоянию на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$32),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$32)&amp;" — один экземпляр на 1 л."</f>
+      <c r="B21" s="81">
+        <f>"1) Акт взаимных расчётов по состоянию на "&amp;TEXT(DAY('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;TEXT(MONTH('ИСХОДНЫЕ ДАННЫЕ'!$E$33),"00")&amp;"."&amp;YEAR('ИСХОДНЫЕ ДАННЫЕ'!$E$33)&amp;" — один экземпляр на 1 л."</f>
         <v/>
       </c>
-      <c r="C21" s="80" t="n"/>
-      <c r="D21" s="80" t="n"/>
-      <c r="E21" s="80" t="n"/>
-      <c r="F21" s="80" t="n"/>
+      <c r="C21" s="81" t="n"/>
+      <c r="D21" s="81" t="n"/>
+      <c r="E21" s="81" t="n"/>
+      <c r="F21" s="81" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="80">
+      <c r="B22" s="81">
         <f>"2) Квитанция для оплаты за "&amp;"III квартал "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."&amp;" — один экземпляр на 1 л."</f>
         <v/>
       </c>
-      <c r="C22" s="80" t="n"/>
-      <c r="D22" s="80" t="n"/>
-      <c r="E22" s="80" t="n"/>
-      <c r="F22" s="80" t="n"/>
+      <c r="C22" s="81" t="n"/>
+      <c r="D22" s="81" t="n"/>
+      <c r="E22" s="81" t="n"/>
+      <c r="F22" s="81" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1"/>
     <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="80">
+      <c r="B24" s="81">
         <f>"«______» ______________ "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$5&amp;" г."</f>
         <v/>
       </c>
-      <c r="C24" s="80" t="n"/>
+      <c r="C24" s="81" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1"/>
     <row r="26" ht="16" customHeight="1">
-      <c r="B26" s="80" t="inlineStr">
+      <c r="B26" s="81" t="inlineStr">
         <is>
           <t>Председатель</t>
         </is>
       </c>
-      <c r="C26" s="80" t="n"/>
+      <c r="C26" s="81" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="B27" s="80">
+      <c r="B27" s="81">
         <f>"МКД "&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$15</f>
         <v/>
       </c>
-      <c r="C27" s="80" t="n"/>
-      <c r="D27" s="82">
+      <c r="C27" s="81" t="n"/>
+      <c r="D27" s="83">
         <f>"___________________  /"&amp;'ИСХОДНЫЕ ДАННЫЕ'!$C$19&amp;"/"</f>
         <v/>
       </c>
-      <c r="E27" s="82" t="n"/>
-      <c r="F27" s="82" t="n"/>
+      <c r="E27" s="83" t="n"/>
+      <c r="F27" s="83" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -35574,7 +35583,7 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="D6:F6"/>
   </mergeCells>
-  <pageMargins left="0.79" right="0.39" top="0.59" bottom="0.59" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.39" top="0.51" bottom="0.51" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>